--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,413 +656,425 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45199</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45108</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45017</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44926</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44835</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44744</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44653</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44561</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44471</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44380</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44289</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44196</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44100</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44009</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43918</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43830</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43736</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43645</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43554</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43465</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43372</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43281</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43190</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43008</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42917</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42826</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42735</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2612300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2766200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2950400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2806200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2650700</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2917500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>3153200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3015700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2760700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2817000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2953800</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2669000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2641800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2574900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2049800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2285800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2424500</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2519200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2584500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2442500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2448600</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2545800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2577000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1967700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2031500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2188100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2133700</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2060300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2173500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2279300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2212600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2020900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1979200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2046300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1867100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1880800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1851000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1629800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1657500</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1759300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1820000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1842000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1785000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1791900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1815200</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1798400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>644600</v>
+      </c>
+      <c r="E10" s="3">
         <v>734700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>762300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>672500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>590400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>744000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>873900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>803100</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>739800</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>837900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>907500</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>801900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>761000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>723900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>420000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>628300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>665200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>699200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>742500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>657500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>656700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>730600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>778600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>719200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AB10" s="3">
-        <v>792100</v>
       </c>
       <c r="AC10" s="3">
         <v>792100</v>
       </c>
       <c r="AD10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AE10" s="3">
         <v>683100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>703300</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1095,8 +1107,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1187,8 +1200,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1279,100 +1295,106 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E14" s="3">
         <v>923200</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41700</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>32100</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>730300</v>
-      </c>
-      <c r="I14" s="3">
-        <v>1900</v>
       </c>
       <c r="J14" s="3">
         <v>1900</v>
       </c>
       <c r="K14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="L14" s="3">
         <v>4600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>1100</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>6800</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>11200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>26100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26500</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>67200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>12700</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>41800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>74700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>8900</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>35700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>20600</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>19900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>16000</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>22100</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>15200</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>13900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>4000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>16200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1433,8 +1455,8 @@
       <c r="V15" s="3">
         <v>0</v>
       </c>
-      <c r="W15" s="3" t="s">
-        <v>8</v>
+      <c r="W15" s="3">
+        <v>0</v>
       </c>
       <c r="X15" s="3" t="s">
         <v>8</v>
@@ -1445,8 +1467,8 @@
       <c r="Z15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA15" s="3">
-        <v>0</v>
+      <c r="AA15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB15" s="3">
         <v>0</v>
@@ -1463,8 +1485,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1494,192 +1519,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2445200</v>
+      </c>
+      <c r="E17" s="3">
         <v>3499900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2797400</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2680400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2589600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>3423100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2785300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2694900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2507600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2457000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2549400</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2351500</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2359000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2312100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2114400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2134300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2264400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2344100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2317600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2277200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2235200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2258600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2250700</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>167100</v>
+      </c>
+      <c r="E18" s="3">
         <v>-733700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>153000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>125800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>61100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>-505600</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>367900</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>320800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>253100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>360000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>404400</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>317500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>282800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>262800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-64600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>151500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>160100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>175100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>266900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>165300</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>213400</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>287200</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>326300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>268400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>343500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>380100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>355800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>274700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>305300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1712,468 +1744,484 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E20" s="3">
         <v>8500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-2200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-10000</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>1300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2800</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-2500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
-        <v>0</v>
-      </c>
       <c r="M20" s="3">
+        <v>0</v>
+      </c>
+      <c r="N20" s="3">
         <v>11200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>6700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2600</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-5700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>4300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>12400</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>3000</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-2100</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>2900</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>325200</v>
+      </c>
+      <c r="E21" s="3">
         <v>-575600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>307500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>296300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>210100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>-350900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>512300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>459800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>395400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>508600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>564100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>471000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>446000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>414800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>92100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>291300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>318100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>332400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>410400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>306400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>352000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>419500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>451300</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>387100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>458100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>492300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>462600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>382600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>412800</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>17400</v>
+      </c>
+      <c r="E22" s="3">
         <v>20100</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>22900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>13800</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>11500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12200</v>
-      </c>
-      <c r="L22" s="3">
-        <v>14900</v>
       </c>
       <c r="M22" s="3">
         <v>14900</v>
       </c>
       <c r="N22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="O22" s="3">
         <v>15200</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>15900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13000</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>8700</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>9300</v>
-      </c>
-      <c r="U22" s="3">
-        <v>10500</v>
       </c>
       <c r="V22" s="3">
         <v>10500</v>
       </c>
       <c r="W22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="X22" s="3">
         <v>14400</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>7900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>7300</v>
       </c>
       <c r="AB22" s="3">
         <v>7300</v>
       </c>
       <c r="AC22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AD22" s="3">
         <v>8400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>8200</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8500</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>153600</v>
+      </c>
+      <c r="E23" s="3">
         <v>-745300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>128000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>109200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>36500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-518100</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>358700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>306900</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>239800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>345000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>400700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>304500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>273600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>248600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-75000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>137100</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>153400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>178200</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>259400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>158600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>198500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>277500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>316400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>256900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>332500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>371600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>344400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>269400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>300000</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4200</v>
+      </c>
+      <c r="E24" s="3">
         <v>15000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>26800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>28900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>2900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15600</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>78200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>61400</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>50700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>73800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>64200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>67700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>25200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>43200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>-26400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>26700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-111300</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>22500</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>56700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>37000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-59800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>49500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>118800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>47600</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>46300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>100500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>82700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>68400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>65500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2264,192 +2312,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E26" s="3">
         <v>-760300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>101200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>80300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>33600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-533700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>280500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>245400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>189100</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>271200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>336500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>236800</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>248400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>205500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-48600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>110500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>264700</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>155700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>202700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>121600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>258200</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>228000</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>197500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>209200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>286100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>271000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>261700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>201100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>234500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E27" s="3">
         <v>-760500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>101200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>80200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>33500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-534000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>280400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>245300</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>189100</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>271000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>336300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>236800</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>248200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>205100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-48300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>110500</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>264700</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>155500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>202400</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>121600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>254600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>226300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>196600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>208500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>285600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>270000</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>260700</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>200600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>233700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2540,31 +2597,34 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
-      </c>
-      <c r="E29" s="3">
-        <v>0</v>
-      </c>
-      <c r="F29" s="3">
-        <v>0</v>
-      </c>
-      <c r="G29" s="3">
-        <v>0</v>
-      </c>
-      <c r="H29" s="3">
-        <v>0</v>
-      </c>
-      <c r="I29" s="3">
-        <v>0</v>
-      </c>
-      <c r="J29" s="3">
-        <v>0</v>
+        <v>-10000</v>
+      </c>
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K29" s="3">
         <v>0</v>
@@ -2584,17 +2644,17 @@
       <c r="P29" s="3">
         <v>0</v>
       </c>
-      <c r="Q29" s="3" t="s">
-        <v>8</v>
+      <c r="Q29" s="3">
+        <v>0</v>
       </c>
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
-      </c>
-      <c r="T29" s="3" t="s">
+      <c r="S29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
@@ -2602,11 +2662,11 @@
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
+      <c r="W29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="X29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2614,11 +2674,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2632,8 +2692,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2724,8 +2787,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2816,192 +2882,201 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-8500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>2200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>10000</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-1300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2800</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>2500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
-        <v>0</v>
-      </c>
       <c r="M32" s="3">
+        <v>0</v>
+      </c>
+      <c r="N32" s="3">
         <v>-11200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-6700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2600</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>5700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-4300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-12400</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-3000</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>2100</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>4000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>3800</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E33" s="3">
         <v>-760500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>101200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>80200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>33500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-534000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>280400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>245300</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>189100</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>271000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>336300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>236800</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>248200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>205100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-48300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>110500</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>264700</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>155500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>202400</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>121600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>226400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>226300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>196600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>208500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>240400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>270000</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>260700</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>200600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>233700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3092,197 +3167,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E35" s="3">
         <v>-760500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>101200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>80200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>33500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-534000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>280400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>245300</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>189100</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>271000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>336300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>236800</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>248200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>205100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-48300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>110500</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>264700</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>155500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>202400</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>121600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>226400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>226300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>196600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>208500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>240400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>270000</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>260700</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>200600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>233700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45199</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45108</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45017</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44926</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44835</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44744</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44653</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44561</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44471</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44380</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44289</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44196</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44100</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44009</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43918</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43830</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43736</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43645</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43554</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43465</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43372</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43281</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43190</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43008</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42917</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42826</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42735</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3315,8 +3399,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3349,100 +3434,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>642600</v>
+      </c>
+      <c r="E41" s="3">
         <v>518500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>570900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>572900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>509600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>327000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>224000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>230600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>268900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>1128000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>753700</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>557300</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>768600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>781200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>737700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>263100</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>134800</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>111300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>128100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>105700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>119100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>91400</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>518200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>114800</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>84900</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>84500</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>130200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>188400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>121700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3453,40 +3542,40 @@
         <v>0</v>
       </c>
       <c r="F42" s="3">
+        <v>0</v>
+      </c>
+      <c r="G42" s="3">
         <v>150000</v>
       </c>
-      <c r="G42" s="3">
+      <c r="H42" s="3">
         <v>158000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>110000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>265000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>310000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>323000</v>
       </c>
-      <c r="L42" s="3">
-        <v>0</v>
-      </c>
       <c r="M42" s="3">
+        <v>0</v>
+      </c>
+      <c r="N42" s="3">
         <v>662400</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>782300</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>571700</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>407800</v>
-      </c>
-      <c r="Q42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="R42" s="3" t="s">
         <v>8</v>
@@ -3503,8 +3592,8 @@
       <c r="V42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W42" s="3">
-        <v>0</v>
+      <c r="W42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X42" s="3">
         <v>0</v>
@@ -3533,376 +3622,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1874700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1943100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2087100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2052400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1904800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2003300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2105800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2044700</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1840000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1880500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2017600</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1813900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1709500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1711000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1586400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1644800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1526600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1787200</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1819500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1743600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1606200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1755700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1737900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2551900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2519700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2618700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2729900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2793800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2900100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2826000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2513200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2391700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2215600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2082000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>1996600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1913000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1842000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1922000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2195400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2282300</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2338000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2367600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2338100</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2287600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2214300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2061200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>535200</v>
+      </c>
+      <c r="E45" s="3">
         <v>523000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>574600</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>556000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>528900</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>514000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>519900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>466200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>414800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>421900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>434900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>416000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>400800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>410000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>499800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>509800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>485700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>491400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>493100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>501600</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>496500</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>487100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>456300</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>447300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>481300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>345500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>374900</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>307800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>297900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5604200</v>
+      </c>
+      <c r="E46" s="3">
         <v>5504300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5851300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6061100</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5895100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5854300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5940700</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5564700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5238400</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5646100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5950600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5566000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5363700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5152000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>4746000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4613000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4429500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4727800</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4808300</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4689000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4509300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4548500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4773700</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3993,192 +4097,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5421700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5193300</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5357600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5342000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5049000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4924900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4986800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4937400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5026800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4827900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4842700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4769900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4914400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4708300</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4752600</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4804200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5021900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4934700</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5058000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4995200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4699900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4586200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4421100</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2035100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1979900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2919000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2915500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2785700</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2651100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>3392700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3462900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3507900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3523500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3531900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3516600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3602400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3493400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3452700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3424000</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3498900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3436200</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3516300</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3499600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3482800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3466800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3305600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4269,8 +4382,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4361,100 +4477,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>498800</v>
+      </c>
+      <c r="E52" s="3">
         <v>461000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>457200</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>444800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>390600</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>370700</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>369200</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>421700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>451400</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>452800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>467600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>437600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>447300</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>430500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>418100</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>415700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>436400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>294100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>423400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>421300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>407100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>399400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>393700</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>389900</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>387900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>390900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>391200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>357500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>279700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4545,100 +4667,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13559900</v>
+      </c>
+      <c r="E54" s="3">
         <v>13138500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>14585200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14763500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14120400</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13801000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14689500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14386700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14224500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14450300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14792800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14290100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14327800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13784200</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13369400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13256900</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13386700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13392800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13806100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13605100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13099100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13000900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>12894000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4671,8 +4799,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4705,560 +4834,579 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1038000</v>
+      </c>
+      <c r="E57" s="3">
         <v>1082400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1184100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1211700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1094000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1217700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1359200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1296100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1228600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1147000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1131200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1064800</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1016900</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>989900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>845300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>899200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>825000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>964100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>976200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>914200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>811900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>925200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>951200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>897500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>810000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>859900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>871400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>780500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>729400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>1001700</v>
+      </c>
+      <c r="E58" s="3">
         <v>922700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1038000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1056500</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>840600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1542100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1498900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1546500</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>624500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>588700</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>958800</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>953900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>377300</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>356100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>135400</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1210500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1051500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1273200</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1891500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1763300</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1742400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1333900</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1146500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1106200</v>
+      </c>
+      <c r="E59" s="3">
         <v>1183500</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1065800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1050200</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1135700</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1144900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1066300</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1029100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1093200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1166100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1088900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>988600</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>977100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1041100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>891600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>761600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>836100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>877400</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>838000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>756700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>712000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>698200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>638400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>566500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>641600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>664300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>595200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>549900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>606200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3145900</v>
+      </c>
+      <c r="E60" s="3">
         <v>3188600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3287900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3318400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3070300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3904700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3924400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3871600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>2946400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2901700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3178900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3007300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2371200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2387100</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>1872200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2871300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2712600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3114700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3705800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3434200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3266200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2957300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2736100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1701800</v>
+      </c>
+      <c r="E61" s="3">
         <v>1675600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2013300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2265100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1978600</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1020000</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1052100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1088400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1700300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1710200</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1723300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1719100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2356900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2282800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2573200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1514000</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1518400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1483600</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1169500</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1498000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1515600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1528600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1884000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1083000</v>
+      </c>
+      <c r="E62" s="3">
         <v>1002900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1071900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1074200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1053700</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1051200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1106100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1139100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1149700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1085900</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1116700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1064600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1058500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>947300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>999200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1024000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1029300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1029200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1109200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1095800</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>877200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>912100</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>870500</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>801900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>783100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>755000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>713100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>677900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>576300</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5349,8 +5497,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5441,8 +5592,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5533,100 +5687,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5936800</v>
+      </c>
+      <c r="E66" s="3">
         <v>5873000</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>6379100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6664000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6108900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5982300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6088900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6105700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5803100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5704800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6025700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5797600</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5793400</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5623600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5450600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5415600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5266800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5634000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5991000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6034300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5665300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5437200</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5528500</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5659,8 +5819,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5751,8 +5912,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5843,8 +6007,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5935,8 +6102,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6027,100 +6197,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>6970200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6830800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7591200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7490000</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7409800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7376300</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7910700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7630800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7692100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7930000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7867800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7673100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7559200</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7430900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7225800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7274100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7232300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>6991100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6903300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6709800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6588200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6635900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6409600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6211,8 +6387,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6303,8 +6482,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6395,100 +6577,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7623100</v>
+      </c>
+      <c r="E76" s="3">
         <v>7265500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8206100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8099500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8011500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7818800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8600600</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8281000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8421400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8745500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8767100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8492400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8534300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8160700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7918800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7841400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8119800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7758800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7815100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7570800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7433800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7563800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7365600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6579,197 +6767,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45199</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45108</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45017</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44926</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44835</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44744</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44653</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44561</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44471</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44380</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44289</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44196</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44100</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44009</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43918</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43830</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43736</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43645</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43554</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43465</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43372</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43281</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43190</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43008</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42917</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42826</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42735</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>139500</v>
+      </c>
+      <c r="E81" s="3">
         <v>-760500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>101200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>80200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>33500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-534000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>280400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>245300</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>189100</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>271000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>336300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>236800</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>248200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>205100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-48300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>110500</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>264700</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>155500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>202400</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>121600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>226400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>226300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>196600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>208500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>240400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>270000</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>260700</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>200600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>233700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6802,100 +6999,104 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>154200</v>
+      </c>
+      <c r="E83" s="3">
         <v>149600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>156600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>169900</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>159000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>153500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>141600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>141400</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>143400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>148600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>148500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>151200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>156600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>151300</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>154100</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>145500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>153800</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>144900</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>140500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>137300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>139100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>133000</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>127000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>122700</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>118400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>113500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>109800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>105000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>104400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6986,8 +7187,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7078,8 +7282,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7170,8 +7377,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7262,8 +7472,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7354,100 +7567,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>296300</v>
+      </c>
+      <c r="E89" s="3">
         <v>512000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>263600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>257300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>241700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>224800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>147700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>55000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>212400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>498700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>338400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>259600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>407800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>598500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>568500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>195000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>440700</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>411800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>396200</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>170100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>286900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>273500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>437800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>183200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>319400</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>460300</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>248000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>165900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>342900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7480,100 +7699,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-127400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-116700</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-128500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-150700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-150000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-150600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-129500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-300900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-147700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-112700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-114700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-160100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-69100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-80600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-115600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-139800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-124600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-144100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-136900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-151200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-144600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-247400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7664,8 +7887,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7756,100 +7982,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-240400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-127400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>37300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-639900</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-251000</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-153300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-105600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-115500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-670700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>442500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>4800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-333300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-324100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-420200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-77000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-133400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-141600</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-120600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-142100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-211800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-303900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-542500</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-244400</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7882,8 +8114,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7974,8 +8207,11 @@
       <c r="AF96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8066,8 +8302,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8158,8 +8397,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8250,280 +8492,292 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>63100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-430000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-294700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>451000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>197300</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>39900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-51800</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>9000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-397300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-559200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-155600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-120200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-119100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-132000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-24200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>87200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-279600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-304900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-232200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>26800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>46500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-156500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>221400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>86600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>16300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>166400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>90900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>13300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-3500</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-7700</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>8900</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-17500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>22800</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>7400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-20400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>4000</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3100</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>600</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>1500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-1800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-11400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1600</v>
       </c>
-      <c r="AA101" s="3">
-        <v>0</v>
-      </c>
       <c r="AB101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC101" s="3">
         <v>4100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1200</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>12100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>700</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>124100</v>
+      </c>
+      <c r="E102" s="3">
         <v>-52500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>63200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>182700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>103000</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-6600</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-38300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-859100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>374400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>196400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-211400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-12600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>43500</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>474600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>128300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>23500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-16800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>22400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-13400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>27700</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-426900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>403400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>30000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>66800</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>9600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="154" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,425 +656,438 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45199</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45108</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45017</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44926</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44835</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44744</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44653</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44561</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44471</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44380</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44289</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44196</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44100</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44009</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43918</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43830</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43736</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43645</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43554</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43465</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43372</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43281</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43190</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43008</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42917</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42826</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42735</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2679400</v>
+      </c>
+      <c r="E8" s="3">
         <v>2612300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2766200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2950400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2806200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2650700</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2917500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>3153200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3015700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2760700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2817000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2953800</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2669000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2641800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2574900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2049800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2285800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2424500</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2519200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2584500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2442500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2448600</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2545800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2024400</v>
+      </c>
+      <c r="E9" s="3">
         <v>1967700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2031500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2188100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2133700</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2060300</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2173500</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2279300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2212600</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2020900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>1979200</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2046300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1867100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1880800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1851000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1629800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1657500</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1759300</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1820000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1842000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1785000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1791900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1815200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>655000</v>
+      </c>
+      <c r="E10" s="3">
         <v>644600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>734700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>762300</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>672500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>590400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>744000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>873900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>803100</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>739800</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>837900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>907500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>801900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>761000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>723900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>420000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>628300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>665200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>699200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>742500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>657500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>656700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>730600</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>778600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>719200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AC10" s="3">
-        <v>792100</v>
       </c>
       <c r="AD10" s="3">
         <v>792100</v>
       </c>
       <c r="AE10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AF10" s="3">
         <v>683100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>703300</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1108,8 +1121,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1203,8 +1217,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1298,103 +1315,109 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>7800</v>
+      </c>
+      <c r="E14" s="3">
         <v>12400</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>923200</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>41700</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>32100</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43400</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>730300</v>
-      </c>
-      <c r="J14" s="3">
-        <v>1900</v>
       </c>
       <c r="K14" s="3">
         <v>1900</v>
       </c>
       <c r="L14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="M14" s="3">
         <v>4600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>1100</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>6800</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>11200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>26100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26500</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>67200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>12700</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>41800</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>74700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>8900</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>35700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>20600</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>19900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>16000</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>22100</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>15200</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>13900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>15900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>4000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>16200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1458,8 +1481,8 @@
       <c r="W15" s="3">
         <v>0</v>
       </c>
-      <c r="X15" s="3" t="s">
-        <v>8</v>
+      <c r="X15" s="3">
+        <v>0</v>
       </c>
       <c r="Y15" s="3" t="s">
         <v>8</v>
@@ -1470,8 +1493,8 @@
       <c r="AA15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB15" s="3">
-        <v>0</v>
+      <c r="AB15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC15" s="3">
         <v>0</v>
@@ -1488,8 +1511,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1520,198 +1546,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2532800</v>
+      </c>
+      <c r="E17" s="3">
         <v>2445200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>3499900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2797400</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2680400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2589600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>3423100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2785300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2694900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2507600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2457000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2549400</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2351500</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2359000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2312100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2114400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2134300</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2264400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2344100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2317600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2277200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2235200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2258600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>146600</v>
+      </c>
+      <c r="E18" s="3">
         <v>167100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>-733700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>153000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>125800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>61100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>-505600</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>367900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>320800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>253100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>360000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>404400</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>317500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>282800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>262800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>-64600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>151500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>160100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>175100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>266900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>165300</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>213400</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>287200</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>326300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>268400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>343500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>380100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>355800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>274700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>305300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1745,483 +1778,499 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>3900</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>8500</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-2200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-10000</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2800</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-2500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-1100</v>
       </c>
-      <c r="M20" s="3">
-        <v>0</v>
-      </c>
       <c r="N20" s="3">
+        <v>0</v>
+      </c>
+      <c r="O20" s="3">
         <v>11200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>6700</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2600</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-5700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>4300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>12400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>3000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>2900</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>3200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>301900</v>
+      </c>
+      <c r="E21" s="3">
         <v>325200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>-575600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>307500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>296300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>210100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>-350900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>512300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>459800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>395400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>508600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>564100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>471000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>446000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>414800</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>92100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>291300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>318100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>332400</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>410400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>306400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>352000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>419500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>451300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>387100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>458100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>492300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>462600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>382600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>412800</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E22" s="3">
         <v>17400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>20100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>22900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14600</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>13800</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>11500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12200</v>
-      </c>
-      <c r="M22" s="3">
-        <v>14900</v>
       </c>
       <c r="N22" s="3">
         <v>14900</v>
       </c>
       <c r="O22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="P22" s="3">
         <v>15200</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>15900</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>14900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>13000</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>8700</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>11000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>9300</v>
-      </c>
-      <c r="V22" s="3">
-        <v>10500</v>
       </c>
       <c r="W22" s="3">
         <v>10500</v>
       </c>
       <c r="X22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Y22" s="3">
         <v>14400</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>7900</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AB22" s="3">
-        <v>7300</v>
       </c>
       <c r="AC22" s="3">
         <v>7300</v>
       </c>
       <c r="AD22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AE22" s="3">
         <v>8400</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>8200</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8500</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>132800</v>
+      </c>
+      <c r="E23" s="3">
         <v>153600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>-745300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>128000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>109200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>36500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-518100</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>358700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>306900</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>239800</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>345000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>400700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>304500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>273600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>248600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>-75000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>137100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>153400</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>178200</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>259400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>158600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>198500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>277500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>316400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>256900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>332500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>371600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>344400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>269400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>300000</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>27800</v>
+      </c>
+      <c r="E24" s="3">
         <v>4200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>15000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>26800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>28900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>2900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15600</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>78200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>61400</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>50700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>73800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>64200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>67700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>25200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>43200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>-26400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>26700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-111300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>22500</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>56700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>37000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-59800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>49500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>118800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>47600</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>46300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>100500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>82700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>68400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>65500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2315,198 +2364,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E26" s="3">
         <v>149400</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>-760300</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>101200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>80300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>33600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-533700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>280500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>245400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>189100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>271200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>336500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>236800</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>248400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>205500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>-48600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>110500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>264700</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>155700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>202700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>121600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>258200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>228000</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>197500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>209200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>286100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>271000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>261700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>201100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>234500</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E27" s="3">
         <v>149500</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>-760500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>101200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>80200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>33500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-534000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>280400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>245300</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>189100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>271000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>336300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>236800</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>248200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>205100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>-48300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>110500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>264700</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>155500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>202400</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>121600</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>254600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>226300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>196600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>208500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>285600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>270000</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>260700</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>200600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>233700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2600,16 +2658,19 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3">
+      <c r="D29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E29" s="3">
         <v>-10000</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>8</v>
@@ -2626,8 +2687,8 @@
       <c r="J29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K29" s="3">
-        <v>0</v>
+      <c r="K29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L29" s="3">
         <v>0</v>
@@ -2647,17 +2708,17 @@
       <c r="Q29" s="3">
         <v>0</v>
       </c>
-      <c r="R29" s="3" t="s">
-        <v>8</v>
+      <c r="R29" s="3">
+        <v>0</v>
       </c>
       <c r="S29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T29" s="3">
-        <v>0</v>
-      </c>
-      <c r="U29" s="3" t="s">
+      <c r="T29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
@@ -2665,11 +2726,11 @@
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
+      <c r="X29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Y29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2677,11 +2738,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2695,8 +2756,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2790,8 +2854,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2885,198 +2952,207 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-3900</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-8500</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>2200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>10000</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2800</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>2500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>1100</v>
       </c>
-      <c r="M32" s="3">
-        <v>0</v>
-      </c>
       <c r="N32" s="3">
+        <v>0</v>
+      </c>
+      <c r="O32" s="3">
         <v>-11200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-6700</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2600</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>5700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-4300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-12400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-3000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>2100</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>4000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>3800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1300</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E33" s="3">
         <v>139500</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>-760500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>101200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>80200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>33500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-534000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>280400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>245300</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>189100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>271000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>336300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>236800</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>248200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>205100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>-48300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>110500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>264700</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>155500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>202400</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>121600</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>226400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>226300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>196600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>208500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>240400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>270000</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>260700</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>200600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>233700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3170,203 +3246,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E35" s="3">
         <v>139500</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>-760500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>101200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>80200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>33500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-534000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>280400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>245300</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>189100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>271000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>336300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>236800</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>248200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>205100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>-48300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>110500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>264700</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>155500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>202400</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>121600</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>226400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>226300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>196600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>208500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>240400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>270000</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>260700</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>200600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>233700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45199</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45108</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45017</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44926</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44835</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44744</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44653</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44561</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44471</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44380</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44289</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44196</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44100</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44009</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43918</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43830</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43736</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43645</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43554</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43465</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43372</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43281</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43190</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43008</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42917</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42826</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42735</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3400,8 +3485,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3435,108 +3521,112 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>658500</v>
+      </c>
+      <c r="E41" s="3">
         <v>642600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>518500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>570900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>572900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>509600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>327000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>224000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>230600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>268900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>1128000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>753700</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>557300</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>768600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>781200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>737700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>263100</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>134800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>111300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>128100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>105700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>119100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>91400</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>518200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>114800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>84900</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84500</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>130200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>188400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>121700</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3">
-        <v>0</v>
+      <c r="D42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="E42" s="3">
         <v>0</v>
@@ -3545,40 +3635,40 @@
         <v>0</v>
       </c>
       <c r="G42" s="3">
+        <v>0</v>
+      </c>
+      <c r="H42" s="3">
         <v>150000</v>
       </c>
-      <c r="H42" s="3">
+      <c r="I42" s="3">
         <v>158000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>110000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>265000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>310000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>323000</v>
       </c>
-      <c r="M42" s="3">
-        <v>0</v>
-      </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>662400</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>782300</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>571700</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>407800</v>
-      </c>
-      <c r="R42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S42" s="3" t="s">
         <v>8</v>
@@ -3595,8 +3685,8 @@
       <c r="W42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X42" s="3">
-        <v>0</v>
+      <c r="X42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y42" s="3">
         <v>0</v>
@@ -3625,388 +3715,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2007200</v>
+      </c>
+      <c r="E43" s="3">
         <v>1874700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1943100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2087100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2052400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1904800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2003300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2105800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2044700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1840000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1880500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2017600</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1813900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1709500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1711000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1586400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1644800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1526600</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1787200</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1819500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1743600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1606200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1755700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2527700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2551900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2519700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2618700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2729900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2793800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2900100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2826000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2513200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2391700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2215600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2082000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>1996600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1913000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1842000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1922000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2195400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2282300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2338000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2367600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2338100</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2287600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2214300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>528300</v>
+      </c>
+      <c r="E45" s="3">
         <v>535200</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>523000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>574600</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>556000</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>528900</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>514000</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>519900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>466200</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>414800</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>421900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>434900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>416000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>400800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>410000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>499800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>509800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>485700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>491400</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>493100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>501600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>496500</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>487100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>456300</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>447300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>481300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>345500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>374900</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>307800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>297900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5721700</v>
+      </c>
+      <c r="E46" s="3">
         <v>5604200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5504300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5851300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>6061100</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5895100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5854300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5940700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5564700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5238400</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5646100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5950600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5566000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5363700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5152000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>4746000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4613000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4429500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4727800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4808300</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4689000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4509300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4548500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4100,198 +4205,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5298700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5421700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5193300</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5357600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5342000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5049000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>4924900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4986800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4937400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5026800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4827900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4842700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4769900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4914400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4708300</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4752600</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4804200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5021900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4934700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5058000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4995200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4699900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4586200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1994000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2035100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1979900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2919000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2915500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2785700</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2651100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>3392700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3462900</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3507900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3523500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3531900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3516600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3602400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3493400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3452700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3424000</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3498900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3436200</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3516300</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3499600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3482800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3466800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4385,8 +4499,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4480,103 +4597,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>517100</v>
+      </c>
+      <c r="E52" s="3">
         <v>498800</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>461000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>457200</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>444800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>390600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>370700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>369200</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>421700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>451400</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>452800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>467600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>437600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>447300</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>430500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>418100</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>415700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>436400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>294100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>423400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>421300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>407100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>399400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>393700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>389900</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>387900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>390900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>391200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>357500</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>279700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4670,103 +4793,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13531500</v>
+      </c>
+      <c r="E54" s="3">
         <v>13559900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13138500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>14585200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14763500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14120400</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13801000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14689500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14386700</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14224500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14450300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14792800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14290100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14327800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13784200</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13369400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13256900</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13386700</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13392800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13806100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13605100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13099100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13000900</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4800,8 +4929,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4835,578 +4965,597 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1101900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1038000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1082400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1184100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1211700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1094000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1217700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1359200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1296100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1228600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1147000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1131200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1064800</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1016900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>989900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>845300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>899200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>825000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>964100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>976200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>914200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>811900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>925200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>951200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>897500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>810000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>859900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>871400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>780500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>729400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>931500</v>
+      </c>
+      <c r="E58" s="3">
         <v>1001700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>922700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1038000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1056500</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>840600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1542100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1498900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1546500</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>624500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>588700</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>958800</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>953900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>377300</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>356100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>135400</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1210500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1051500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1273200</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1891500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1763300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1742400</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1333900</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1086700</v>
+      </c>
+      <c r="E59" s="3">
         <v>1106200</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1183500</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1065800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1050200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1135700</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1144900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1066300</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1029100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1093200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1166100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1088900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>988600</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>977100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1041100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>891600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>761600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>836100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>877400</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>838000</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>756700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>712000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>698200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>638400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>566500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>641600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>664300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>595200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>549900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>606200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>3120100</v>
+      </c>
+      <c r="E60" s="3">
         <v>3145900</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3188600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3287900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3318400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3070300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3904700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3924400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3871600</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>2946400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2901700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3178900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3007300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2371200</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2387100</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>1872200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2871300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2712600</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3114700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3705800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3434200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3266200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2957300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1694500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1701800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1675600</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2013300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2265100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1978600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1020000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1052100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1088400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1700300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1710200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1723300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1719100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>2356900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2282800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2573200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1514000</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1518400</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1483600</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1169500</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1498000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1515600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1528600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>1069100</v>
+      </c>
+      <c r="E62" s="3">
         <v>1083000</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1002900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1071900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1074200</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1053700</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1051200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1106100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1139100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1149700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1085900</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1116700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1064600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1058500</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>947300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>999200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1024000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1029300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1029200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1109200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1095800</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>877200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>912100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>870500</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>801900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>783100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>755000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>713100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>677900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>576300</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5500,8 +5649,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5595,8 +5747,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5690,103 +5845,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5889600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5936800</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5873000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>6379100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6664000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6108900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5982300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6088900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6105700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5803100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5704800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6025700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5797600</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5793400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5623600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5450600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5415600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5266800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5634000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5991000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>6034300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5665300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5437200</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5820,8 +5981,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5915,8 +6077,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6010,8 +6175,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6105,8 +6273,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6200,103 +6371,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7075200</v>
+      </c>
+      <c r="E72" s="3">
         <v>6970200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6830800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7591200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7490000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7409800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7376300</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7910700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7630800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7692100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7930000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7867800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7673100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7559200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7430900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7225800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7274100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7232300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>6991100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6903300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6709800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6588200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6635900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6390,8 +6567,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6485,8 +6665,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6580,103 +6763,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7641900</v>
+      </c>
+      <c r="E76" s="3">
         <v>7623100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7265500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8206100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8099500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8011500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7818800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8600600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8281000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8421400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8745500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8767100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8492400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8534300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8160700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>7918800</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7841400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8119800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7758800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7815100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7570800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7433800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7563800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6770,203 +6959,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45381</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45199</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45108</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45017</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44926</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44835</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44744</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44653</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44561</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44471</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44380</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44289</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44196</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44100</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44009</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43918</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43830</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43736</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43645</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43554</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43465</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43372</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43281</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43190</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43008</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42917</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42826</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42735</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>105000</v>
+      </c>
+      <c r="E81" s="3">
         <v>139500</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>-760500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>101200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>80200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>33500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-534000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>280400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>245300</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>189100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>271000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>336300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>236800</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>248200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>205100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>-48300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>110500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>264700</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>155500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>202400</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>121600</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>226400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>226300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>196600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>208500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>240400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>270000</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>260700</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>200600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>233700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7000,8 +7198,9 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
@@ -7009,94 +7208,97 @@
         <v>154200</v>
       </c>
       <c r="E83" s="3">
+        <v>154200</v>
+      </c>
+      <c r="F83" s="3">
         <v>149600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>156600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>169900</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>159000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>153500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>141600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>141400</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>143400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>148600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>148500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>151200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>156600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>151300</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>154100</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>145500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>153800</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>144900</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>140500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>137300</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>139100</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>133000</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>127000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>122700</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>118400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>113500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>109800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>105000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>104400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7190,8 +7392,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7285,8 +7490,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7380,8 +7588,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7475,8 +7686,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7570,103 +7784,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>183700</v>
+      </c>
+      <c r="E89" s="3">
         <v>296300</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>512000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>263600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>257300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>241700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>224800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>147700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>55000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>212400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>498700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>338400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>259600</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>407800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>598500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>568500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>195000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>440700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>411800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>396200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>170100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>286900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>273500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>437800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>183200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>319400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>460300</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>248000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>165900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>342900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7700,103 +7920,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-86800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-240400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-127400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-116700</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-128500</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-150700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-150000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-129500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-300900</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-147700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-112700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-114700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-160100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-69100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-80600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-115600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-139800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-124600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-144100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-136900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-151200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-144600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7890,8 +8114,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7985,103 +8212,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-240400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-127400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>37300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-639900</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-251000</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-153300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-105600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-115500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-670700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>442500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>4800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-333300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-324100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-420200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-77000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-133400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-141600</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-120600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-142100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-211800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-303900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-542500</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8115,8 +8348,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8210,8 +8444,11 @@
       <c r="AG96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8305,8 +8542,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8400,8 +8640,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8495,289 +8738,301 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-76100</v>
+      </c>
+      <c r="E100" s="3">
         <v>63100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-430000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-294700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>451000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>197300</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>39900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-51800</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>9000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-397300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-559200</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-155600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-120200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-119100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-132000</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-24200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>87200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-279600</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-304900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-232200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>26800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>46500</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-156500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>221400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>86600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>16300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>166400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>90900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>5100</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-3500</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-7700</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>8900</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-17500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>22800</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-2700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>7400</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-20400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>4000</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-3100</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>600</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>1500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1600</v>
       </c>
-      <c r="AB101" s="3">
-        <v>0</v>
-      </c>
       <c r="AC101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD101" s="3">
         <v>4100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1200</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>12100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>700</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>15900</v>
+      </c>
+      <c r="E102" s="3">
         <v>124100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-52500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>63200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>182700</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>103000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-6600</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-38300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-859100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>374400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>196400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-211400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>43500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>474600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>128300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>23500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-16800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>22400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-13400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>27700</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-426900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>403400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>30000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>66800</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>9600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="157" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,438 +656,451 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E7" s="2">
         <v>45381</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45199</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45108</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45017</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44926</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44835</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44744</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44653</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44561</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44471</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44380</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44289</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44196</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44100</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44009</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43918</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43830</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43736</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43645</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43554</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43465</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43372</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43281</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43190</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43008</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42917</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42826</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42735</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2801300</v>
+      </c>
+      <c r="E8" s="3">
         <v>2679400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2612300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2766200</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2950400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2806200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2650700</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2917500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>3153200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3015700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2760700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2817000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2953800</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2669000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2641800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2574900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2049800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2285800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2424500</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2519200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2584500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2442500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2448600</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2042300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2024400</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1967700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2031500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2188100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2133700</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2060300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2173500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2279300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2212600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2020900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>1979200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2046300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1867100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1880800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1851000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1629800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1657500</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1759300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1820000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1842000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1785000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1791900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>759000</v>
+      </c>
+      <c r="E10" s="3">
         <v>655000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>644600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>734700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>762300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>672500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>590400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>744000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>873900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>803100</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>739800</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>837900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>907500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>801900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>761000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>723900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>420000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>628300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>665200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>699200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>742500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>657500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>656700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>730600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>778600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>719200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AD10" s="3">
-        <v>792100</v>
       </c>
       <c r="AE10" s="3">
         <v>792100</v>
       </c>
       <c r="AF10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AG10" s="3">
         <v>683100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>703300</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1122,8 +1135,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1220,8 +1234,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1318,106 +1335,112 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E14" s="3">
         <v>7800</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>12400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>923200</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>41700</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>32100</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>43400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>730300</v>
-      </c>
-      <c r="K14" s="3">
-        <v>1900</v>
       </c>
       <c r="L14" s="3">
         <v>1900</v>
       </c>
       <c r="M14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="N14" s="3">
         <v>4600</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>1100</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>6800</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>11200</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>26100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26500</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>67200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>12700</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>41800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>74700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>8900</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>35700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>20600</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>19900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>16000</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>22100</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>15200</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>13900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>4000</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>16200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1484,8 +1507,8 @@
       <c r="X15" s="3">
         <v>0</v>
       </c>
-      <c r="Y15" s="3" t="s">
-        <v>8</v>
+      <c r="Y15" s="3">
+        <v>0</v>
       </c>
       <c r="Z15" s="3" t="s">
         <v>8</v>
@@ -1496,8 +1519,8 @@
       <c r="AB15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC15" s="3">
-        <v>0</v>
+      <c r="AC15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD15" s="3">
         <v>0</v>
@@ -1514,8 +1537,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1547,204 +1573,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2587300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2532800</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2445200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>3499900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2797400</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2680400</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2589600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>3423100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2785300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2694900</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2507600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2457000</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2549400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2351500</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2359000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2312100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2114400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2134300</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2264400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2344100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2317600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2277200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2235200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>214000</v>
+      </c>
+      <c r="E18" s="3">
         <v>146600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>167100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>-733700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>153000</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>125800</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>61100</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>-505600</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>367900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>320800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>253100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>360000</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>404400</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>317500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>282800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>262800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>-64600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>151500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>160100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>175100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>266900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>165300</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>213400</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>287200</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>326300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>268400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>343500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>380100</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>355800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>274700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>305300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1779,498 +1812,514 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-1600</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>8500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-2200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>600</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-10000</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2800</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-2500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-1100</v>
       </c>
-      <c r="N20" s="3">
-        <v>0</v>
-      </c>
       <c r="O20" s="3">
+        <v>0</v>
+      </c>
+      <c r="P20" s="3">
         <v>11200</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>2300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>6700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2600</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-5700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>4300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>12400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>3000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>2900</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>3200</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>383900</v>
+      </c>
+      <c r="E21" s="3">
         <v>301900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>325200</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>-575600</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>307500</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>296300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>210100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>-350900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>512300</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>459800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>395400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>508600</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>564100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>471000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>446000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>414800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>92100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>291300</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>318100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>332400</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>410400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>306400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>352000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>419500</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>451300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>387100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>458100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>492300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>462600</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>382600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>412800</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>12600</v>
+      </c>
+      <c r="E22" s="3">
         <v>14900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>17400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>20100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>22900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>14600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>13800</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>12100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>11500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12200</v>
-      </c>
-      <c r="N22" s="3">
-        <v>14900</v>
       </c>
       <c r="O22" s="3">
         <v>14900</v>
       </c>
       <c r="P22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="Q22" s="3">
         <v>15200</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>15900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>14900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>13000</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>8700</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>11000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>9300</v>
-      </c>
-      <c r="W22" s="3">
-        <v>10500</v>
       </c>
       <c r="X22" s="3">
         <v>10500</v>
       </c>
       <c r="Y22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="Z22" s="3">
         <v>14400</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>7900</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>7300</v>
       </c>
       <c r="AD22" s="3">
         <v>7300</v>
       </c>
       <c r="AE22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AF22" s="3">
         <v>8400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>8200</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8500</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>199800</v>
+      </c>
+      <c r="E23" s="3">
         <v>132800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>153600</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>-745300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>128000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>109200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>36500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-518100</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>358700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>306900</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>239800</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>345000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>400700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>304500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>273600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>248600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>-75000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>137100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>153400</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>178200</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>259400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>158600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>198500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>277500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>316400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>256900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>332500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>371600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>344400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>269400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>300000</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E24" s="3">
         <v>27800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>4200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>15000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>26800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>28900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>2900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15600</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>78200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>61400</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>50700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>73800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>64200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>67700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>25200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>43200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>-26400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>26700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-111300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>22500</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>56700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>37000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-59800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>49500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>118800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>47600</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>46300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>100500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>82700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>68400</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>65500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2367,204 +2416,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>157500</v>
+      </c>
+      <c r="E26" s="3">
         <v>105000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>149400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>-760300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>101200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>80300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>33600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-533700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>280500</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>245400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>189100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>271200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>336500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>236800</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>248400</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>205500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>-48600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>110500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>264700</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>155700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>202700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>121600</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>258200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>228000</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>197500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>209200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>286100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>271000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>261700</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>201100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>234500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E27" s="3">
         <v>105000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>149500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>-760500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>101200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>80200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>33500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-534000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>280400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>245300</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>189100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>271000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>336300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>236800</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>248200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>205100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>-48300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>110500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>264700</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>155500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>202400</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>121600</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>254600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>226300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>196600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>208500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>285600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>270000</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>260700</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>200600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>233700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2661,19 +2719,22 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
       <c r="D29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E29" s="3">
+      <c r="E29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F29" s="3">
         <v>-10000</v>
-      </c>
-      <c r="F29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="G29" s="3" t="s">
         <v>8</v>
@@ -2690,8 +2751,8 @@
       <c r="K29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L29" s="3">
-        <v>0</v>
+      <c r="L29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M29" s="3">
         <v>0</v>
@@ -2711,17 +2772,17 @@
       <c r="R29" s="3">
         <v>0</v>
       </c>
-      <c r="S29" s="3" t="s">
-        <v>8</v>
+      <c r="S29" s="3">
+        <v>0</v>
       </c>
       <c r="T29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U29" s="3">
-        <v>0</v>
-      </c>
-      <c r="V29" s="3" t="s">
+      <c r="U29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
@@ -2729,11 +2790,11 @@
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
+      <c r="Y29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Z29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2741,11 +2802,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2759,8 +2820,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2857,8 +2921,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2955,204 +3022,213 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>1600</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-8500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>2200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-600</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>10000</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2800</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>2500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>1100</v>
       </c>
-      <c r="N32" s="3">
-        <v>0</v>
-      </c>
       <c r="O32" s="3">
+        <v>0</v>
+      </c>
+      <c r="P32" s="3">
         <v>-11200</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-2300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-6700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2600</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>5700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-4300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-12400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-3000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>2100</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>4000</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>3800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>1300</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E33" s="3">
         <v>105000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>139500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>-760500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>101200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>80200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>33500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-534000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>280400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>245300</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>189100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>271000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>336300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>236800</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>248200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>205100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>-48300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>110500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>264700</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>155500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>202400</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>121600</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>226400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>226300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>196600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>208500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>240400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>270000</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>260700</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>200600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>233700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3249,209 +3325,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E35" s="3">
         <v>105000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>139500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>-760500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>101200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>80200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>33500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-534000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>280400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>245300</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>189100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>271000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>336300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>236800</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>248200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>205100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>-48300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>110500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>264700</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>155500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>202400</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>121600</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>226400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>226300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>196600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>208500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>240400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>270000</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>260700</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>200600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>233700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E38" s="2">
         <v>45381</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45199</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45108</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45017</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44926</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44835</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44744</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44653</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44561</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44471</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44380</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44289</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44196</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44100</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44009</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43918</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43830</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43736</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43645</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43554</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43465</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43372</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43281</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43190</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43008</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42917</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42826</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42735</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3486,8 +3571,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3522,114 +3608,118 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>497400</v>
+      </c>
+      <c r="E41" s="3">
         <v>658500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>642600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>518500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>570900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>572900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>509600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>327000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>224000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>230600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>268900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>1128000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>753700</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>557300</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>768600</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>781200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>737700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>263100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>134800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>111300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>128100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>105700</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>119100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>91400</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>518200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>114800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>84900</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>84500</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>130200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>188400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>121700</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
       <c r="D42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="E42" s="3">
-        <v>0</v>
+      <c r="E42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3638,40 +3728,40 @@
         <v>0</v>
       </c>
       <c r="H42" s="3">
+        <v>0</v>
+      </c>
+      <c r="I42" s="3">
         <v>150000</v>
       </c>
-      <c r="I42" s="3">
+      <c r="J42" s="3">
         <v>158000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>110000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>265000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>310000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>323000</v>
       </c>
-      <c r="N42" s="3">
-        <v>0</v>
-      </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>662400</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>782300</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>571700</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>407800</v>
-      </c>
-      <c r="S42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T42" s="3" t="s">
         <v>8</v>
@@ -3688,8 +3778,8 @@
       <c r="X42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y42" s="3">
-        <v>0</v>
+      <c r="Y42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z42" s="3">
         <v>0</v>
@@ -3718,400 +3808,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2018500</v>
+      </c>
+      <c r="E43" s="3">
         <v>2007200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1874700</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1943100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2087100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2052400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1904800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2003300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2105800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2044700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1840000</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1880500</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2017600</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1813900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1709500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1711000</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1586400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1644800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1526600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1787200</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1819500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1743600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1606200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2579900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2527700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2551900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2519700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2618700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2729900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2793800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2900100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2826000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2513200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2391700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2215600</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2082000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>1996600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1913000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1842000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1922000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2195400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2282300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2338000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2367600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2338100</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2287600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>545500</v>
+      </c>
+      <c r="E45" s="3">
         <v>528300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>535200</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>523000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>574600</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>556000</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>528900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>514000</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>519900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>466200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>414800</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>421900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>434900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>416000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>400800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>410000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>499800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>509800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>485700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>491400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>493100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>501600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>496500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>487100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>456300</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>447300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>481300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>345500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>374900</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>307800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>297900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5641300</v>
+      </c>
+      <c r="E46" s="3">
         <v>5721700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5604200</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5504300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5851300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>6061100</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5895100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5854300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5940700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5564700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5238400</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5646100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5950600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5566000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5363700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5152000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>4746000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4613000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4429500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4727800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4808300</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4689000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4509300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4208,204 +4313,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5155400</v>
+      </c>
+      <c r="E48" s="3">
         <v>5298700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5421700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5193300</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5357600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5342000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5049000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>4924900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4986800</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4937400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5026800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4827900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4842700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4769900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4914400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4708300</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4752600</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4804200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>5021900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4934700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5058000</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4995200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4699900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1978100</v>
+      </c>
+      <c r="E49" s="3">
         <v>1994000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2035100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1979900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>2919000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2915500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2785700</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2651100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>3392700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3462900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3507900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3523500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3531900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3516600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3602400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3493400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3452700</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3424000</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3498900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3436200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3516300</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3499600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3482800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4502,8 +4616,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4600,106 +4717,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>504800</v>
+      </c>
+      <c r="E52" s="3">
         <v>517100</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>498800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>461000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>457200</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>444800</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>390600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>370700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>369200</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>421700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>451400</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>452800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>467600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>437600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>447300</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>430500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>418100</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>415700</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>436400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>294100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>423400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>421300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>407100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>399400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>393700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>389900</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>387900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>390900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>391200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>357500</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>279700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4796,106 +4919,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13279600</v>
+      </c>
+      <c r="E54" s="3">
         <v>13531500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13559900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13138500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>14585200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14763500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14120400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13801000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14689500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14386700</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14224500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14450300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14792800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14290100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14327800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>13784200</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13369400</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13256900</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13386700</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13392800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13806100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13605100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13099100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4930,8 +5059,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4966,596 +5096,615 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1082800</v>
+      </c>
+      <c r="E57" s="3">
         <v>1101900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1038000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1082400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1184100</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1211700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1094000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1217700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1359200</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1296100</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1228600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1147000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1131200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1064800</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1016900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>989900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>845300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>899200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>825000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>964100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>976200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>914200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>811900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>925200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>951200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>897500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>810000</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>859900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>871400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>780500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>729400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>718000</v>
+      </c>
+      <c r="E58" s="3">
         <v>931500</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>1001700</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>922700</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1038000</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1056500</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>840600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1542100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1498900</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1546500</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>624500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>588700</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>958800</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>953900</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>377300</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>356100</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>135400</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>1210500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1051500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1273200</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1891500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1763300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1742400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>1136900</v>
+      </c>
+      <c r="E59" s="3">
         <v>1086700</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>1106200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>1183500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>1065800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>1050200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>1135700</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>1144900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1066300</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1029100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1093200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1166100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1088900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>988600</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>977100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1041100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>891600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>761600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>836100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>877400</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>838000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>756700</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>712000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>698200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>638400</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>566500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>641600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>664300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>595200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>549900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>606200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2937700</v>
+      </c>
+      <c r="E60" s="3">
         <v>3120100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3145900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3188600</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3287900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3318400</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3070300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3904700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3924400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3871600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>2946400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2901700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3178900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3007300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2371200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2387100</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>1872200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2871300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2712600</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3114700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3705800</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3434200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3266200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1691500</v>
+      </c>
+      <c r="E61" s="3">
         <v>1694500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1701800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1675600</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2013300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2265100</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1978600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1020000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1052100</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1088400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1700300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1710200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1723300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1719100</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>2356900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2282800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2573200</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1514000</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1518400</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1483600</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1169500</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1498000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1515600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>997900</v>
+      </c>
+      <c r="E62" s="3">
         <v>1069100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>1083000</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>1002900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>1071900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>1074200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>1053700</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>1051200</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1106100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1139100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1149700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1085900</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1116700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1064600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1058500</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>947300</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>999200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1024000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1029300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1029200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1109200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1095800</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>877200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>912100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>870500</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>801900</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>783100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>755000</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>713100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>677900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>576300</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5652,8 +5801,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5750,8 +5902,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5848,106 +6003,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5633100</v>
+      </c>
+      <c r="E66" s="3">
         <v>5889600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5936800</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5873000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>6379100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>6664000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6108900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5982300</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6088900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6105700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5803100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5704800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6025700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5797600</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5793400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5623600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5450600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5415600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5266800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5634000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5991000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>6034300</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5665300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5982,8 +6143,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6080,8 +6242,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6178,8 +6343,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6276,8 +6444,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6374,106 +6545,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7144800</v>
+      </c>
+      <c r="E72" s="3">
         <v>7075200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>6970200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6830800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7591200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7490000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7409800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7376300</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7910700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7630800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7692100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7930000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7867800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7673100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7559200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7430900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7225800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7274100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7232300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>6991100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6903300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6709800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6588200</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6570,8 +6747,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6668,8 +6848,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6766,106 +6949,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7646500</v>
+      </c>
+      <c r="E76" s="3">
         <v>7641900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7623100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7265500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>8206100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8099500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8011500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7818800</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8600600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8281000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8421400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8745500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8767100</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8492400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8534300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8160700</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>7918800</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7841400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8119800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7758800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7815100</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7570800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7433800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6962,209 +7151,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45472</v>
+      </c>
+      <c r="E80" s="2">
         <v>45381</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45199</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45108</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45017</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44926</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44835</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44744</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44653</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44561</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44471</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44380</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44289</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44196</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44100</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44009</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43918</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43830</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43736</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43645</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43554</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43465</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43372</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43281</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43190</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43008</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42917</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42826</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42735</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>157400</v>
+      </c>
+      <c r="E81" s="3">
         <v>105000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>139500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>-760500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>101200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>80200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>33500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-534000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>280400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>245300</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>189100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>271000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>336300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>236800</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>248200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>205100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>-48300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>110500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>264700</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>155500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>202400</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>121600</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>226400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>226300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>196600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>208500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>240400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>270000</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>260700</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>200600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>233700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7199,106 +7397,110 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>154200</v>
+        <v>171500</v>
       </c>
       <c r="E83" s="3">
         <v>154200</v>
       </c>
       <c r="F83" s="3">
+        <v>154200</v>
+      </c>
+      <c r="G83" s="3">
         <v>149600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>156600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>169900</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>159000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>153500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>141600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>141400</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>143400</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>148600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>148500</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>151200</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>156600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>151300</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>154100</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>145500</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>153800</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>144900</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>140500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>137300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>139100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>133000</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>127000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>122700</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>118400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>113500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>109800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>105000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>104400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7395,8 +7597,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7493,8 +7698,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7591,8 +7799,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7689,8 +7900,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7787,106 +8001,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>233600</v>
+      </c>
+      <c r="E89" s="3">
         <v>183700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>296300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>512000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>263600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>257300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>241700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>224800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>147700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>55000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>212400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>498700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>338400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>259600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>407800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>598500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>568500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>195000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>440700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>411800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>396200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>170100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>286900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>273500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>437800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>183200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>319400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>460300</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>248000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>165900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>342900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7921,106 +8141,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-91400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-86800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-240400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-127400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-116700</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-128500</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-150700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-129500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-300900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-147700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-112700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-114700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-160100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-69100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-80600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-115600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-139800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-124600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-144100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-136900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-151200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8117,8 +8341,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8215,106 +8442,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-91400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-240400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-127400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>37300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-639900</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-251000</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-153300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-105600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-115500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-670700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>442500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>4800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-333300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-324100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-420200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-77000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-133400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-141600</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-120600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-142100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-211800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-303900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8349,8 +8582,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8447,8 +8681,11 @@
       <c r="AH96" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8545,8 +8782,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8643,8 +8883,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8741,298 +8984,310 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-305400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-76100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>63100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-430000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-294700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>451000</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>197300</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>39900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-51800</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>9000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-397300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-559200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-155600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-120200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-119100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-132000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-24200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>87200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-279600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-304900</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-232200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>26800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>46500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>221400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>86600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>16300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>166400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>90900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>5100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-7100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>13300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-3500</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-7700</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>8900</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-17500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>22800</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-2700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>7400</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-20400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>4000</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-3100</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>600</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>1500</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1600</v>
       </c>
-      <c r="AC101" s="3">
-        <v>0</v>
-      </c>
       <c r="AD101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE101" s="3">
         <v>4100</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1200</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>12100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>700</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-161100</v>
+      </c>
+      <c r="E102" s="3">
         <v>15900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>124100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-52500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-1900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>63200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>182700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>103000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-6600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-38300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-859100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>374400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>196400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-211400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-12600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>43500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>474600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>128300</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>23500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-16800</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>22400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-13400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>27700</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>403400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>30000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>66800</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>9600</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="160" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,451 +656,464 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E7" s="2">
         <v>45472</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45381</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45199</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45108</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45017</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44926</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44835</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44744</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44653</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44561</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44471</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44380</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44289</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44196</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44100</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44009</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43918</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43830</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43736</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43645</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43554</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43465</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43372</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43281</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43190</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43008</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42917</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42826</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42735</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2719000</v>
+      </c>
+      <c r="E8" s="3">
         <v>2801300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2679400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2612300</v>
       </c>
-      <c r="G8" s="3">
-        <v>2766200</v>
-      </c>
       <c r="H8" s="3">
-        <v>2950400</v>
+        <v>2766100</v>
       </c>
       <c r="I8" s="3">
+        <v>2950500</v>
+      </c>
+      <c r="J8" s="3">
         <v>2806200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2650700</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2917500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>3153200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3015700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2760700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2817000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2953800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2669000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2641800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2574900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2049800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2285800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2424500</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2519200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2584500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2442500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2010000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2042300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2024400</v>
       </c>
-      <c r="F9" s="3">
-        <v>1967700</v>
-      </c>
       <c r="G9" s="3">
-        <v>2031500</v>
+        <v>1963200</v>
       </c>
       <c r="H9" s="3">
+        <v>2031400</v>
+      </c>
+      <c r="I9" s="3">
         <v>2188100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2133700</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2060300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2173500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2279300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2212600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2020900</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>1979200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2046300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1867100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1880800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1851000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1629800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1657500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1759300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1820000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1842000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1785000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>709000</v>
+      </c>
+      <c r="E10" s="3">
         <v>759000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>655000</v>
       </c>
-      <c r="F10" s="3">
-        <v>644600</v>
-      </c>
       <c r="G10" s="3">
+        <v>649000</v>
+      </c>
+      <c r="H10" s="3">
         <v>734700</v>
       </c>
-      <c r="H10" s="3">
-        <v>762300</v>
-      </c>
       <c r="I10" s="3">
+        <v>762400</v>
+      </c>
+      <c r="J10" s="3">
         <v>672500</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>590400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>744000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>873900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>803100</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>739800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>837900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>907500</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>801900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>761000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>723900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>420000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>628300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>665200</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>699200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>742500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>657500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>656700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>730600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>778600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>719200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AE10" s="3">
-        <v>792100</v>
       </c>
       <c r="AF10" s="3">
         <v>792100</v>
       </c>
       <c r="AG10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AH10" s="3">
         <v>683100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>703300</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1136,8 +1149,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1237,8 +1251,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1338,132 +1355,138 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
-        <v>41300</v>
+        <v>19500</v>
       </c>
       <c r="E14" s="3">
-        <v>7800</v>
+        <v>41400</v>
       </c>
       <c r="F14" s="3">
-        <v>12400</v>
+        <v>7900</v>
       </c>
       <c r="G14" s="3">
+        <v>104700</v>
+      </c>
+      <c r="H14" s="3">
         <v>923200</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>41700</v>
       </c>
-      <c r="I14" s="3">
-        <v>32100</v>
-      </c>
       <c r="J14" s="3">
+        <v>32200</v>
+      </c>
+      <c r="K14" s="3">
         <v>43400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>730300</v>
-      </c>
-      <c r="L14" s="3">
-        <v>1900</v>
       </c>
       <c r="M14" s="3">
         <v>1900</v>
       </c>
       <c r="N14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="O14" s="3">
         <v>4600</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>1100</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>6800</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>11200</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>26100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>26500</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>67200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>12700</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>41800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>74700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>8900</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>35700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>20600</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>19900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>16000</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>22100</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>15200</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>13900</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>4000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>16200</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>156200</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>171500</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>154200</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>154200</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>149600</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>156600</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>169900</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1510,8 +1533,8 @@
       <c r="Y15" s="3">
         <v>0</v>
       </c>
-      <c r="Z15" s="3" t="s">
-        <v>8</v>
+      <c r="Z15" s="3">
+        <v>0</v>
       </c>
       <c r="AA15" s="3" t="s">
         <v>8</v>
@@ -1522,8 +1545,8 @@
       <c r="AC15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD15" s="3">
-        <v>0</v>
+      <c r="AD15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AE15" s="3">
         <v>0</v>
@@ -1540,8 +1563,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1574,210 +1600,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
-        <v>2587300</v>
+        <v>2487200</v>
       </c>
       <c r="E17" s="3">
-        <v>2532800</v>
+        <v>2545900</v>
       </c>
       <c r="F17" s="3">
-        <v>2445200</v>
+        <v>2524900</v>
       </c>
       <c r="G17" s="3">
-        <v>3499900</v>
+        <v>2340500</v>
       </c>
       <c r="H17" s="3">
-        <v>2797400</v>
+        <v>2576600</v>
       </c>
       <c r="I17" s="3">
-        <v>2680400</v>
+        <v>2755700</v>
       </c>
       <c r="J17" s="3">
+        <v>2648300</v>
+      </c>
+      <c r="K17" s="3">
         <v>2589600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>3423100</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2785300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2694900</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2507600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2457000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2549400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2351500</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2359000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2312100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2114400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2134300</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2264400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2344100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2317600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2277200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
-        <v>214000</v>
+        <v>231800</v>
       </c>
       <c r="E18" s="3">
-        <v>146600</v>
+        <v>255400</v>
       </c>
       <c r="F18" s="3">
-        <v>167100</v>
+        <v>154500</v>
       </c>
       <c r="G18" s="3">
-        <v>-733700</v>
+        <v>271800</v>
       </c>
       <c r="H18" s="3">
-        <v>153000</v>
+        <v>189500</v>
       </c>
       <c r="I18" s="3">
-        <v>125800</v>
+        <v>194800</v>
       </c>
       <c r="J18" s="3">
+        <v>157900</v>
+      </c>
+      <c r="K18" s="3">
         <v>61100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>-505600</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>367900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>320800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>253100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>360000</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>404400</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>317500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>282800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>262800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>-64600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>151500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>160100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>175100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>266900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>165300</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>213400</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>287200</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>326300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>268400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>343500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>380100</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>355800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>274700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>305300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1813,513 +1846,529 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
-        <v>-1600</v>
+        <v>-700</v>
       </c>
       <c r="E20" s="3">
-        <v>1100</v>
+        <v>1600</v>
       </c>
       <c r="F20" s="3">
-        <v>3900</v>
+        <v>-1100</v>
       </c>
       <c r="G20" s="3">
-        <v>8500</v>
+        <v>-3900</v>
       </c>
       <c r="H20" s="3">
-        <v>-2200</v>
+        <v>-8500</v>
       </c>
       <c r="I20" s="3">
-        <v>600</v>
+        <v>2200</v>
       </c>
       <c r="J20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="K20" s="3">
         <v>-10000</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>1300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>2800</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-2500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-1100</v>
       </c>
-      <c r="O20" s="3">
-        <v>0</v>
-      </c>
       <c r="P20" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q20" s="3">
         <v>11200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>6700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2600</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-5700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>4300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>12400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>3000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>2900</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>3200</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
-        <v>383900</v>
+        <v>388700</v>
       </c>
       <c r="E21" s="3">
-        <v>301900</v>
+        <v>425300</v>
       </c>
       <c r="F21" s="3">
-        <v>325200</v>
+        <v>309800</v>
       </c>
       <c r="G21" s="3">
-        <v>-575600</v>
+        <v>429900</v>
       </c>
       <c r="H21" s="3">
-        <v>307500</v>
+        <v>347600</v>
       </c>
       <c r="I21" s="3">
-        <v>296300</v>
+        <v>349200</v>
       </c>
       <c r="J21" s="3">
+        <v>328400</v>
+      </c>
+      <c r="K21" s="3">
         <v>210100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>-350900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>512300</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>459800</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>395400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>508600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>564100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>471000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>446000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>414800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>92100</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>291300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>318100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>332400</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>410400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>306400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>352000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>419500</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>451300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>387100</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>458100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>492300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>462600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>382600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>412800</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>11200</v>
+      </c>
+      <c r="E22" s="3">
         <v>12600</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>14900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>17400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>20100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>22900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>13800</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>12100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>11500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12200</v>
-      </c>
-      <c r="O22" s="3">
-        <v>14900</v>
       </c>
       <c r="P22" s="3">
         <v>14900</v>
       </c>
       <c r="Q22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="R22" s="3">
         <v>15200</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>15900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>14900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>13000</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>8700</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>11000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>9300</v>
-      </c>
-      <c r="X22" s="3">
-        <v>10500</v>
       </c>
       <c r="Y22" s="3">
         <v>10500</v>
       </c>
       <c r="Z22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AA22" s="3">
         <v>14400</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>9000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>7900</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>7300</v>
       </c>
       <c r="AE22" s="3">
         <v>7300</v>
       </c>
       <c r="AF22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AG22" s="3">
         <v>8400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>8200</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8500</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>201800</v>
+      </c>
+      <c r="E23" s="3">
         <v>199800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>132800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>153600</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>-745300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>128000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>109200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>36500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>-518100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>358700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>306900</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>239800</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>345000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>400700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>304500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>273600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>248600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>-75000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>137100</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>153400</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>178200</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>259400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>158600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>198500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>277500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>316400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>256900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>332500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>371600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>344400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>269400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>300000</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E24" s="3">
         <v>42300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>27800</v>
       </c>
-      <c r="F24" s="3">
-        <v>4200</v>
-      </c>
       <c r="G24" s="3">
+        <v>14200</v>
+      </c>
+      <c r="H24" s="3">
         <v>15000</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>26800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>28900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>2900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>15600</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>78200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>61400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>50700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>73800</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>64200</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>67700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>25200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>43200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>-26400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>26700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-111300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>22500</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>56700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>37000</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>49500</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>118800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>47600</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>46300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>100500</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>82700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>68400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>65500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2419,210 +2468,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E26" s="3">
         <v>157500</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>105000</v>
       </c>
-      <c r="F26" s="3">
-        <v>149400</v>
-      </c>
       <c r="G26" s="3">
+        <v>139400</v>
+      </c>
+      <c r="H26" s="3">
         <v>-760300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>101200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>80300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>33600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>-533700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>280500</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>245400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>189100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>271200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>336500</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>236800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>248400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>205500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>-48600</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>110500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>264700</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>155700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>202700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>121600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>258200</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>228000</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>197500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>209200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>286100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>271000</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>261700</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>201100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>234500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E27" s="3">
         <v>157400</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>105000</v>
       </c>
-      <c r="F27" s="3">
-        <v>149500</v>
-      </c>
       <c r="G27" s="3">
-        <v>-760500</v>
+        <v>139500</v>
       </c>
       <c r="H27" s="3">
+        <v>-760400</v>
+      </c>
+      <c r="I27" s="3">
         <v>101200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>80200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>33500</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>-534000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>280400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>245300</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>189100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>271000</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>336300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>236800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>248200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>205100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>-48300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>110500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>264700</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>155500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>202400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>121600</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>254600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>226300</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>196600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>208500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>285600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>270000</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>260700</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>200600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>233700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2722,31 +2780,34 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
-      <c r="D29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E29" s="3" t="s">
-        <v>8</v>
+      <c r="D29" s="3">
+        <v>0</v>
+      </c>
+      <c r="E29" s="3">
+        <v>0</v>
       </c>
       <c r="F29" s="3">
-        <v>-10000</v>
-      </c>
-      <c r="G29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="H29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="I29" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="J29" s="3" t="s">
-        <v>8</v>
+        <v>0</v>
+      </c>
+      <c r="G29" s="3">
+        <v>0</v>
+      </c>
+      <c r="H29" s="3">
+        <v>0</v>
+      </c>
+      <c r="I29" s="3">
+        <v>0</v>
+      </c>
+      <c r="J29" s="3">
+        <v>0</v>
       </c>
       <c r="K29" s="3" t="s">
         <v>8</v>
@@ -2754,8 +2815,8 @@
       <c r="L29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M29" s="3">
-        <v>0</v>
+      <c r="M29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N29" s="3">
         <v>0</v>
@@ -2775,17 +2836,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2793,11 +2854,11 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AA29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2805,11 +2866,11 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2823,8 +2884,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2924,8 +2988,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3025,210 +3092,219 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
-        <v>1600</v>
+        <v>700</v>
       </c>
       <c r="E32" s="3">
-        <v>-1100</v>
+        <v>-1600</v>
       </c>
       <c r="F32" s="3">
-        <v>-3900</v>
+        <v>1100</v>
       </c>
       <c r="G32" s="3">
-        <v>-8500</v>
+        <v>3900</v>
       </c>
       <c r="H32" s="3">
-        <v>2200</v>
+        <v>8500</v>
       </c>
       <c r="I32" s="3">
-        <v>-600</v>
+        <v>-2200</v>
       </c>
       <c r="J32" s="3">
+        <v>600</v>
+      </c>
+      <c r="K32" s="3">
         <v>10000</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-1300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-2800</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>2500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>1100</v>
       </c>
-      <c r="O32" s="3">
-        <v>0</v>
-      </c>
       <c r="P32" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q32" s="3">
         <v>-11200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-6700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2600</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>5700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-4300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-12400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>2100</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>4000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>3800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1300</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E33" s="3">
         <v>157400</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>105000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>139500</v>
       </c>
-      <c r="G33" s="3">
-        <v>-760500</v>
-      </c>
       <c r="H33" s="3">
+        <v>-760400</v>
+      </c>
+      <c r="I33" s="3">
         <v>101200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>80200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>33500</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>-534000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>280400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>245300</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>189100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>271000</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>336300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>236800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>248200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>205100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>-48300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>110500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>264700</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>155500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>202400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>121600</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>226400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226300</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>196600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>208500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>240400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>270000</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>260700</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>200600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>233700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3328,215 +3404,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E35" s="3">
         <v>157400</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>105000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>139500</v>
       </c>
-      <c r="G35" s="3">
-        <v>-760500</v>
-      </c>
       <c r="H35" s="3">
+        <v>-760400</v>
+      </c>
+      <c r="I35" s="3">
         <v>101200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>80200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>33500</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>-534000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>280400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>245300</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>189100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>271000</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>336300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>236800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>248200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>205100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>-48300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>110500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>264700</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>155500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>202400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>121600</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>226400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226300</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>196600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>208500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>240400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>270000</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>260700</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>200600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>233700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E38" s="2">
         <v>45472</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45381</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45199</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45108</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45017</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44926</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44835</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44744</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44653</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44561</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44471</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44380</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44289</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44196</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44100</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44009</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43918</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43830</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43736</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43645</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43554</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43465</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43372</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43281</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43190</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43008</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42917</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42826</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42735</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3572,8 +3657,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3609,117 +3695,121 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>424000</v>
+      </c>
+      <c r="E41" s="3">
         <v>497400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>658500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>642600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>518500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>570900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>572900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>509600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>327000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>224000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>230600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>268900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>1128000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>753700</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>557300</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>768600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>781200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>737700</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>263100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>134800</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>111300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>128100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>105700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>119100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>91400</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>518200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>114800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>84900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>84500</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>130200</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>188400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>121700</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E42" s="3" t="s">
-        <v>8</v>
+      <c r="D42" s="3">
+        <v>0</v>
+      </c>
+      <c r="E42" s="3">
+        <v>0</v>
       </c>
       <c r="F42" s="3">
         <v>0</v>
@@ -3731,40 +3821,40 @@
         <v>0</v>
       </c>
       <c r="I42" s="3">
+        <v>0</v>
+      </c>
+      <c r="J42" s="3">
         <v>150000</v>
       </c>
-      <c r="J42" s="3">
+      <c r="K42" s="3">
         <v>158000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>110000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>265000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>310000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>323000</v>
       </c>
-      <c r="O42" s="3">
-        <v>0</v>
-      </c>
       <c r="P42" s="3">
+        <v>0</v>
+      </c>
+      <c r="Q42" s="3">
         <v>662400</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>782300</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>571700</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>407800</v>
-      </c>
-      <c r="T42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U42" s="3" t="s">
         <v>8</v>
@@ -3781,8 +3871,8 @@
       <c r="Y42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z42" s="3">
-        <v>0</v>
+      <c r="Z42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA42" s="3">
         <v>0</v>
@@ -3811,435 +3901,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2043400</v>
+      </c>
+      <c r="E43" s="3">
         <v>2018500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2007200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>1874700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1943100</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2087100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2052400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1904800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2003300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2105800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2044700</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>1840000</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1880500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2017600</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1813900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1709500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1711000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1586400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1644800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1526600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1787200</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1819500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1743600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2612100</v>
+      </c>
+      <c r="E44" s="3">
         <v>2579900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2527700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2551900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2519700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2618700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2729900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2793800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2900100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2826000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2513200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2391700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2215600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2082000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>1996600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1913000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1842000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1922000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2195400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2282300</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2338000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2367600</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2338100</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
-        <v>545500</v>
+        <v>20800</v>
       </c>
       <c r="E45" s="3">
-        <v>528300</v>
+        <v>16800</v>
       </c>
       <c r="F45" s="3">
-        <v>535200</v>
+        <v>15800</v>
       </c>
       <c r="G45" s="3">
-        <v>523000</v>
+        <v>19300</v>
       </c>
       <c r="H45" s="3">
-        <v>574600</v>
+        <v>22400</v>
       </c>
       <c r="I45" s="3">
-        <v>556000</v>
+        <v>22500</v>
       </c>
       <c r="J45" s="3">
+        <v>21900</v>
+      </c>
+      <c r="K45" s="3">
         <v>528900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>514000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>519900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>466200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>414800</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>421900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>434900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>416000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>400800</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>410000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>499800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>509800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>485700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>491400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>493100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>501600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>496500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>487100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>456300</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>447300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>481300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>345500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>374900</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>307800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>297900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5621400</v>
+      </c>
+      <c r="E46" s="3">
         <v>5641300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5721700</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5604200</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5504300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5851300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>6061100</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5895100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5854300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5940700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5564700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5238400</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5646100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5950600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5566000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5363700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5152000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>4746000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4613000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4429500</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4727800</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4808300</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4689000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
-        <v>0</v>
-      </c>
-      <c r="E47" s="3">
-        <v>0</v>
-      </c>
-      <c r="F47" s="3">
-        <v>0</v>
-      </c>
-      <c r="G47" s="3">
-        <v>0</v>
-      </c>
-      <c r="H47" s="3">
-        <v>0</v>
-      </c>
-      <c r="I47" s="3">
-        <v>0</v>
-      </c>
-      <c r="J47" s="3">
-        <v>0</v>
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4316,210 +4421,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5142900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5155400</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5298700</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5421700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5193300</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5357600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5342000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5049000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>4924900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4986800</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4937400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5026800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4827900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4842700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4769900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4914400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4708300</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4752600</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4804200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>5021900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4934700</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5058000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4995200</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2019300</v>
+      </c>
+      <c r="E49" s="3">
         <v>1978100</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1994000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2035100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1979900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2919000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2915500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2785700</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2651100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>3392700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3462900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3507900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3523500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3531900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3516600</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3602400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3493400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3452700</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3424000</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3498900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3436200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3516300</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3499600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4619,8 +4733,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4720,109 +4837,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
-      <c r="D52" s="3">
-        <v>504800</v>
-      </c>
-      <c r="E52" s="3">
-        <v>517100</v>
-      </c>
-      <c r="F52" s="3">
-        <v>498800</v>
-      </c>
-      <c r="G52" s="3">
-        <v>461000</v>
-      </c>
-      <c r="H52" s="3">
-        <v>457200</v>
-      </c>
-      <c r="I52" s="3">
-        <v>444800</v>
-      </c>
-      <c r="J52" s="3">
+      <c r="D52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K52" s="3">
         <v>390600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>370700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>369200</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>421700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>451400</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>452800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>467600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>437600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>447300</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>430500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>418100</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>415700</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>436400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>294100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>423400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>421300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>407100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>399400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>393700</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>389900</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>387900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>390900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>391200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>357500</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>279700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4922,109 +5045,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13313200</v>
+      </c>
+      <c r="E54" s="3">
         <v>13279600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13531500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13559900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13138500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>14585200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14763500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14120400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13801000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14689500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14386700</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14224500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14450300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14792800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14290100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14327800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>13784200</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13369400</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13256900</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13386700</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13392800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13806100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13605100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5060,8 +5189,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5097,614 +5227,633 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1061200</v>
+      </c>
+      <c r="E57" s="3">
         <v>1082800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1101900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1038000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1082400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1184100</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1211700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1094000</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1217700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1359200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1296100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1228600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1147000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1131200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1064800</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1016900</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>989900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>845300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>899200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>825000</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>964100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>976200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>914200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>811900</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>925200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>951200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>897500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>810000</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>859900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>871400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>780500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>729400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>718000</v>
+        <v>576900</v>
       </c>
       <c r="E58" s="3">
-        <v>931500</v>
+        <v>827900</v>
       </c>
       <c r="F58" s="3">
-        <v>1001700</v>
+        <v>1040800</v>
       </c>
       <c r="G58" s="3">
-        <v>922700</v>
+        <v>1110600</v>
       </c>
       <c r="H58" s="3">
-        <v>1038000</v>
+        <v>1029100</v>
       </c>
       <c r="I58" s="3">
-        <v>1056500</v>
+        <v>1144100</v>
       </c>
       <c r="J58" s="3">
+        <v>1163000</v>
+      </c>
+      <c r="K58" s="3">
         <v>840600</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1542100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1498900</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1546500</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>624500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>588700</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>958800</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>953900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>377300</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>356100</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>135400</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>1210500</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1051500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1273200</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1891500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1763300</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>1136900</v>
+        <v>35100</v>
       </c>
       <c r="E59" s="3">
-        <v>1086700</v>
+        <v>34400</v>
       </c>
       <c r="F59" s="3">
-        <v>1106200</v>
+        <v>34500</v>
       </c>
       <c r="G59" s="3">
-        <v>1183500</v>
+        <v>39800</v>
       </c>
       <c r="H59" s="3">
-        <v>1065800</v>
+        <v>39200</v>
       </c>
       <c r="I59" s="3">
-        <v>1050200</v>
+        <v>47100</v>
       </c>
       <c r="J59" s="3">
+        <v>41200</v>
+      </c>
+      <c r="K59" s="3">
         <v>1135700</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1144900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1066300</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1029100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1093200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1166100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1088900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>988600</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>977100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1041100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>891600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>761600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>836100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>877400</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>838000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>756700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>712000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>698200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>638400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>566500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>641600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>664300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>595200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>549900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>606200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2771000</v>
+      </c>
+      <c r="E60" s="3">
         <v>2937700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>3120100</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3145900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3188600</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3287900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3318400</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3070300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3904700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3924400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3871600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>2946400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2901700</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3178900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3007300</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2371200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2387100</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>1872200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2871300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2712600</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3114700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3705800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3434200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>1691500</v>
+        <v>2014400</v>
       </c>
       <c r="E61" s="3">
-        <v>1694500</v>
+        <v>1993100</v>
       </c>
       <c r="F61" s="3">
-        <v>1701800</v>
+        <v>2016300</v>
       </c>
       <c r="G61" s="3">
-        <v>1675600</v>
+        <v>2039300</v>
       </c>
       <c r="H61" s="3">
-        <v>2013300</v>
+        <v>1990600</v>
       </c>
       <c r="I61" s="3">
-        <v>2265100</v>
+        <v>2323900</v>
       </c>
       <c r="J61" s="3">
+        <v>2569300</v>
+      </c>
+      <c r="K61" s="3">
         <v>1978600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1020000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1052100</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1088400</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1700300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1710200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1723300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1719100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>2356900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2282800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2573200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1514000</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1518400</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1483600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1169500</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1498000</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>997900</v>
+        <v>343900</v>
       </c>
       <c r="E62" s="3">
-        <v>1069100</v>
+        <v>335100</v>
       </c>
       <c r="F62" s="3">
-        <v>1083000</v>
+        <v>361500</v>
       </c>
       <c r="G62" s="3">
-        <v>1002900</v>
+        <v>348000</v>
       </c>
       <c r="H62" s="3">
-        <v>1071900</v>
+        <v>340300</v>
       </c>
       <c r="I62" s="3">
-        <v>1074200</v>
+        <v>356100</v>
       </c>
       <c r="J62" s="3">
+        <v>341400</v>
+      </c>
+      <c r="K62" s="3">
         <v>1053700</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1051200</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1106100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1139100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1149700</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1085900</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1116700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1064600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1058500</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>947300</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>999200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1024000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1029300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1029200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1109200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1095800</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>877200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>912100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>870500</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>801900</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>783100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>755000</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>713100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>677900</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>576300</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5804,8 +5953,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5905,8 +6057,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6006,109 +6161,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
-        <v>5633100</v>
+        <v>5457500</v>
       </c>
       <c r="E66" s="3">
-        <v>5889600</v>
+        <v>5627100</v>
       </c>
       <c r="F66" s="3">
-        <v>5936800</v>
+        <v>5883700</v>
       </c>
       <c r="G66" s="3">
-        <v>5873000</v>
+        <v>5930700</v>
       </c>
       <c r="H66" s="3">
-        <v>6379100</v>
+        <v>5867100</v>
       </c>
       <c r="I66" s="3">
-        <v>6664000</v>
+        <v>6373100</v>
       </c>
       <c r="J66" s="3">
+        <v>6657800</v>
+      </c>
+      <c r="K66" s="3">
         <v>6108900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5982300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6088900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6105700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5803100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5704800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6025700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5797600</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5793400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5623600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5450600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5415600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5266800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5634000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5991000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>6034300</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6144,8 +6305,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6245,8 +6407,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6346,8 +6511,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6447,8 +6615,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6548,109 +6719,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7306800</v>
+      </c>
+      <c r="E72" s="3">
         <v>7144800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7075200</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>6970200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6830800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7591200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7490000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7409800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7376300</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7910700</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7630800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7692100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7930000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7867800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7673100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7559200</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7430900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7225800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7274100</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7232300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>6991100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6903300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6709800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6750,8 +6927,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6851,8 +7031,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6952,109 +7135,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7849500</v>
+      </c>
+      <c r="E76" s="3">
         <v>7646500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7641900</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7623100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7265500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>8206100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8099500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8011500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7818800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8600600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8281000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8421400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8745500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8767100</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8492400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8534300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8160700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>7918800</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7841400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8119800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7758800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7815100</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7570800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7154,215 +7343,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45563</v>
+      </c>
+      <c r="E80" s="2">
         <v>45472</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45381</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45199</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45108</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45017</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44926</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44835</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44744</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44653</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44561</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44471</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44380</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44289</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44196</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44100</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44009</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43918</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43830</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43736</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43645</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43554</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43465</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43372</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43281</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43190</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43008</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42917</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42826</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42735</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>162000</v>
+      </c>
+      <c r="E81" s="3">
         <v>157400</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>105000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>139500</v>
       </c>
-      <c r="G81" s="3">
-        <v>-760500</v>
-      </c>
       <c r="H81" s="3">
+        <v>-760400</v>
+      </c>
+      <c r="I81" s="3">
         <v>101200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>80200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>33500</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>-534000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>280400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>245300</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>189100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>271000</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>336300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>236800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>248200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>205100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>-48300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>110500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>264700</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>155500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>202400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>121600</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>226400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226300</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>196600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>208500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>240400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>270000</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>260700</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>200600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>233700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7398,109 +7596,113 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>171500</v>
+        <v>142600</v>
       </c>
       <c r="E83" s="3">
-        <v>154200</v>
+        <v>149600</v>
       </c>
       <c r="F83" s="3">
-        <v>154200</v>
+        <v>162700</v>
       </c>
       <c r="G83" s="3">
-        <v>149600</v>
+        <v>151800</v>
       </c>
       <c r="H83" s="3">
+        <v>146500</v>
+      </c>
+      <c r="I83" s="3">
+        <v>134700</v>
+      </c>
+      <c r="J83" s="3">
+        <v>134200</v>
+      </c>
+      <c r="K83" s="3">
+        <v>159000</v>
+      </c>
+      <c r="L83" s="3">
+        <v>153500</v>
+      </c>
+      <c r="M83" s="3">
+        <v>141600</v>
+      </c>
+      <c r="N83" s="3">
+        <v>141400</v>
+      </c>
+      <c r="O83" s="3">
+        <v>143400</v>
+      </c>
+      <c r="P83" s="3">
+        <v>148600</v>
+      </c>
+      <c r="Q83" s="3">
+        <v>148500</v>
+      </c>
+      <c r="R83" s="3">
+        <v>151200</v>
+      </c>
+      <c r="S83" s="3">
         <v>156600</v>
       </c>
-      <c r="I83" s="3">
-        <v>169900</v>
-      </c>
-      <c r="J83" s="3">
-        <v>159000</v>
-      </c>
-      <c r="K83" s="3">
-        <v>153500</v>
-      </c>
-      <c r="L83" s="3">
-        <v>141600</v>
-      </c>
-      <c r="M83" s="3">
-        <v>141400</v>
-      </c>
-      <c r="N83" s="3">
-        <v>143400</v>
-      </c>
-      <c r="O83" s="3">
-        <v>148600</v>
-      </c>
-      <c r="P83" s="3">
-        <v>148500</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>151200</v>
-      </c>
-      <c r="R83" s="3">
-        <v>156600</v>
-      </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>151300</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>154100</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>145500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>153800</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>144900</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>140500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>137300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>139100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>133000</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>127000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>122700</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>118400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>113500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>109800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>105000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>104400</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7600,8 +7802,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7701,8 +7906,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7802,8 +8010,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7903,8 +8114,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8004,109 +8218,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>319600</v>
+      </c>
+      <c r="E89" s="3">
         <v>233600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>183700</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>296300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>512000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>263600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>257300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>241700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>224800</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>147700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>55000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>212400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>498700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>338400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>259600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>407800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>598500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>568500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>195000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>440700</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>411800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>396200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>170100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>286900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>273500</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>437800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>183200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>319400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>460300</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>248000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>165900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>342900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8142,109 +8362,113 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-115400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-91400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-86800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-240400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-127400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-116700</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-128500</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-150700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-129500</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-300900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-147700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-112700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-114700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-160100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-69100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-80600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-115600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-139800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-124600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-144100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-136900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8344,8 +8568,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8445,109 +8672,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-115400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-91400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-240400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-127400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>37300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-639900</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-251000</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-153300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-105600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-115500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-670700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>442500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>4800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-333300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-324100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-420200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-77000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-133400</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-141600</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-120600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-142100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-211800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8583,31 +8816,32 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
-      <c r="D96" s="3">
-        <v>0</v>
-      </c>
-      <c r="E96" s="3">
-        <v>0</v>
-      </c>
-      <c r="F96" s="3">
-        <v>0</v>
-      </c>
-      <c r="G96" s="3">
-        <v>0</v>
-      </c>
-      <c r="H96" s="3">
-        <v>0</v>
-      </c>
-      <c r="I96" s="3">
-        <v>0</v>
-      </c>
-      <c r="J96" s="3">
-        <v>0</v>
+      <c r="D96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I96" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K96" s="3">
         <v>0</v>
@@ -8684,8 +8918,11 @@
       <c r="AI96" s="3">
         <v>0</v>
       </c>
+      <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8785,8 +9022,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8886,8 +9126,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8987,307 +9230,319 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-270100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-305400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-76100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>63100</v>
       </c>
-      <c r="G100" s="3">
-        <v>-430000</v>
-      </c>
       <c r="H100" s="3">
+        <v>-430100</v>
+      </c>
+      <c r="I100" s="3">
         <v>-294700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>451000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>197300</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>39900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-51800</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>9000</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-397300</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-559200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-155600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-120200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-119100</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-132000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-24200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>87200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-279600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-304900</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-232200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>26800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>46500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>221400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>86600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>16300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>166400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>90900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
-        <v>2100</v>
+        <v>-6900</v>
       </c>
       <c r="E101" s="3">
-        <v>-4900</v>
+        <v>-8200</v>
       </c>
       <c r="F101" s="3">
-        <v>5100</v>
+        <v>-5100</v>
       </c>
       <c r="G101" s="3">
-        <v>-7100</v>
+        <v>-5400</v>
       </c>
       <c r="H101" s="3">
-        <v>-8200</v>
+        <v>-8400</v>
       </c>
       <c r="I101" s="3">
-        <v>-5100</v>
+        <v>3100</v>
       </c>
       <c r="J101" s="3">
+        <v>13300</v>
+      </c>
+      <c r="K101" s="3">
         <v>-5400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-8400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>3100</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>13300</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-3500</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-7700</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>8900</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-17500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>22800</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-2700</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>7400</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-20400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>4000</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-3100</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>600</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>1500</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>1600</v>
       </c>
-      <c r="AD101" s="3">
-        <v>0</v>
-      </c>
       <c r="AE101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF101" s="3">
         <v>4100</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1200</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>12100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>700</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-73400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-161100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>15900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>124100</v>
       </c>
-      <c r="G102" s="3">
-        <v>-52500</v>
-      </c>
       <c r="H102" s="3">
-        <v>-1900</v>
+        <v>-52400</v>
       </c>
       <c r="I102" s="3">
-        <v>63200</v>
+        <v>-2000</v>
       </c>
       <c r="J102" s="3">
+        <v>63300</v>
+      </c>
+      <c r="K102" s="3">
         <v>182700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>103000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-6600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-38300</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-859100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>374400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>196400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-211400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-12600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>43500</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>474600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>128300</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>23500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-16800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>22400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-13400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>27700</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>403400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>30000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>66800</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>9600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,464 +656,476 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E7" s="2">
         <v>45563</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45472</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45381</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45199</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45108</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45017</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44926</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44835</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44744</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44653</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44561</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44471</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44380</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44289</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44196</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44100</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44009</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43918</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43830</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43736</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43645</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43554</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43465</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43372</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43281</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43190</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43008</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42917</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42826</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2637200</v>
+      </c>
+      <c r="E8" s="3">
         <v>2719000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2801300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2679400</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2612300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2766100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2950500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2806200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2650700</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2917500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>3153200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3015700</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2760700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2817000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2953800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2669000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2641800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2574900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2049800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2285800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2424500</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2519200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2584500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1992700</v>
+      </c>
+      <c r="E9" s="3">
         <v>2010000</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2042300</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2024400</v>
       </c>
-      <c r="G9" s="3">
-        <v>1963200</v>
-      </c>
       <c r="H9" s="3">
+        <v>1963400</v>
+      </c>
+      <c r="I9" s="3">
         <v>2031400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2188100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2133700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2060300</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2173500</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2279300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2212600</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2020900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>1979200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2046300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1867100</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1880800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1851000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1629800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1657500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1759300</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1820000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1842000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>644500</v>
+      </c>
+      <c r="E10" s="3">
         <v>709000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>759000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>655000</v>
       </c>
-      <c r="G10" s="3">
-        <v>649000</v>
-      </c>
       <c r="H10" s="3">
+        <v>648900</v>
+      </c>
+      <c r="I10" s="3">
         <v>734700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>762400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>672500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>590400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>744000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>873900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>803100</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>739800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>837900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>907500</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>801900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>761000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>723900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>420000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>628300</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>665200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>699200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>742500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>657500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>656700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>730600</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>778600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>719200</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AF10" s="3">
-        <v>792100</v>
       </c>
       <c r="AG10" s="3">
         <v>792100</v>
       </c>
       <c r="AH10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AI10" s="3">
         <v>683100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>703300</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1150,8 +1162,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1254,8 +1267,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1358,139 +1374,145 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>43500</v>
+      </c>
+      <c r="E14" s="3">
         <v>19500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>41400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>7900</v>
       </c>
-      <c r="G14" s="3">
-        <v>104700</v>
-      </c>
       <c r="H14" s="3">
+        <v>104600</v>
+      </c>
+      <c r="I14" s="3">
         <v>923200</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>41700</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>32200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>43400</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>730300</v>
-      </c>
-      <c r="M14" s="3">
-        <v>1900</v>
       </c>
       <c r="N14" s="3">
         <v>1900</v>
       </c>
       <c r="O14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="P14" s="3">
         <v>4600</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>1100</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>6800</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>11200</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>26100</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>26500</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>67200</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>12700</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>41800</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>74700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>8900</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>35700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>20600</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>19900</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>16000</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>22100</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>15200</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>13900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>15900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>4000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>16200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>156400</v>
+      </c>
+      <c r="E15" s="3">
         <v>156200</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>171500</v>
-      </c>
-      <c r="F15" s="3">
-        <v>154200</v>
       </c>
       <c r="G15" s="3">
         <v>154200</v>
       </c>
       <c r="H15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="I15" s="3">
         <v>149600</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>169900</v>
       </c>
-      <c r="K15" s="3">
-        <v>0</v>
-      </c>
       <c r="L15" s="3">
         <v>0</v>
       </c>
@@ -1536,8 +1558,8 @@
       <c r="Z15" s="3">
         <v>0</v>
       </c>
-      <c r="AA15" s="3" t="s">
-        <v>8</v>
+      <c r="AA15" s="3">
+        <v>0</v>
       </c>
       <c r="AB15" s="3" t="s">
         <v>8</v>
@@ -1548,8 +1570,8 @@
       <c r="AD15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE15" s="3">
-        <v>0</v>
+      <c r="AE15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF15" s="3">
         <v>0</v>
@@ -1566,8 +1588,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1601,216 +1626,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2471900</v>
+      </c>
+      <c r="E17" s="3">
         <v>2487200</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2545900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2524900</v>
       </c>
-      <c r="G17" s="3">
-        <v>2340500</v>
-      </c>
       <c r="H17" s="3">
+        <v>2340600</v>
+      </c>
+      <c r="I17" s="3">
         <v>2576600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2755700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2648300</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2589600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>3423100</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2785300</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2694900</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2507600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2457000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2549400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2351500</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2359000</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2312100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2114400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2134300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2264400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2344100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2317600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>165300</v>
+      </c>
+      <c r="E18" s="3">
         <v>231800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>255400</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>154500</v>
       </c>
-      <c r="G18" s="3">
-        <v>271800</v>
-      </c>
       <c r="H18" s="3">
+        <v>271700</v>
+      </c>
+      <c r="I18" s="3">
         <v>189500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>194800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>157900</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>61100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>-505600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>367900</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>320800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>253100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>360000</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>404400</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>317500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>282800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>262800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>-64600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>151500</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>160100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>175100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>266900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>165300</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>213400</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>287200</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>326300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>268400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>343500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>380100</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>355800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>274700</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>305300</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1847,528 +1879,544 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>1600</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-1100</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-3900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-8500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>2200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-10000</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>1300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2800</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-2500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-1100</v>
       </c>
-      <c r="P20" s="3">
-        <v>0</v>
-      </c>
       <c r="Q20" s="3">
+        <v>0</v>
+      </c>
+      <c r="R20" s="3">
         <v>11200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>6700</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>2600</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-5700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>4300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>12400</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>3000</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>2900</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>3200</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>321300</v>
+      </c>
+      <c r="E21" s="3">
         <v>388700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>425300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>309800</v>
       </c>
-      <c r="G21" s="3">
-        <v>429900</v>
-      </c>
       <c r="H21" s="3">
+        <v>429800</v>
+      </c>
+      <c r="I21" s="3">
         <v>347600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>349200</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>328400</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>210100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>-350900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>512300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>459800</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>395400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>508600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>564100</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>471000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>446000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>414800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>92100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>291300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>318100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>332400</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>410400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>306400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>352000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>419500</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>451300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>387100</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>458100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>492300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>462600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>382600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>412800</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>9900</v>
+      </c>
+      <c r="E22" s="3">
         <v>11200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>12600</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>14900</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>17400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>20100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>22900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>17100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14600</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>13800</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>12100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>11500</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12200</v>
-      </c>
-      <c r="P22" s="3">
-        <v>14900</v>
       </c>
       <c r="Q22" s="3">
         <v>14900</v>
       </c>
       <c r="R22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="S22" s="3">
         <v>15200</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>15900</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>14900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>13000</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>8700</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>11000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>9300</v>
-      </c>
-      <c r="Y22" s="3">
-        <v>10500</v>
       </c>
       <c r="Z22" s="3">
         <v>10500</v>
       </c>
       <c r="AA22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AB22" s="3">
         <v>14400</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>7900</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AE22" s="3">
-        <v>7300</v>
       </c>
       <c r="AF22" s="3">
         <v>7300</v>
       </c>
       <c r="AG22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AH22" s="3">
         <v>8400</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>8200</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E23" s="3">
         <v>201800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>199800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>132800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>153600</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>-745300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>128000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>109200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>36500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-518100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>358700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>306900</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>239800</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>345000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>400700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>304500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>273600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>248600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>-75000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>137100</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>153400</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>178200</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>259400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>158600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>198500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>277500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>316400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>256900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>332500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>371600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>344400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>269400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>300000</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>18300</v>
+      </c>
+      <c r="E24" s="3">
         <v>39800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>42300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>27800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>14200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>15000</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>26800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>28900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>2900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15600</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>78200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>61400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>50700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>73800</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>64200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>67700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>25200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>43200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>-26400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>26700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-111300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>22500</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>56700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>37000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>49500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>118800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>47600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>46300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>100500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>82700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>68400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>65500</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2471,216 +2519,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E26" s="3">
         <v>162000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>157500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>105000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>139400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>-760300</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>101200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>80300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>33600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-533700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>280500</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>245400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>189100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>271200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>336500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>236800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>248400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>205500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>-48600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>110500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>264700</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>155700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>202700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>121600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>258200</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>228000</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>197500</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>209200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>286100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>271000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>261700</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>201100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>234500</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E27" s="3">
         <v>162000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>157400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>105000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>139500</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>-760400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>101200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>80200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>33500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-534000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>280400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>245300</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>189100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>271000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>336300</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>236800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>248200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>205100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>-48300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>110500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>264700</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>155500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>202400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>121600</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>254600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>226300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>196600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>208500</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>285600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>270000</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>260700</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>200600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>233700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2783,8 +2840,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2809,8 +2869,8 @@
       <c r="J29" s="3">
         <v>0</v>
       </c>
-      <c r="K29" s="3" t="s">
-        <v>8</v>
+      <c r="K29" s="3">
+        <v>0</v>
       </c>
       <c r="L29" s="3" t="s">
         <v>8</v>
@@ -2818,8 +2878,8 @@
       <c r="M29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="N29" s="3">
-        <v>0</v>
+      <c r="N29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="O29" s="3">
         <v>0</v>
@@ -2839,17 +2899,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2857,11 +2917,11 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2869,11 +2929,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2887,8 +2947,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2991,8 +3054,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3095,216 +3161,225 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-1600</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>1100</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>3900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>8500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-2200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>10000</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-1300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2800</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>2500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>1100</v>
       </c>
-      <c r="P32" s="3">
-        <v>0</v>
-      </c>
       <c r="Q32" s="3">
+        <v>0</v>
+      </c>
+      <c r="R32" s="3">
         <v>-11200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-6700</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-2600</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>5700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-4300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-12400</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>2100</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>4000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>3800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1300</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3000</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E33" s="3">
         <v>162000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>157400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>105000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>139500</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>-760400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>101200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>80200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>33500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-534000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>280400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>245300</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>189100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>271000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>336300</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>236800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>248200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>205100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>-48300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>110500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>264700</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>155500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>202400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>121600</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>226400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>226300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>196600</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>208500</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>240400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>270000</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>260700</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>200600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>233700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3407,221 +3482,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E35" s="3">
         <v>162000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>157400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>105000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>139500</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>-760400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>101200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>80200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>33500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-534000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>280400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>245300</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>189100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>271000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>336300</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>236800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>248200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>205100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>-48300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>110500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>264700</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>155500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>202400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>121600</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>226400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>226300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>196600</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>208500</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>240400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>270000</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>260700</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>200600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>233700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E38" s="2">
         <v>45563</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45472</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45381</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45199</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45108</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45017</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44926</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44835</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44744</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44653</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44561</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44471</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44380</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44289</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44196</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44100</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44009</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43918</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43830</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43736</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43645</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43554</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43465</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43372</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43281</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43190</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43008</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42917</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42826</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3658,8 +3742,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3696,112 +3781,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>666600</v>
+      </c>
+      <c r="E41" s="3">
         <v>424000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>497400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>658500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>642600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>518500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>570900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>572900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>509600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>327000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>224000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>230600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>268900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>1128000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>753700</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>557300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>768600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>781200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>737700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>263100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>134800</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>111300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>128100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>105700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>119100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>91400</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>518200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>114800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>84900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>84500</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>130200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>188400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>121700</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3824,40 +3913,40 @@
         <v>0</v>
       </c>
       <c r="J42" s="3">
+        <v>0</v>
+      </c>
+      <c r="K42" s="3">
         <v>150000</v>
       </c>
-      <c r="K42" s="3">
+      <c r="L42" s="3">
         <v>158000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>110000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>265000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>310000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>323000</v>
       </c>
-      <c r="P42" s="3">
-        <v>0</v>
-      </c>
       <c r="Q42" s="3">
+        <v>0</v>
+      </c>
+      <c r="R42" s="3">
         <v>662400</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>782300</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>571700</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>407800</v>
-      </c>
-      <c r="U42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V42" s="3" t="s">
         <v>8</v>
@@ -3874,8 +3963,8 @@
       <c r="Z42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA42" s="3">
-        <v>0</v>
+      <c r="AA42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AB42" s="3">
         <v>0</v>
@@ -3904,424 +3993,439 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1804200</v>
+      </c>
+      <c r="E43" s="3">
         <v>2043400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2018500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2007200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>1874700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1943100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2087100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2052400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1904800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2003300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2105800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2044700</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1840000</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1880500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2017600</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1813900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1709500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1711000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1586400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1644800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1526600</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1787200</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1819500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2513600</v>
+      </c>
+      <c r="E44" s="3">
         <v>2612100</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2579900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2527700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2551900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2519700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2618700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2729900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2793800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2900100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2826000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2513200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2391700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2215600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2082000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>1996600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1913000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1842000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1922000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2195400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2282300</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2338000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2367600</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>22300</v>
+      </c>
+      <c r="E45" s="3">
         <v>20800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>16800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>15800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>19300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22500</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>21900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>528900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>514000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>519900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>466200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>414800</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>421900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>434900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>416000</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>400800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>410000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>499800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>509800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>485700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>491400</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>493100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>501600</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>496500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>487100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>456300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>447300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>481300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>345500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>374900</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>307800</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>297900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5496900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5621400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5641300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5721700</v>
       </c>
-      <c r="G46" s="3">
-        <v>5604200</v>
-      </c>
       <c r="H46" s="3">
+        <v>5604300</v>
+      </c>
+      <c r="I46" s="3">
         <v>5504300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5851300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>6061100</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5895100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5854300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5940700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5564700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5238400</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5646100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5950600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5566000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5363700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5152000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>4746000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4613000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4429500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4727800</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4808300</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4346,8 +4450,8 @@
       <c r="J47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
+      <c r="K47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L47" s="3">
         <v>0</v>
@@ -4424,216 +4528,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>4953900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5142900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5155400</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5298700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5421700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5193300</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5357600</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5342000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5049000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>4924900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4986800</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4937400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5026800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4827900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4842700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4769900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4914400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4708300</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4752600</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4804200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>5021900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4934700</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5058000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1904000</v>
+      </c>
+      <c r="E49" s="3">
         <v>2019300</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1978100</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1994000</v>
       </c>
-      <c r="G49" s="3">
-        <v>2035100</v>
-      </c>
       <c r="H49" s="3">
+        <v>2035000</v>
+      </c>
+      <c r="I49" s="3">
         <v>1979900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2919000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2915500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2785700</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2651100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>3392700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3462900</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3507900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3523500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3531900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3516600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3602400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3493400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3452700</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3424000</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3498900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3436200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3516300</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4736,8 +4849,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4840,8 +4956,11 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4866,86 +4985,89 @@
       <c r="J52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K52" s="3">
+      <c r="K52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L52" s="3">
         <v>390600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>370700</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>369200</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>421700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>451400</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>452800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>467600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>437600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>447300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>430500</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>418100</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>415700</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>436400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>294100</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>423400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>421300</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>407100</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>399400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>393700</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>389900</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>387900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>390900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>391200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>357500</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>279700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5048,112 +5170,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>12778600</v>
+      </c>
+      <c r="E54" s="3">
         <v>13313200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13279600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13531500</v>
       </c>
-      <c r="G54" s="3">
-        <v>13559900</v>
-      </c>
       <c r="H54" s="3">
+        <v>13559800</v>
+      </c>
+      <c r="I54" s="3">
         <v>13138500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>14585200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14763500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14120400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13801000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14689500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14386700</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14224500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14450300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14792800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14290100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14327800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>13784200</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13369400</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13256900</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13386700</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13392800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13806100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5190,8 +5318,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5228,632 +5357,651 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>978500</v>
+      </c>
+      <c r="E57" s="3">
         <v>1061200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1082800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1101900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1038000</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1082400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1184100</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1211700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1094000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1217700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1359200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1296100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1228600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1147000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1131200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1064800</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1016900</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>989900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>845300</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>899200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>825000</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>964100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>976200</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>914200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>811900</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>925200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>951200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>897500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>810000</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>859900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>871400</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>780500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>729400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>667900</v>
+      </c>
+      <c r="E58" s="3">
         <v>576900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>827900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>1040800</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1110600</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1029100</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1144100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1163000</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>840600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1542100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1498900</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1546500</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>624500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>588700</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>958800</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>953900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>377300</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>356100</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>135400</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>1210500</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1051500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1273200</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1891500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>31000</v>
+      </c>
+      <c r="E59" s="3">
         <v>35100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>34400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34500</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>39800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>47100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>41200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>1135700</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1144900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1066300</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1029100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1093200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1166100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1088900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>988600</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>977100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1041100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>891600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>761600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>836100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>877400</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>838000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>756700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>712000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>698200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>638400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>566500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>641600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>664300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>595200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>549900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>606200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2672300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2771000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2937700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>3120100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3145900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3188600</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3287900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3318400</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3070300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3904700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3924400</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3871600</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>2946400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2901700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3178900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3007300</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2371200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2387100</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>1872200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2871300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2712600</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>3114700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3705800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1960400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2014400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1993100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2016300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2039300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1990600</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2323900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2569300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>1978600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1020000</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1052100</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1088400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1700300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1710200</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1723300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1719100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>2356900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2282800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2573200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1514000</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1518400</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1483600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1169500</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>328400</v>
+      </c>
+      <c r="E62" s="3">
         <v>343900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>335100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>361500</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>348000</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>340300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>356100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>341400</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>1053700</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1051200</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1106100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1139100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1149700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1085900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1116700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1064600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1058500</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>947300</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>999200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1024000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1029300</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1029200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1109200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>877200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>912100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>870500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>801900</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>783100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>755000</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>713100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>677900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>576300</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5956,8 +6104,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6060,8 +6211,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6164,112 +6318,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5221700</v>
+      </c>
+      <c r="E66" s="3">
         <v>5457500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5627100</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5883700</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5930700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5867100</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>6373100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6657800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6108900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5982300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6088900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6105700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>5803100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5704800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6025700</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5797600</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5793400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5623600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5450600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5415600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5266800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5634000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5991000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6306,8 +6466,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6410,8 +6571,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6514,8 +6678,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6618,8 +6785,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6722,112 +6892,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7325100</v>
+      </c>
+      <c r="E72" s="3">
         <v>7306800</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7144800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7075200</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>6970200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6830800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7591200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7490000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7409800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7376300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7910700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7630800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7692100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7930000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7867800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7673100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7559200</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7430900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7225800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7274100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7232300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>6991100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6903300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6930,8 +7106,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7034,8 +7213,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7138,112 +7320,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7551400</v>
+      </c>
+      <c r="E76" s="3">
         <v>7849500</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7646500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7641900</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7623100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7265500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>8206100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8099500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8011500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7818800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8600600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8281000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8421400</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8745500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8767100</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8492400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8534300</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8160700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>7918800</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7841400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8119800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7758800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7815100</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7346,221 +7534,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45657</v>
+      </c>
+      <c r="E80" s="2">
         <v>45563</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45472</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45381</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45199</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45108</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45017</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44926</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44835</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44744</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44653</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44561</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44471</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44380</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44289</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44196</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44100</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44009</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43918</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43830</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43736</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43645</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43554</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43465</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43372</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43281</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43190</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43008</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42917</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42826</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42735</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>93200</v>
+      </c>
+      <c r="E81" s="3">
         <v>162000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>157400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>105000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>139500</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>-760400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>101200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>80200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>33500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-534000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>280400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>245300</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>189100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>271000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>336300</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>236800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>248200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>205100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>-48300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>110500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>264700</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>155500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>202400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>121600</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>226400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>226300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>196600</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>208500</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>240400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>270000</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>260700</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>200600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>233700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7597,112 +7794,116 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>267500</v>
+      </c>
+      <c r="E83" s="3">
         <v>142600</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>149600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>162700</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>151800</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>146500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>134700</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>134200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>159000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>153500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>141600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>141400</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>143400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>148600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>148500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>151200</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>156600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>151300</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>154100</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>145500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>153800</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>144900</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>140500</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>137300</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>139100</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>133000</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>127000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>122700</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>118400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>113500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>109800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>105000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>104400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7805,8 +8006,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7909,8 +8113,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8013,8 +8220,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8117,8 +8327,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8221,112 +8434,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>397000</v>
+      </c>
+      <c r="E89" s="3">
         <v>319600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>233600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>183700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>296300</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>512000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>263600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>257300</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>241700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>224800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>147700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>55000</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>212400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>498700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>338400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>259600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>407800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>598500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>568500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>195000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>440700</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>411800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>396200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>170100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>286900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>273500</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>437800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>183200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>319400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>460300</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>248000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>165900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>342900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8363,112 +8582,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-160800</v>
+      </c>
+      <c r="E91" s="3">
         <v>-115400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-91400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-86800</v>
       </c>
-      <c r="G91" s="3">
-        <v>-240400</v>
-      </c>
       <c r="H91" s="3">
+        <v>-240300</v>
+      </c>
+      <c r="I91" s="3">
         <v>-127400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-116700</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-128500</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-150700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-129500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-300900</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-147700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-112700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-114700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-160100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-69100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-80600</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-115600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-139800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-124600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-144100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8571,8 +8794,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8675,112 +8901,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-160800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-115400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-91400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-86800</v>
       </c>
-      <c r="G94" s="3">
-        <v>-240400</v>
-      </c>
       <c r="H94" s="3">
+        <v>-240300</v>
+      </c>
+      <c r="I94" s="3">
         <v>-127400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>37300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-639900</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-251000</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-153300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-105600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-115500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-670700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>442500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>4800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-333300</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-324100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-420200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-77000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-133400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-141600</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-120600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-142100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8817,8 +9049,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8843,8 +9076,8 @@
       <c r="J96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K96" s="3">
-        <v>0</v>
+      <c r="K96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L96" s="3">
         <v>0</v>
@@ -8921,8 +9154,11 @@
       <c r="AJ96" s="3">
         <v>0</v>
       </c>
+      <c r="AK96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9025,8 +9261,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9129,8 +9368,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9233,316 +9475,328 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E100" s="3">
         <v>-270100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-305400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-76100</v>
       </c>
-      <c r="G100" s="3">
-        <v>63100</v>
-      </c>
       <c r="H100" s="3">
+        <v>63200</v>
+      </c>
+      <c r="I100" s="3">
         <v>-430100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-294700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>451000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>197300</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>39900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-51800</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>9000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-397300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-559200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-155600</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-120200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-119100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-132000</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-24200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>87200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-279600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-304900</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-232200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>26800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>46500</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>221400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>86600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>16300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>166400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>90900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>-6900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-8200</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-5100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5400</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-8400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>3100</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>13300</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>13300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-3500</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-7700</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>8900</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-17500</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>22800</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-2700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>7400</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-20400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>4000</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-3100</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>600</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>1500</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1600</v>
       </c>
-      <c r="AE101" s="3">
-        <v>0</v>
-      </c>
       <c r="AF101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG101" s="3">
         <v>4100</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>1200</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>12100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>700</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>242600</v>
+      </c>
+      <c r="E102" s="3">
         <v>-73400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-161100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>15900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>124100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-52400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2000</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>63300</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>182700</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>103000</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-6600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-38300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-859100</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>374400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>196400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-211400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-12600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>43500</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>474600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>128300</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>23500</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-16800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>22400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>27700</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>403400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>30000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>66800</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>9600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="179" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,476 +656,489 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E7" s="2">
         <v>45657</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45563</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45472</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45381</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45199</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45108</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45017</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44926</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44835</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44744</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44653</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44561</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44471</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44380</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44289</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44196</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44100</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44009</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43918</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43830</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43736</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43645</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43554</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43465</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43372</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43281</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43190</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43008</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42917</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42735</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2525800</v>
+      </c>
+      <c r="E8" s="3">
         <v>2637200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2719000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2801300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2679400</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2612300</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2766100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2950500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2806200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2650700</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2917500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>3153200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3015700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2760700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2817000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2953800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2669000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2641800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2574900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2049800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2285800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2424500</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2519200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2584500</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>1917300</v>
+      </c>
+      <c r="E9" s="3">
         <v>1992700</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2010000</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2042300</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2024400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1963400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2031400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2188100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2133700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2060300</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2173500</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2279300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2212600</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2020900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>1979200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2046300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>1867100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1880800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1851000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1629800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1657500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1759300</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1820000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1842000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>608500</v>
+      </c>
+      <c r="E10" s="3">
         <v>644500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>709000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>759000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>655000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>648900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>734700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>762400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>672500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>590400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>744000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>873900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>803100</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>739800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>837900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>907500</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>801900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>761000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>723900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>420000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>628300</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>665200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>699200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>742500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>657500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>656700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>730600</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>778600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>719200</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AG10" s="3">
-        <v>792100</v>
       </c>
       <c r="AH10" s="3">
         <v>792100</v>
       </c>
       <c r="AI10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AJ10" s="3">
         <v>683100</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>703300</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1163,8 +1176,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1270,8 +1284,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1377,145 +1394,151 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>25300</v>
+      </c>
+      <c r="E14" s="3">
         <v>43500</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>19500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>41400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>7900</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>104600</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>923200</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>41700</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>32200</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>43400</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>730300</v>
-      </c>
-      <c r="N14" s="3">
-        <v>1900</v>
       </c>
       <c r="O14" s="3">
         <v>1900</v>
       </c>
       <c r="P14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="Q14" s="3">
         <v>4600</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>1100</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>6800</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>11200</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>26100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>26500</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>67200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>12700</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>41800</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>74700</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>8900</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>35700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>20600</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>19900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>16000</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>22100</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>15200</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>13900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>15900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>16200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>150400</v>
+      </c>
+      <c r="E15" s="3">
         <v>156400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>156200</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>171500</v>
-      </c>
-      <c r="G15" s="3">
-        <v>154200</v>
       </c>
       <c r="H15" s="3">
         <v>154200</v>
       </c>
       <c r="I15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="J15" s="3">
         <v>149600</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>156600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>169900</v>
       </c>
-      <c r="L15" s="3">
-        <v>0</v>
-      </c>
       <c r="M15" s="3">
         <v>0</v>
       </c>
@@ -1561,8 +1584,8 @@
       <c r="AA15" s="3">
         <v>0</v>
       </c>
-      <c r="AB15" s="3" t="s">
-        <v>8</v>
+      <c r="AB15" s="3">
+        <v>0</v>
       </c>
       <c r="AC15" s="3" t="s">
         <v>8</v>
@@ -1573,8 +1596,8 @@
       <c r="AE15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF15" s="3">
-        <v>0</v>
+      <c r="AF15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG15" s="3">
         <v>0</v>
@@ -1591,8 +1614,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1627,222 +1653,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2404500</v>
+      </c>
+      <c r="E17" s="3">
         <v>2471900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2487200</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2545900</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2524900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2340600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2576600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2755700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2648300</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2589600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>3423100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2785300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2694900</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2507600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2457000</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2549400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2351500</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2359000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2312100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2114400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2134300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2264400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2344100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2317600</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>121300</v>
+      </c>
+      <c r="E18" s="3">
         <v>165300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>231800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>255400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>154500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>271700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>189500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>194800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>157900</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>61100</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>-505600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>367900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>320800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>253100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>360000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>404400</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>317500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>282800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>262800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>-64600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>151500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>160100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>175100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>266900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>165300</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>213400</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>287200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>326300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>268400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>343500</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>380100</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>355800</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>274700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>305300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1880,543 +1913,559 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>1600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-1100</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-3900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-8500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>2200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-600</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-10000</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>1300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2800</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-2500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-1100</v>
       </c>
-      <c r="Q20" s="3">
-        <v>0</v>
-      </c>
       <c r="R20" s="3">
+        <v>0</v>
+      </c>
+      <c r="S20" s="3">
         <v>11200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>2300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>6700</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2600</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-5700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>4300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>12400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>3000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>3200</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>272200</v>
+      </c>
+      <c r="E21" s="3">
         <v>321300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>388700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>425300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>309800</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>429800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>347600</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>349200</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>328400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>210100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>-350900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>512300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>459800</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>395400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>508600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>564100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>471000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>446000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>414800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>92100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>291300</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>318100</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>332400</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>410400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>306400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>352000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>419500</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>451300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>387100</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>458100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>492300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>462600</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>382600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>412800</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>6400</v>
+      </c>
+      <c r="E22" s="3">
         <v>9900</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>11200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>12600</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>14900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>17400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>20100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>22900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>14600</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>13800</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>12100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>11500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>12200</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>14900</v>
       </c>
       <c r="R22" s="3">
         <v>14900</v>
       </c>
       <c r="S22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="T22" s="3">
         <v>15200</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>15900</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>14900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>13000</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>8700</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>11000</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>9300</v>
-      </c>
-      <c r="Z22" s="3">
-        <v>10500</v>
       </c>
       <c r="AA22" s="3">
         <v>10500</v>
       </c>
       <c r="AB22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AC22" s="3">
         <v>14400</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9000</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>7900</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AF22" s="3">
-        <v>7300</v>
       </c>
       <c r="AG22" s="3">
         <v>7300</v>
       </c>
       <c r="AH22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AI22" s="3">
         <v>8400</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>8200</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8500</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>90100</v>
+      </c>
+      <c r="E23" s="3">
         <v>111500</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>201800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>199800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>132800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>153600</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>-745300</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>128000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>109200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>36500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-518100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>358700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>306900</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>239800</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>345000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>400700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>304500</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>273600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>248600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>-75000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>137100</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>153400</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>178200</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>259400</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>158600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>198500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>277500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>316400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>256900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>332500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>371600</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>344400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>269400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>300000</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>17500</v>
+      </c>
+      <c r="E24" s="3">
         <v>18300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>39800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>42300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>27800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>14200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>15000</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>26800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>28900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>2900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15600</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>78200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>61400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>50700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>73800</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>64200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>67700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>25200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>43200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>-26400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>26700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>-111300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>22500</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>56700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>37000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>49500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>118800</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>47600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>46300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>100500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>82700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>68400</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>65500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2522,222 +2571,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E26" s="3">
         <v>93200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>162000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>157500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>105000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>139400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>-760300</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>101200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>80300</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>33600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-533700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>280500</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>245400</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>189100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>271200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>336500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>236800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>248400</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>205500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>-48600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>110500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>264700</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>155700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>202700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>121600</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>258200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>228000</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>197500</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>209200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>286100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>271000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>261700</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>201100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>234500</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E27" s="3">
         <v>93200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>162000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>157400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>105000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>139500</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>-760400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>101200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>80200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>33500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-534000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>280400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>245300</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>189100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>271000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>336300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>236800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>248200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>205100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>-48300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>110500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>264700</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>155500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>202400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>121600</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>254600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>226300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>196600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>208500</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>285600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>270000</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>260700</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>233700</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2843,8 +2901,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2872,8 +2933,8 @@
       <c r="K29" s="3">
         <v>0</v>
       </c>
-      <c r="L29" s="3" t="s">
-        <v>8</v>
+      <c r="L29" s="3">
+        <v>0</v>
       </c>
       <c r="M29" s="3" t="s">
         <v>8</v>
@@ -2881,8 +2942,8 @@
       <c r="N29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O29" s="3">
-        <v>0</v>
+      <c r="O29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P29" s="3">
         <v>0</v>
@@ -2902,17 +2963,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2920,11 +2981,11 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2932,11 +2993,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2950,8 +3011,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3057,8 +3121,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3164,222 +3231,231 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-1600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>1100</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>3900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>8500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-2200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>600</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>10000</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-1300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2800</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>2500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>1100</v>
       </c>
-      <c r="Q32" s="3">
-        <v>0</v>
-      </c>
       <c r="R32" s="3">
+        <v>0</v>
+      </c>
+      <c r="S32" s="3">
         <v>-11200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-2300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-6700</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2600</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>5700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-12400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>2100</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>4000</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>3800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>1300</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>3000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E33" s="3">
         <v>93200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>162000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>157400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>105000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>139500</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>-760400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>101200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>80200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>33500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-534000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>280400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>245300</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>189100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>271000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>336300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>236800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>248200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>205100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>-48300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>110500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>264700</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>155500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>202400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>121600</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>226400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>226300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>196600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>208500</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>240400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>270000</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>260700</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>233700</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3485,227 +3561,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E35" s="3">
         <v>93200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>162000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>157400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>105000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>139500</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>-760400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>101200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>80200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>33500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-534000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>280400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>245300</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>189100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>271000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>336300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>236800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>248200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>205100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>-48300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>110500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>264700</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>155500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>202400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>121600</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>226400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>226300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>196600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>208500</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>240400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>270000</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>260700</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>233700</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E38" s="2">
         <v>45657</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45563</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45472</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45381</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45199</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45108</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45017</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44926</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44835</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44744</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44653</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44561</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44471</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44380</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44289</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44196</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44100</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44009</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43918</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43830</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43736</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43645</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43554</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43465</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43372</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43281</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43190</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43008</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42917</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42735</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3743,8 +3828,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3782,115 +3868,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>702500</v>
+      </c>
+      <c r="E41" s="3">
         <v>666600</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>424000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>497400</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>658500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>642600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>518500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>570900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>572900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>509600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>327000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>224000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>230600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>268900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>1128000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>753700</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>557300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>768600</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>781200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>737700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>263100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>134800</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>111300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>128100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>105700</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>119100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>91400</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>518200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>114800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>84900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>84500</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>130200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>188400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>121700</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3916,40 +4006,40 @@
         <v>0</v>
       </c>
       <c r="K42" s="3">
+        <v>0</v>
+      </c>
+      <c r="L42" s="3">
         <v>150000</v>
       </c>
-      <c r="L42" s="3">
+      <c r="M42" s="3">
         <v>158000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>110000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>265000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>310000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>323000</v>
       </c>
-      <c r="Q42" s="3">
-        <v>0</v>
-      </c>
       <c r="R42" s="3">
+        <v>0</v>
+      </c>
+      <c r="S42" s="3">
         <v>662400</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>782300</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>571700</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>407800</v>
-      </c>
-      <c r="V42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W42" s="3" t="s">
         <v>8</v>
@@ -3966,8 +4056,8 @@
       <c r="AA42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB42" s="3">
-        <v>0</v>
+      <c r="AB42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC42" s="3">
         <v>0</v>
@@ -3996,436 +4086,451 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2129700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1804200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2043400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2018500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2007200</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1874700</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1943100</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2087100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2052400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1904800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2003300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2105800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2044700</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1840000</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1880500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2017600</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1813900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1709500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1711000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1586400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1644800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1526600</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1787200</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1819500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2610400</v>
+      </c>
+      <c r="E44" s="3">
         <v>2513600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2612100</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2579900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2527700</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2551900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2519700</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2618700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2729900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2793800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2900100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2826000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2513200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2391700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2215600</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2082000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>1996600</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1913000</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1842000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1922000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>2195400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2282300</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2338000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2367600</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E45" s="3">
         <v>22300</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>20800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>16800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>15800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>19300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>22400</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22500</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>21900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>528900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>514000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>519900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>466200</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>414800</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>421900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>434900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>416000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>400800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>410000</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>499800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>509800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>485700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>491400</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>493100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>501600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>496500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>487100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>456300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>447300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>481300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>345500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>374900</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>307800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>297900</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5977900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5496900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5621400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5641300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5721700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5604300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5504300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5851300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>6061100</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5895100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5854300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5940700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5564700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5238400</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5646100</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5950600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5566000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5363700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5152000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>4746000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4613000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4429500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4727800</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4808300</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4453,8 +4558,8 @@
       <c r="K47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
+      <c r="L47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M47" s="3">
         <v>0</v>
@@ -4531,222 +4636,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5032100</v>
+      </c>
+      <c r="E48" s="3">
         <v>4953900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5142900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5155400</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5298700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5421700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5193300</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5357600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5342000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5049000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>4924900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4986800</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4937400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5026800</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4827900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4842700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4769900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4914400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4708300</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4752600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4804200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>5021900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4934700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>5058000</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1950000</v>
+      </c>
+      <c r="E49" s="3">
         <v>1904000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2019300</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1978100</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1994000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2035000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1979900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>2919000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2915500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2785700</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2651100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>3392700</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3462900</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3507900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3523500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3531900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3516600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3602400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3493400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3452700</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3424000</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3498900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3436200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3516300</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4852,8 +4966,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4959,8 +5076,11 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -4988,86 +5108,89 @@
       <c r="K52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L52" s="3">
+      <c r="L52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M52" s="3">
         <v>390600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>370700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>369200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>421700</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>451400</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>452800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>467600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>437600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>447300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>430500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>418100</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>415700</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>436400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>294100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>423400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>421300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>407100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>399400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>393700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>389900</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>387900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>390900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>391200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>357500</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>279700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5173,115 +5296,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13408500</v>
+      </c>
+      <c r="E54" s="3">
         <v>12778600</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13313200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13279600</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13531500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13559800</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13138500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>14585200</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14763500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14120400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13801000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14689500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14386700</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14224500</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14450300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14792800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14290100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14327800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>13784200</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13369400</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13256900</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13386700</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13392800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13806100</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5319,8 +5448,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5358,650 +5488,669 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1124600</v>
+      </c>
+      <c r="E57" s="3">
         <v>978500</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1061200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1082800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1101900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1038000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1082400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1184100</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1211700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1094000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1217700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1359200</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1296100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1228600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1147000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1131200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1064800</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1016900</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>989900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>845300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>899200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>825000</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>964100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>976200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>914200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>811900</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>925200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>951200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>897500</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>810000</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>859900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>871400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>780500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>729400</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>797900</v>
+      </c>
+      <c r="E58" s="3">
         <v>667900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>576900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>827900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>1040800</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1110600</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1029100</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1144100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1163000</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>840600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1542100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1498900</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1546500</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>624500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>588700</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>958800</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>953900</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>377300</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>356100</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>135400</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>1210500</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1051500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1273200</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1891500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>29600</v>
+      </c>
+      <c r="E59" s="3">
         <v>31000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>35100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>34400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34500</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>39800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>47100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>41200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>1135700</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1144900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1066300</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1029100</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1093200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1166100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1088900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>988600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>977100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1041100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>891600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>761600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>836100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>877400</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>838000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>756700</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>712000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>698200</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>638400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>566500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>641600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>664300</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>595200</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>549900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>606200</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2972400</v>
+      </c>
+      <c r="E60" s="3">
         <v>2672300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2771000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2937700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>3120100</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3145900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3188600</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3287900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3318400</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3070300</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3904700</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3924400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3871600</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>2946400</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2901700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3178900</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3007300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2371200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2387100</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>1872200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2871300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2712600</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>3114700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3705800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>1990300</v>
+      </c>
+      <c r="E61" s="3">
         <v>1960400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2014400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1993100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>2016300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2039300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1990600</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2323900</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2569300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1978600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1020000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1052100</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1088400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1700300</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1710200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1723300</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1719100</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>2356900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2282800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2573200</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1514000</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1518400</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1483600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1169500</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>340400</v>
+      </c>
+      <c r="E62" s="3">
         <v>328400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>343900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>335100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>361500</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>348000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>340300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>356100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>341400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>1053700</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1051200</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1106100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1139100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1149700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1085900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1116700</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1064600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1058500</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>947300</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>999200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1024000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1029300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1029200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1109200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>877200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>912100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>870500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>801900</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>783100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>755000</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>713100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>677900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>576300</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6107,8 +6256,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6214,8 +6366,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6321,115 +6476,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5546600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5221700</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5457500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5627100</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5883700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5930700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5867100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>6373100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6657800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6108900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5982300</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6088900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6105700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5803100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5704800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6025700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5797600</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5793400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5623600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5450600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5415600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5266800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5634000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5991000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6467,8 +6628,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6574,8 +6736,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6681,8 +6846,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6788,8 +6956,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6895,115 +7066,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7372200</v>
+      </c>
+      <c r="E72" s="3">
         <v>7325100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7306800</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7144800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7075200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>6970200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6830800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7591200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7490000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7409800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7376300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7910700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7630800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7692100</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7930000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7867800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7673100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7559200</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7430900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7225800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7274100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7232300</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>6991100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6903300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7109,8 +7286,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7216,8 +7396,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7323,115 +7506,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>7856100</v>
+      </c>
+      <c r="E76" s="3">
         <v>7551400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7849500</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7646500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7641900</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7623100</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7265500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>8206100</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8099500</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8011500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7818800</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8600600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8281000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8421400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8745500</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8767100</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8492400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8534300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8160700</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>7918800</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7841400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8119800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7758800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7815100</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7537,227 +7726,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45745</v>
+      </c>
+      <c r="E80" s="2">
         <v>45657</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45563</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45472</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45381</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45199</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45108</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45017</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44926</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44835</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44744</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44653</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44561</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44471</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44380</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44289</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44196</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44100</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44009</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43918</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43830</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43736</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43645</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43554</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43465</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43372</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43281</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43190</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43008</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42917</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42826</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42735</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>72600</v>
+      </c>
+      <c r="E81" s="3">
         <v>93200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>162000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>157400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>105000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>139500</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>-760400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>101200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>80200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>33500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-534000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>280400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>245300</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>189100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>271000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>336300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>236800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>248200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>205100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>-48300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>110500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>264700</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>155500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>202400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>121600</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>226400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>226300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>196600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>208500</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>240400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>270000</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>260700</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>200600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>233700</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7795,115 +7993,119 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>147200</v>
+      </c>
+      <c r="E83" s="3">
         <v>267500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>142600</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>149600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>162700</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>151800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>146500</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>134700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>159000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>153500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>141600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>141400</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>143400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>148600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>148500</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>151200</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>156600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>151300</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>154100</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>145500</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>153800</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>144900</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>140500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>137300</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>139100</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>133000</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>127000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>122700</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>118400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>113500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>109800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>105000</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>104400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8009,8 +8211,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8116,8 +8321,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8223,8 +8431,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8330,8 +8541,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8437,115 +8651,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>3700</v>
+      </c>
+      <c r="E89" s="3">
         <v>397000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>319600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>233600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>183700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>296300</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>512000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>263600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>257300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>241700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>224800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>147700</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>55000</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>212400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>498700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>338400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>259600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>407800</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>598500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>568500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>195000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>440700</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>411800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>396200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>170100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>286900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>273500</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>437800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>183200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>319400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>460300</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>248000</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>165900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>342900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8583,115 +8803,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-160800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-115400</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-91400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-86800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-240300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-127400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-116700</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-128500</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-150700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-150600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-129500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-300900</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-147700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-112700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-114700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-160100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-69100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-80600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-115600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-139800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-124600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8797,8 +9021,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8904,115 +9131,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-89100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-160800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-115400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-91400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-86800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-240300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-127400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>37300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-639900</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-251000</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-153300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-105600</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-115500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-670700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>442500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>4800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-333300</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-324100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-420200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-77000</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-133400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-141600</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-120600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-142100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9050,8 +9283,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9079,8 +9313,8 @@
       <c r="K96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L96" s="3">
-        <v>0</v>
+      <c r="L96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M96" s="3">
         <v>0</v>
@@ -9157,8 +9391,11 @@
       <c r="AK96" s="3">
         <v>0</v>
       </c>
+      <c r="AL96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9264,8 +9501,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9371,8 +9611,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9478,325 +9721,337 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>90800</v>
+      </c>
+      <c r="E100" s="3">
         <v>22100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-270100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-305400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-76100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>63200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-430100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-294700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>451000</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>197300</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>39900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-51800</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>9000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-397300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-559200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-155600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-120200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-119100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-132000</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-24200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>87200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-279600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-304900</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>26800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>46500</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>221400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>86600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>16300</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>166400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>90900</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-4900</v>
+      </c>
+      <c r="E101" s="3">
         <v>4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-6900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-8200</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-5100</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5400</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>3100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>13300</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-3500</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-7700</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>8900</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-17500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>22800</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-2700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>7400</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-20400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>4000</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-3100</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>600</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>1500</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1600</v>
       </c>
-      <c r="AF101" s="3">
-        <v>0</v>
-      </c>
       <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH101" s="3">
         <v>4100</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1200</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>12100</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>700</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>35900</v>
+      </c>
+      <c r="E102" s="3">
         <v>242600</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-73400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-161100</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>15900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>124100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-52400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2000</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>63300</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>182700</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>103000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-6600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-38300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-859100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>374400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>196400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-211400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-12600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>43500</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>474600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>128300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>23500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-16800</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>22400</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>27700</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>403400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>30000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>400</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>66800</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>9600</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="183" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="187" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,489 +656,502 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="17" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="21" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E7" s="2">
         <v>45745</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45657</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45563</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45472</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45381</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45199</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45108</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45017</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44926</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44835</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44744</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44653</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44561</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44471</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44380</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44289</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44196</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44100</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44009</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43918</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43830</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43736</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43645</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43554</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43465</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43372</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43281</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43190</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43008</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42826</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42735</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2802100</v>
+      </c>
+      <c r="E8" s="3">
         <v>2525800</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2637200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2719000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2801300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2679400</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2612300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2766100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2950500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2806200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2650700</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2917500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>3153200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>3015700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2760700</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>2817000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2953800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2669000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2641800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2574900</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2049800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2285800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2424500</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2519200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2584500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2061500</v>
+      </c>
+      <c r="E9" s="3">
         <v>1917300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>1992700</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2010000</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>2042300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>2024400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>1963400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2031400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2188100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2133700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2060300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2173500</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2279300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2212600</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2020900</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>1979200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2046300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1867100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1880800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1851000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1629800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1657500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1759300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1820000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1842000</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>740600</v>
+      </c>
+      <c r="E10" s="3">
         <v>608500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>644500</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>709000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>759000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>655000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>648900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>734700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>762400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>672500</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>590400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>744000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>873900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>803100</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>739800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>837900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>907500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>801900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>761000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>723900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>420000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>628300</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>665200</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>699200</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>742500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>657500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>656700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>730600</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>778600</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>719200</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AH10" s="3">
-        <v>792100</v>
       </c>
       <c r="AI10" s="3">
         <v>792100</v>
       </c>
       <c r="AJ10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AK10" s="3">
         <v>683100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>703300</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1177,8 +1190,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1287,8 +1301,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1397,151 +1414,157 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>29400</v>
+      </c>
+      <c r="E14" s="3">
         <v>25300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>43500</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>19500</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>41400</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>7900</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>104600</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>923200</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>41700</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>32200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>43400</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>730300</v>
-      </c>
-      <c r="O14" s="3">
-        <v>1900</v>
       </c>
       <c r="P14" s="3">
         <v>1900</v>
       </c>
       <c r="Q14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="R14" s="3">
         <v>4600</v>
       </c>
-      <c r="R14" s="3">
+      <c r="S14" s="3">
         <v>1100</v>
       </c>
-      <c r="S14" s="3">
+      <c r="T14" s="3">
         <v>6800</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>11200</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>26100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>26500</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>67200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>12700</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>41800</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>74700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>8900</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>35700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>20600</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>19900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>16000</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>22100</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>15200</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>13900</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>15900</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>4000</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>16200</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>155600</v>
+      </c>
+      <c r="E15" s="3">
         <v>150400</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>156400</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>156200</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>171500</v>
-      </c>
-      <c r="H15" s="3">
-        <v>154200</v>
       </c>
       <c r="I15" s="3">
         <v>154200</v>
       </c>
       <c r="J15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="K15" s="3">
         <v>149600</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>156600</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>169900</v>
       </c>
-      <c r="M15" s="3">
-        <v>0</v>
-      </c>
       <c r="N15" s="3">
         <v>0</v>
       </c>
@@ -1587,8 +1610,8 @@
       <c r="AB15" s="3">
         <v>0</v>
       </c>
-      <c r="AC15" s="3" t="s">
-        <v>8</v>
+      <c r="AC15" s="3">
+        <v>0</v>
       </c>
       <c r="AD15" s="3" t="s">
         <v>8</v>
@@ -1599,8 +1622,8 @@
       <c r="AF15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG15" s="3">
-        <v>0</v>
+      <c r="AG15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AH15" s="3">
         <v>0</v>
@@ -1617,8 +1640,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1654,228 +1680,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2584000</v>
+      </c>
+      <c r="E17" s="3">
         <v>2404500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2471900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2487200</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2545900</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2524900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2340600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2576600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2755700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2648300</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2589600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>3423100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2785300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2694900</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2507600</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2457000</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2549400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2351500</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2359000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2312100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2114400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2134300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2264400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2344100</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2317600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>218100</v>
+      </c>
+      <c r="E18" s="3">
         <v>121300</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>165300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>231800</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>255400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>154500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>271700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>189500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>194800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>157900</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>61100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>-505600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>367900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>320800</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>253100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>360000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>404400</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>317500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>282800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>262800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>-64600</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>151500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>160100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>175100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>266900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>165300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>213400</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>287200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>326300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>268400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>343500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>380100</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>355800</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>274700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>305300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1914,558 +1947,574 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>1600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-1100</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-3900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-8500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>2200</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-600</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-10000</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>1300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>2800</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-2500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-1100</v>
       </c>
-      <c r="R20" s="3">
-        <v>0</v>
-      </c>
       <c r="S20" s="3">
+        <v>0</v>
+      </c>
+      <c r="T20" s="3">
         <v>11200</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>2300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>6700</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>700</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2600</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-5700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>4300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>12400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>3000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>3700</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-500</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>2900</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>3200</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>370700</v>
+      </c>
+      <c r="E21" s="3">
         <v>272200</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>321300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>388700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>425300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>309800</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>429800</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>347600</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>349200</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>328400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>210100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>-350900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>512300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>459800</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>395400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>508600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>564100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>471000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>446000</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>414800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>92100</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>291300</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>318100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>332400</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>410400</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>306400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>352000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>419500</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>451300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>387100</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>458100</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>492300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>462600</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>382600</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>412800</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>5200</v>
+      </c>
+      <c r="E22" s="3">
         <v>6400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>9900</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>11200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>12600</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>14900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>17400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>20100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>22900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>14600</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>13800</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>12100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>11500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12200</v>
-      </c>
-      <c r="R22" s="3">
-        <v>14900</v>
       </c>
       <c r="S22" s="3">
         <v>14900</v>
       </c>
       <c r="T22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="U22" s="3">
         <v>15200</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>15900</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>14900</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>13000</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>8700</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>11000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AA22" s="3">
-        <v>10500</v>
       </c>
       <c r="AB22" s="3">
         <v>10500</v>
       </c>
       <c r="AC22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AD22" s="3">
         <v>14400</v>
       </c>
-      <c r="AD22" s="3">
+      <c r="AE22" s="3">
         <v>9000</v>
       </c>
-      <c r="AE22" s="3">
+      <c r="AF22" s="3">
         <v>7900</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AG22" s="3">
-        <v>7300</v>
       </c>
       <c r="AH22" s="3">
         <v>7300</v>
       </c>
       <c r="AI22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AJ22" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ22" s="3">
+      <c r="AK22" s="3">
         <v>8200</v>
       </c>
-      <c r="AK22" s="3">
+      <c r="AL22" s="3">
         <v>8500</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>180500</v>
+      </c>
+      <c r="E23" s="3">
         <v>90100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>111500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>201800</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>199800</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>132800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>153600</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>-745300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>128000</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>109200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>36500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>-518100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>358700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>306900</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>239800</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>345000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>400700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>304500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>273600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>248600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>-75000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>137100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>153400</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>178200</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>259400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>158600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>198500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>277500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>316400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>256900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>332500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>371600</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>344400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>269400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>300000</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>34000</v>
+      </c>
+      <c r="E24" s="3">
         <v>17500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>18300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>39800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>42300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>27800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>14200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>15000</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>26800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>28900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>2900</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>15600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>78200</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>61400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>50700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>73800</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>64200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>67700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>25200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>43200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>-26400</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>26700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-111300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>22500</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>56700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>37000</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>49500</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>118800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>47600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>46300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>100500</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>82700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>68400</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>65500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2574,228 +2623,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E26" s="3">
         <v>72600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>93200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>162000</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>157500</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>105000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>139400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>-760300</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>101200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>80300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>33600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>-533700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>280500</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>245400</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>189100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>271200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>336500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>236800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>248400</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>205500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>-48600</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>110500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>264700</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>155700</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>202700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>121600</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>258200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>228000</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>197500</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>209200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>286100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>271000</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>261700</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>201100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>234500</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E27" s="3">
         <v>72600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>93200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>162000</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>157400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>105000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>139500</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>-760400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>101200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>80200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>33500</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>-534000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>280400</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>245300</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>189100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>271000</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>336300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>236800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>248200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>205100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>-48300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>110500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>264700</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>155500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>202400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>121600</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>254600</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>226300</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>196600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>208500</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>285600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>270000</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>260700</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>200600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>233700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2904,8 +2962,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2936,8 +2997,8 @@
       <c r="L29" s="3">
         <v>0</v>
       </c>
-      <c r="M29" s="3" t="s">
-        <v>8</v>
+      <c r="M29" s="3">
+        <v>0</v>
       </c>
       <c r="N29" s="3" t="s">
         <v>8</v>
@@ -2945,8 +3006,8 @@
       <c r="O29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P29" s="3">
-        <v>0</v>
+      <c r="P29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q29" s="3">
         <v>0</v>
@@ -2966,17 +3027,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2984,11 +3045,11 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2996,11 +3057,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AH29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3014,8 +3075,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3124,8 +3188,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3234,228 +3301,237 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-1600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>1100</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>3900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>8500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-2200</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>600</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>10000</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-1300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-2800</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>2500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>1100</v>
       </c>
-      <c r="R32" s="3">
-        <v>0</v>
-      </c>
       <c r="S32" s="3">
+        <v>0</v>
+      </c>
+      <c r="T32" s="3">
         <v>-11200</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-2300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-6700</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-700</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2600</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>5700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>500</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>2100</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>4000</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>3800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>1300</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E33" s="3">
         <v>72600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>93200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>162000</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>157400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>105000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>139500</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>-760400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>101200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>80200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>33500</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>-534000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>280400</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>245300</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>189100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>271000</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>336300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>236800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>248200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>205100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>-48300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>110500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>264700</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>155500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>202400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>121600</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>226400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>226300</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>196600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>208500</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>240400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>270000</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>260700</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>200600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>233700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3564,233 +3640,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E35" s="3">
         <v>72600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>93200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>162000</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>157400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>105000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>139500</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>-760400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>101200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>80200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>33500</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>-534000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>280400</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>245300</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>189100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>271000</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>336300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>236800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>248200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>205100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>-48300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>110500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>264700</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>155500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>202400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>121600</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>226400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>226300</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>196600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>208500</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>240400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>270000</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>260700</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>200600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>233700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E38" s="2">
         <v>45745</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45657</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45563</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45472</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45381</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45199</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45108</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45017</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44926</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44835</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44744</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44653</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44561</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44471</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44380</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44289</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44196</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44100</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44009</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43918</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43830</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43736</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43645</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43554</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43465</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43372</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43281</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43190</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43008</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42826</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42735</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3829,8 +3914,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3869,118 +3955,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>546700</v>
+      </c>
+      <c r="E41" s="3">
         <v>702500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>666600</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>424000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>497400</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>658500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>642600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>518500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>570900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>572900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>509600</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>327000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>224000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>230600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>268900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>1128000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>753700</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>557300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>768600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>781200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>737700</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>263100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>134800</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>111300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>128100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>105700</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>119100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>91400</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>518200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>114800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>84900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>84500</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>130200</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>188400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>121700</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4009,40 +4099,40 @@
         <v>0</v>
       </c>
       <c r="L42" s="3">
+        <v>0</v>
+      </c>
+      <c r="M42" s="3">
         <v>150000</v>
       </c>
-      <c r="M42" s="3">
+      <c r="N42" s="3">
         <v>158000</v>
       </c>
-      <c r="N42" s="3">
+      <c r="O42" s="3">
         <v>110000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>265000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>310000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>323000</v>
       </c>
-      <c r="R42" s="3">
-        <v>0</v>
-      </c>
       <c r="S42" s="3">
+        <v>0</v>
+      </c>
+      <c r="T42" s="3">
         <v>662400</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>782300</v>
       </c>
-      <c r="U42" s="3">
+      <c r="V42" s="3">
         <v>571700</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>407800</v>
-      </c>
-      <c r="W42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X42" s="3" t="s">
         <v>8</v>
@@ -4059,8 +4149,8 @@
       <c r="AB42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC42" s="3">
-        <v>0</v>
+      <c r="AC42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD42" s="3">
         <v>0</v>
@@ -4089,448 +4179,463 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2254800</v>
+      </c>
+      <c r="E43" s="3">
         <v>2129700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>1804200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2043400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2018500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>2007200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>1874700</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>1943100</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2087100</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>2052400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1904800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2003300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2105800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2044700</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>1840000</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>1880500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2017600</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1813900</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1709500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1711000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1586400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1644800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1526600</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1787200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1819500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2709900</v>
+      </c>
+      <c r="E44" s="3">
         <v>2610400</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2513600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2612100</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2579900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2527700</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2551900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2519700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2618700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2729900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2793800</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2900100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2826000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2513200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2391700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2215600</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2082000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>1996600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>1913000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1842000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1922000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>2195400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>2282300</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2338000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2367600</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>18700</v>
+      </c>
+      <c r="E45" s="3">
         <v>23100</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>22300</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>20800</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>16800</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>15800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>19300</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>22400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>22500</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>21900</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>528900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>514000</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>519900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>466200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>414800</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>421900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>434900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>416000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>400800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>410000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>499800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>509800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>485700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>491400</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>493100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>501600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>496500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>487100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>456300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>447300</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>481300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>345500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>374900</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>307800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>297900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6064900</v>
+      </c>
+      <c r="E46" s="3">
         <v>5977900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>5496900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5621400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5641300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5721700</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5604300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5504300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5851300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>6061100</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5895100</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5854300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5940700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5564700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5238400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5646100</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5950600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5566000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5363700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5152000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>4746000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>4613000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4429500</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4727800</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4808300</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4561,8 +4666,8 @@
       <c r="L47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
+      <c r="M47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N47" s="3">
         <v>0</v>
@@ -4639,228 +4744,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5187900</v>
+      </c>
+      <c r="E48" s="3">
         <v>5032100</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>4953900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5142900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5155400</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5298700</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5421700</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5193300</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5357600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5342000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5049000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>4924900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>4986800</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4937400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>5026800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4827900</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4842700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4769900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4914400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4708300</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4752600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4804200</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>5021900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4934700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5058000</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2044600</v>
+      </c>
+      <c r="E49" s="3">
         <v>1950000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>1904000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2019300</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1978100</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1994000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2035000</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1979900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2919000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2915500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2785700</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2651100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>3392700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>3462900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3507900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3523500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3531900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3516600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3602400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3493400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3452700</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3424000</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3498900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3436200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3516300</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4969,8 +5083,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5079,8 +5196,11 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5111,86 +5231,89 @@
       <c r="L52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M52" s="3">
+      <c r="M52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N52" s="3">
         <v>390600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>370700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>369200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>421700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>451400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>452800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>467600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>437600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>447300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>430500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>418100</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>415700</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>436400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>294100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>423400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>421300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>407100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>399400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>393700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>389900</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>387900</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>390900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>391200</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>357500</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>279700</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5299,118 +5422,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13778800</v>
+      </c>
+      <c r="E54" s="3">
         <v>13408500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>12778600</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13313200</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13279600</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>13531500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13559800</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13138500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>14585200</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>14763500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14120400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>13801000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14689500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14386700</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14224500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14450300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14792800</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14290100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14327800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>13784200</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>13369400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13256900</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13386700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13392800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13806100</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5449,8 +5578,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5489,668 +5619,687 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1173100</v>
+      </c>
+      <c r="E57" s="3">
         <v>1124600</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>978500</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1061200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1082800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1101900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1038000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1082400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1184100</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1211700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1094000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1217700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1359200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1296100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1228600</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1147000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1131200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1064800</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1016900</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>989900</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>845300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>899200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>825000</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>964100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>976200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>914200</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>811900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>925200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>951200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>897500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>810000</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>859900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>871400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>780500</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>729400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>575000</v>
+      </c>
+      <c r="E58" s="3">
         <v>797900</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>667900</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>576900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>827900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>1040800</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>1110600</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1029100</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1144100</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1163000</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>840600</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1542100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1498900</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1546500</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>624500</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>588700</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>958800</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>953900</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>377300</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>356100</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>135400</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>1210500</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>1051500</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1273200</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1891500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>30000</v>
+      </c>
+      <c r="E59" s="3">
         <v>29600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>31000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>35100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>34400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>34500</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>39800</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>39200</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>47100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>41200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>1135700</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>1144900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1066300</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1029100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1093200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1166100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1088900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>988600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>977100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1041100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>891600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>761600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>836100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>877400</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>838000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>756700</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>712000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>698200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>638400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>566500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>641600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>664300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>595200</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>549900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>606200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2853200</v>
+      </c>
+      <c r="E60" s="3">
         <v>2972400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2672300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2771000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2937700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>3120100</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>3145900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3188600</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3287900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3318400</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3070300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3904700</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3924400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3871600</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>2946400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>2901700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3178900</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>3007300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2371200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>2387100</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>1872200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2871300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2712600</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>3114700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>3705800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2054100</v>
+      </c>
+      <c r="E61" s="3">
         <v>1990300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>1960400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2014400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1993100</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2016300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2039300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1990600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2323900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2569300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1978600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>1020000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1052100</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1088400</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1700300</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1710200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1723300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1719100</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>2356900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>2282800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2573200</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>1514000</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>1518400</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1483600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1169500</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>334400</v>
+      </c>
+      <c r="E62" s="3">
         <v>340400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>328400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>343900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>335100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>361500</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>348000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>340300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>356100</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>341400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>1053700</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>1051200</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1106100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1139100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1149700</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1085900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1116700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1064600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1058500</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>947300</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>999200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1024000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>1029300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1029200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1109200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>877200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>912100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>870500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>801900</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>783100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>755000</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>713100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>677900</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>576300</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6259,8 +6408,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6369,8 +6521,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6479,118 +6634,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5481200</v>
+      </c>
+      <c r="E66" s="3">
         <v>5546600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5221700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5457500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5627100</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5883700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5930700</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5867100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>6373100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>6657800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6108900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>5982300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6088900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6105700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5803100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>5704800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6025700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5797600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5793400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5623600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5450600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5415600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5266800</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5634000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5991000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6629,8 +6790,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6739,8 +6901,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6849,8 +7014,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6959,8 +7127,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7069,118 +7240,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7476100</v>
+      </c>
+      <c r="E72" s="3">
         <v>7372200</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7325100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7306800</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7144800</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7075200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>6970200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>6830800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7591200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>7490000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7409800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7376300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7910700</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7630800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7692100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7930000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7867800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7673100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7559200</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7430900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7225800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7274100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7232300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>6991100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>6903300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7289,8 +7466,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7399,8 +7579,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7509,118 +7692,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8292100</v>
+      </c>
+      <c r="E76" s="3">
         <v>7856100</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>7551400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7849500</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7646500</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7641900</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7623100</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7265500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>8206100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>8099500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8011500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>7818800</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8600600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8281000</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8421400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8745500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8767100</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8492400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8534300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8160700</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>7918800</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>7841400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8119800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7758800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7815100</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7729,233 +7918,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45836</v>
+      </c>
+      <c r="E80" s="2">
         <v>45745</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45657</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45563</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45472</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45381</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45199</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45108</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45017</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44926</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44835</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44744</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44653</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44561</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44471</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44380</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44289</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44196</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44100</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44009</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43918</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43830</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43736</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43645</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43554</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43465</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43372</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43281</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43190</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43008</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42917</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42826</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42735</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>146500</v>
+      </c>
+      <c r="E81" s="3">
         <v>72600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>93200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>162000</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>157400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>105000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>139500</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>-760400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>101200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>80200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>33500</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>-534000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>280400</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>245300</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>189100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>271000</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>336300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>236800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>248200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>205100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>-48300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>110500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>264700</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>155500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>202400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>121600</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>226400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>226300</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>196600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>208500</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>240400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>270000</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>260700</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>200600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>233700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7994,118 +8192,122 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>164800</v>
+      </c>
+      <c r="E83" s="3">
         <v>147200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>267500</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>142600</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>149600</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>162700</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>151800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>146500</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>134700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>134200</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>159000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>153500</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>141600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>141400</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>143400</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>148600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>148500</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>151200</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>156600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>151300</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>154100</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>145500</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>153800</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>144900</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>140500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>137300</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>139100</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>133000</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>127000</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>122700</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>118400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>113500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>109800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>105000</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>104400</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8214,8 +8416,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8324,8 +8529,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8434,8 +8642,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8544,8 +8755,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8654,118 +8868,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>206300</v>
+      </c>
+      <c r="E89" s="3">
         <v>3700</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>397000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>319600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>233600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>183700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>296300</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>512000</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>263600</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>257300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>241700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>224800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>147700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>55000</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>212400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>498700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>338400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>259600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>407800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>598500</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>568500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>195000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>440700</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>411800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>396200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>170100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>286900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>273500</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>437800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>183200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>319400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>460300</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>248000</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>165900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>342900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8804,118 +9024,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="E91" s="3">
         <v>-89100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-160800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-115400</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-91400</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-86800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-240300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-127400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-116700</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-128500</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-150700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-150000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-150600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-129500</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-300900</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-147700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-112700</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-114700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-160100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-69100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-80600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-115600</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-139800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9024,8 +9248,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9134,118 +9361,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-80200</v>
+      </c>
+      <c r="E94" s="3">
         <v>-89100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-160800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-115400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-91400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-86800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-240300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-127400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>37300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-639900</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-251000</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-153300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-105600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-115500</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-670700</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>442500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>4800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-333300</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-324100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-420200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-77000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-133400</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-141600</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-120600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-142100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9284,8 +9517,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9316,8 +9550,8 @@
       <c r="L96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M96" s="3">
-        <v>0</v>
+      <c r="M96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N96" s="3">
         <v>0</v>
@@ -9394,8 +9628,11 @@
       <c r="AL96" s="3">
         <v>0</v>
       </c>
+      <c r="AM96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9504,8 +9741,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9614,8 +9854,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9724,334 +9967,346 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-295900</v>
+      </c>
+      <c r="E100" s="3">
         <v>90800</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>22100</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-270100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-305400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-76100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>63200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-430100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-294700</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>451000</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>197300</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>39900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-51800</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>9000</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-397300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-559200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-155600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-120200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-119100</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-132000</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-24200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>87200</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-279600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-304900</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>26800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>46500</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>221400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>86600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>16300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>166400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>90900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>2100</v>
+      </c>
+      <c r="E101" s="3">
         <v>-4900</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>4900</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-6900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-8200</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-5100</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-5400</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8400</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>3100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>13300</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-5400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>-8400</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>3100</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>13300</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-3500</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>-7700</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>8900</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-17500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>22800</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-2700</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>7400</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-20400</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>4000</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>600</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>1500</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>1600</v>
       </c>
-      <c r="AG101" s="3">
-        <v>0</v>
-      </c>
       <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI101" s="3">
         <v>4100</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ101" s="3">
+      <c r="AK101" s="3">
         <v>12100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>700</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-155800</v>
+      </c>
+      <c r="E102" s="3">
         <v>35900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>242600</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-73400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-161100</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>15900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>124100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-52400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2000</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>63300</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>182700</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>103000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-6600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-38300</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-859100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>374400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>196400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-211400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-12600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>43500</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>474600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>128300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>23500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-16800</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>22400</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>27700</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>403400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>30000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>66800</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>9600</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,515 +656,527 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="18" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="22" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="38" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="39" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E7" s="2">
         <v>45927</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45836</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45745</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45657</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45563</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45472</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45381</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45199</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45108</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45017</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44926</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44835</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44744</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44653</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44561</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44471</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44380</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44289</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44196</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44100</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44009</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43918</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43830</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43736</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43645</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43554</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43465</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43372</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43281</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43190</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43008</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42917</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42826</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42735</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2699700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2757900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2802100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2525800</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2637200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2719000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2801300</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2679400</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2612300</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2766100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2950500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2806200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2650700</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2917500</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>3153200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3015700</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>2760700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2817000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2953800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2669000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2641800</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2574900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2049800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2285800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2424500</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2519200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2584500</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2031300</v>
+      </c>
+      <c r="E9" s="3">
         <v>2058900</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2061500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>1917300</v>
       </c>
-      <c r="G9" s="3">
-        <v>1992700</v>
-      </c>
       <c r="H9" s="3">
+        <v>1993900</v>
+      </c>
+      <c r="I9" s="3">
         <v>2010000</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2042300</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2024400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>1963400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>2031400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2188100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2133700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2060300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2173500</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2279300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2212600</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2020900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>1979200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>2046300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>1867100</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1880800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1851000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1629800</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1657500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1759300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1820000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1842000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>668400</v>
+      </c>
+      <c r="E10" s="3">
         <v>699000</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>740600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>608500</v>
       </c>
-      <c r="G10" s="3">
-        <v>644500</v>
-      </c>
       <c r="H10" s="3">
+        <v>643300</v>
+      </c>
+      <c r="I10" s="3">
         <v>709000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>759000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>655000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>648900</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>734700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>762400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>672500</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>590400</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>744000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>873900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>803100</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>739800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>837900</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>907500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>801900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>761000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>723900</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>420000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>628300</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>665200</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>699200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>742500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>657500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>656700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>730600</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>778600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>719200</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AJ10" s="3">
-        <v>792100</v>
       </c>
       <c r="AK10" s="3">
         <v>792100</v>
       </c>
       <c r="AL10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AM10" s="3">
         <v>683100</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>703300</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1205,8 +1217,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1321,8 +1334,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1437,163 +1453,169 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>122300</v>
+      </c>
+      <c r="E14" s="3">
         <v>47100</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>29400</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>25300</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>43500</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>19500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>41400</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>7900</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>104600</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>923200</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>41700</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>32200</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>43400</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>730300</v>
-      </c>
-      <c r="Q14" s="3">
-        <v>1900</v>
       </c>
       <c r="R14" s="3">
         <v>1900</v>
       </c>
       <c r="S14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="T14" s="3">
         <v>4600</v>
       </c>
-      <c r="T14" s="3">
+      <c r="U14" s="3">
         <v>1100</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>6800</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>11200</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>26100</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>26500</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>67200</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>12700</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>41800</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>74700</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>8900</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>35700</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>20600</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>19900</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>16000</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>22100</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>15200</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>13900</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>15900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>4000</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>16200</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>176300</v>
+      </c>
+      <c r="E15" s="3">
         <v>170300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>155600</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>150400</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>156400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>156200</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>171500</v>
-      </c>
-      <c r="J15" s="3">
-        <v>154200</v>
       </c>
       <c r="K15" s="3">
         <v>154200</v>
       </c>
       <c r="L15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="M15" s="3">
         <v>149600</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>156600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>169900</v>
       </c>
-      <c r="O15" s="3">
-        <v>0</v>
-      </c>
       <c r="P15" s="3">
         <v>0</v>
       </c>
@@ -1639,8 +1661,8 @@
       <c r="AD15" s="3">
         <v>0</v>
       </c>
-      <c r="AE15" s="3" t="s">
-        <v>8</v>
+      <c r="AE15" s="3">
+        <v>0</v>
       </c>
       <c r="AF15" s="3" t="s">
         <v>8</v>
@@ -1651,8 +1673,8 @@
       <c r="AH15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI15" s="3">
-        <v>0</v>
+      <c r="AI15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AJ15" s="3">
         <v>0</v>
@@ -1669,8 +1691,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1708,240 +1733,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2509100</v>
+      </c>
+      <c r="E17" s="3">
         <v>2574100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2584000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2404500</v>
       </c>
-      <c r="G17" s="3">
-        <v>2471900</v>
-      </c>
       <c r="H17" s="3">
+        <v>2473100</v>
+      </c>
+      <c r="I17" s="3">
         <v>2487200</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2545900</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2524900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2340600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2576600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2755700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2648300</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2589600</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>3423100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>2785300</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2694900</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2507600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2457000</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2549400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2351500</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2359000</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2312100</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2114400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2134300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2264400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2344100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2317600</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>190600</v>
+      </c>
+      <c r="E18" s="3">
         <v>183800</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>218100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>121300</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
+        <v>164100</v>
+      </c>
+      <c r="I18" s="3">
+        <v>231800</v>
+      </c>
+      <c r="J18" s="3">
+        <v>255400</v>
+      </c>
+      <c r="K18" s="3">
+        <v>154500</v>
+      </c>
+      <c r="L18" s="3">
+        <v>271700</v>
+      </c>
+      <c r="M18" s="3">
+        <v>189500</v>
+      </c>
+      <c r="N18" s="3">
+        <v>194800</v>
+      </c>
+      <c r="O18" s="3">
+        <v>157900</v>
+      </c>
+      <c r="P18" s="3">
+        <v>61100</v>
+      </c>
+      <c r="Q18" s="3">
+        <v>-505600</v>
+      </c>
+      <c r="R18" s="3">
+        <v>367900</v>
+      </c>
+      <c r="S18" s="3">
+        <v>320800</v>
+      </c>
+      <c r="T18" s="3">
+        <v>253100</v>
+      </c>
+      <c r="U18" s="3">
+        <v>360000</v>
+      </c>
+      <c r="V18" s="3">
+        <v>404400</v>
+      </c>
+      <c r="W18" s="3">
+        <v>317500</v>
+      </c>
+      <c r="X18" s="3">
+        <v>282800</v>
+      </c>
+      <c r="Y18" s="3">
+        <v>262800</v>
+      </c>
+      <c r="Z18" s="3">
+        <v>-64600</v>
+      </c>
+      <c r="AA18" s="3">
+        <v>151500</v>
+      </c>
+      <c r="AB18" s="3">
+        <v>160100</v>
+      </c>
+      <c r="AC18" s="3">
+        <v>175100</v>
+      </c>
+      <c r="AD18" s="3">
+        <v>266900</v>
+      </c>
+      <c r="AE18" s="3">
         <v>165300</v>
       </c>
-      <c r="H18" s="3">
-        <v>231800</v>
-      </c>
-      <c r="I18" s="3">
-        <v>255400</v>
-      </c>
-      <c r="J18" s="3">
-        <v>154500</v>
-      </c>
-      <c r="K18" s="3">
-        <v>271700</v>
-      </c>
-      <c r="L18" s="3">
-        <v>189500</v>
-      </c>
-      <c r="M18" s="3">
-        <v>194800</v>
-      </c>
-      <c r="N18" s="3">
-        <v>157900</v>
-      </c>
-      <c r="O18" s="3">
-        <v>61100</v>
-      </c>
-      <c r="P18" s="3">
-        <v>-505600</v>
-      </c>
-      <c r="Q18" s="3">
-        <v>367900</v>
-      </c>
-      <c r="R18" s="3">
-        <v>320800</v>
-      </c>
-      <c r="S18" s="3">
-        <v>253100</v>
-      </c>
-      <c r="T18" s="3">
-        <v>360000</v>
-      </c>
-      <c r="U18" s="3">
-        <v>404400</v>
-      </c>
-      <c r="V18" s="3">
-        <v>317500</v>
-      </c>
-      <c r="W18" s="3">
-        <v>282800</v>
-      </c>
-      <c r="X18" s="3">
-        <v>262800</v>
-      </c>
-      <c r="Y18" s="3">
-        <v>-64600</v>
-      </c>
-      <c r="Z18" s="3">
-        <v>151500</v>
-      </c>
-      <c r="AA18" s="3">
-        <v>160100</v>
-      </c>
-      <c r="AB18" s="3">
-        <v>175100</v>
-      </c>
-      <c r="AC18" s="3">
-        <v>266900</v>
-      </c>
-      <c r="AD18" s="3">
-        <v>165300</v>
-      </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>213400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>287200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>326300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>268400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>343500</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>380100</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>355800</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>274700</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>305300</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1982,588 +2014,604 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1100</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>3000</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
-        <v>400</v>
-      </c>
       <c r="H20" s="3">
+        <v>2200</v>
+      </c>
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>1600</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-1100</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-3900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-8500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>2200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-600</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-10000</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>1300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>2800</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-2500</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1100</v>
       </c>
-      <c r="T20" s="3">
-        <v>0</v>
-      </c>
       <c r="U20" s="3">
+        <v>0</v>
+      </c>
+      <c r="V20" s="3">
         <v>11200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>2300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>6700</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>2600</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>4300</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>12400</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>3000</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>2900</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>3200</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>365800</v>
+      </c>
+      <c r="E21" s="3">
         <v>354500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>370700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>272200</v>
       </c>
-      <c r="G21" s="3">
-        <v>321300</v>
-      </c>
       <c r="H21" s="3">
+        <v>318300</v>
+      </c>
+      <c r="I21" s="3">
         <v>388700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>425300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>309800</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>429800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>347600</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>349200</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>328400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>210100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>-350900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>512300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>459800</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>395400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>508600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>564100</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>471000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>446000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>414800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>92100</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>291300</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>318100</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>332400</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>410400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>306400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>352000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>419500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>451300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>387100</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>458100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>492300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>462600</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>382600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>412800</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>5000</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>6400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>9900</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>11200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>12600</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>14900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>17400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>20100</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>22900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>17100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>14600</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>13800</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>12100</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>11500</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>12200</v>
-      </c>
-      <c r="T22" s="3">
-        <v>14900</v>
       </c>
       <c r="U22" s="3">
         <v>14900</v>
       </c>
       <c r="V22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="W22" s="3">
         <v>15200</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>15900</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>14900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>13000</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>8700</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>11000</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AC22" s="3">
-        <v>10500</v>
       </c>
       <c r="AD22" s="3">
         <v>10500</v>
       </c>
       <c r="AE22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AF22" s="3">
         <v>14400</v>
       </c>
-      <c r="AF22" s="3">
+      <c r="AG22" s="3">
         <v>9000</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>7900</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AI22" s="3">
-        <v>7300</v>
       </c>
       <c r="AJ22" s="3">
         <v>7300</v>
       </c>
       <c r="AK22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AL22" s="3">
         <v>8400</v>
       </c>
-      <c r="AL22" s="3">
+      <c r="AM22" s="3">
         <v>8200</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8500</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>66000</v>
+      </c>
+      <c r="E23" s="3">
         <v>132100</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>180500</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>90100</v>
       </c>
-      <c r="G23" s="3">
-        <v>111500</v>
-      </c>
       <c r="H23" s="3">
+        <v>108500</v>
+      </c>
+      <c r="I23" s="3">
         <v>201800</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>199800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>132800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>153600</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>-745300</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>128000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>109200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>36500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>-518100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>358700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>306900</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>239800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>345000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>400700</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>304500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>273600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>248600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>-75000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>137100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>153400</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>178200</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>259400</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>158600</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>198500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>277500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>316400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>256900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>332500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>371600</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>344400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>269400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>300000</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>24000</v>
+      </c>
+      <c r="E24" s="3">
         <v>23300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>34000</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>17500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>18300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>39800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>42300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>27800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>14200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>15000</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>26800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>28900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>15600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>78200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>61400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>50700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>73800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>64200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>67700</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>25200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>43200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>-26400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>26700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-111300</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>22500</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>56700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>37000</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>49500</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>118800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>47600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>46300</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>100500</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>82700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>68400</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>65500</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2678,240 +2726,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E26" s="3">
         <v>108800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>146500</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>72600</v>
       </c>
-      <c r="G26" s="3">
-        <v>93200</v>
-      </c>
       <c r="H26" s="3">
+        <v>90200</v>
+      </c>
+      <c r="I26" s="3">
         <v>162000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>157500</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>105000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>139400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>-760300</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>101200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>80300</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>33600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>-533700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>280500</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>245400</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>189100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>271200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>336500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>236800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>248400</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>205500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>-48600</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>110500</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>264700</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>155700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>202700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>121600</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>258200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>228000</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>197500</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>209200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>286100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>271000</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>261700</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>201100</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>234500</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E27" s="3">
         <v>108800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>146500</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>72600</v>
       </c>
-      <c r="G27" s="3">
-        <v>93200</v>
-      </c>
       <c r="H27" s="3">
+        <v>90200</v>
+      </c>
+      <c r="I27" s="3">
         <v>162000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>157400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>105000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>139500</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>-760400</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>101200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>80200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>33500</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>280400</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>245300</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>189100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>271000</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>336300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>236800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>248200</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>205100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>110500</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>264700</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>155500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>202400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>121600</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>254600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>226300</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>196600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>208500</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>285600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>270000</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>260700</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>200600</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>233700</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3026,8 +3083,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3064,8 +3124,8 @@
       <c r="N29" s="3">
         <v>0</v>
       </c>
-      <c r="O29" s="3" t="s">
-        <v>8</v>
+      <c r="O29" s="3">
+        <v>0</v>
       </c>
       <c r="P29" s="3" t="s">
         <v>8</v>
@@ -3073,8 +3133,8 @@
       <c r="Q29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="R29" s="3">
-        <v>0</v>
+      <c r="R29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="S29" s="3">
         <v>0</v>
@@ -3094,17 +3154,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -3112,11 +3172,11 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3124,11 +3184,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3142,8 +3202,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3258,8 +3321,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3374,240 +3440,249 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1100</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-3000</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
-        <v>-400</v>
-      </c>
       <c r="H32" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-1600</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>1100</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>3900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>8500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-2200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>600</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>10000</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-1300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-2800</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>2500</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1100</v>
       </c>
-      <c r="T32" s="3">
-        <v>0</v>
-      </c>
       <c r="U32" s="3">
+        <v>0</v>
+      </c>
+      <c r="V32" s="3">
         <v>-11200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-2300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-6700</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-2600</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>5700</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>2100</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>4000</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>1300</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>3000</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E33" s="3">
         <v>108800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>146500</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>72600</v>
       </c>
-      <c r="G33" s="3">
-        <v>93200</v>
-      </c>
       <c r="H33" s="3">
+        <v>90200</v>
+      </c>
+      <c r="I33" s="3">
         <v>162000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>157400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>105000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>139500</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>-760400</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>101200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>80200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>33500</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>280400</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>245300</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>189100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>271000</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>336300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>236800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>248200</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>205100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>110500</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>264700</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>155500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>202400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>121600</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>226400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>226300</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>196600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>208500</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>240400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>270000</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>260700</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>200600</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>233700</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3722,245 +3797,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E35" s="3">
         <v>108800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>146500</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>72600</v>
       </c>
-      <c r="G35" s="3">
-        <v>93200</v>
-      </c>
       <c r="H35" s="3">
+        <v>90200</v>
+      </c>
+      <c r="I35" s="3">
         <v>162000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>157400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>105000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>139500</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>-760400</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>101200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>80200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>33500</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>280400</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>245300</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>189100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>271000</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>336300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>236800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>248200</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>205100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>110500</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>264700</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>155500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>202400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>121600</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>226400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>226300</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>196600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>208500</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>240400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>270000</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>260700</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>200600</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>233700</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E38" s="2">
         <v>45927</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45836</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45745</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45657</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45563</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45472</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45381</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45199</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45108</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45017</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44926</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44835</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44744</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44653</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44561</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44471</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44380</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44289</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44196</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44100</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44009</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43918</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43830</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43736</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43645</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43554</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43465</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43372</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43281</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43190</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43008</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42917</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42826</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42735</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4001,8 +4085,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4043,124 +4128,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>856100</v>
+      </c>
+      <c r="E41" s="3">
         <v>516200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>546700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>702500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>666600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>424000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>497400</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>658500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>642600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>518500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>570900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>572900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>509600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>327000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>224000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>230600</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>268900</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>1128000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>753700</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>557300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>768600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>781200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>737700</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>263100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>134800</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>111300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>128100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>105700</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>119100</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>91400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>518200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>114800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>84900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>84500</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>130200</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>188400</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>121700</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4195,40 +4284,40 @@
         <v>0</v>
       </c>
       <c r="N42" s="3">
+        <v>0</v>
+      </c>
+      <c r="O42" s="3">
         <v>150000</v>
       </c>
-      <c r="O42" s="3">
+      <c r="P42" s="3">
         <v>158000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>110000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>265000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>310000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>323000</v>
       </c>
-      <c r="T42" s="3">
-        <v>0</v>
-      </c>
       <c r="U42" s="3">
+        <v>0</v>
+      </c>
+      <c r="V42" s="3">
         <v>662400</v>
       </c>
-      <c r="V42" s="3">
+      <c r="W42" s="3">
         <v>782300</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>571700</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>407800</v>
-      </c>
-      <c r="Y42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Z42" s="3" t="s">
         <v>8</v>
@@ -4245,8 +4334,8 @@
       <c r="AD42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE42" s="3">
-        <v>0</v>
+      <c r="AE42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AF42" s="3">
         <v>0</v>
@@ -4275,472 +4364,487 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>1924100</v>
+      </c>
+      <c r="E43" s="3">
         <v>2249600</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2254800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2129700</v>
       </c>
-      <c r="G43" s="3">
-        <v>1804200</v>
-      </c>
       <c r="H43" s="3">
+        <v>1762100</v>
+      </c>
+      <c r="I43" s="3">
         <v>2043400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2018500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2007200</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>1874700</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1943100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>2087100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2052400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>1904800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>2003300</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2105800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2044700</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>1840000</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1880500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>2017600</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>1813900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1709500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1711000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1586400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1644800</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1526600</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1787200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1819500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2661700</v>
+      </c>
+      <c r="E44" s="3">
         <v>2692900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2709900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2610400</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2513600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2612100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2579900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2527700</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2551900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2519700</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2618700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2729900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2793800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2900100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2826000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2513200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2391700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2215600</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2082000</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>1996600</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1913000</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1842000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1922000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>2195400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2282300</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2338000</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2367600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E45" s="3">
         <v>32800</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>18700</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>23100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>22300</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>20800</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>16800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>15800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>19300</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>22400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>21900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>528900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>514000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>519900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>466200</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>414800</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>421900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>434900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>416000</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>400800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>410000</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>499800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>509800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>485700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>491400</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>493100</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>501600</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>496500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>487100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>456300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>447300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>481300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>345500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>374900</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>307800</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>297900</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>5967100</v>
+      </c>
+      <c r="E46" s="3">
         <v>6007600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6064900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>5977900</v>
       </c>
-      <c r="G46" s="3">
-        <v>5496900</v>
-      </c>
       <c r="H46" s="3">
+        <v>5454800</v>
+      </c>
+      <c r="I46" s="3">
         <v>5621400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5641300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5721700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5604300</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5504300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5851300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>6061100</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>5895100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5854300</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5940700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5564700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5238400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5646100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5950600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5566000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5363700</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5152000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>4746000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4613000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4429500</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4727800</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4808300</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4777,8 +4881,8 @@
       <c r="N47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
+      <c r="O47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P47" s="3">
         <v>0</v>
@@ -4855,240 +4959,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5180700</v>
+      </c>
+      <c r="E48" s="3">
         <v>5079900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5187900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5032100</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>4953900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>5142900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5155400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5298700</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5421700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5193300</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5357600</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5342000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5049000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>4924900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4986800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4937400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>5026800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>4827900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4842700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4769900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4914400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4708300</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4752600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4804200</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>5021900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>4934700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>5058000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>2023500</v>
+      </c>
+      <c r="E49" s="3">
         <v>2032900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2044600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>1950000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1904000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>2019300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>1978100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1994000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>2035000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>1979900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>2919000</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2915500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2785700</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2651100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>3392700</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3462900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3507900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3523500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3531900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3516600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3602400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3493400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3452700</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3424000</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3498900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3436200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3516300</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5203,8 +5316,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5319,8 +5435,11 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5357,86 +5476,89 @@
       <c r="N52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O52" s="3">
+      <c r="O52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P52" s="3">
         <v>390600</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>370700</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>369200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>421700</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>451400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>452800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>467600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>437600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>447300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>430500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>418100</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>415700</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>436400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>294100</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>423400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>421300</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>407100</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>399400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>393700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>389900</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>387900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>390900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>391200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>357500</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>279700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5551,124 +5673,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13687300</v>
+      </c>
+      <c r="E54" s="3">
         <v>13620500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13778800</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13408500</v>
       </c>
-      <c r="G54" s="3">
-        <v>12778600</v>
-      </c>
       <c r="H54" s="3">
+        <v>12736500</v>
+      </c>
+      <c r="I54" s="3">
         <v>13313200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13279600</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13531500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13559800</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13138500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>14585200</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14763500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14120400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>13801000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>14689500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14386700</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14224500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14450300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14792800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14290100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14327800</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>13784200</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13369400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13256900</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13386700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13392800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13806100</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5709,8 +5837,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5751,704 +5880,723 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1088900</v>
+      </c>
+      <c r="E57" s="3">
         <v>1187800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1173100</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1124600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>978500</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>1061200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1082800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1101900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1038000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1082400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1184100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1211700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1094000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1217700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1359200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1296100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1228600</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1147000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1131200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1064800</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1016900</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>989900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>845300</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>899200</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>825000</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>964100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>976200</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>914200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>811900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>925200</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>951200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>897500</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>810000</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>859900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>871400</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>780500</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>729400</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>411700</v>
+      </c>
+      <c r="E58" s="3">
         <v>294800</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>575000</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>797900</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>667900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>576900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>827900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>1040800</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1110600</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1029100</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1144100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1163000</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>840600</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>1542100</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1498900</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1546500</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>624500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>588700</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>958800</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>953900</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>377300</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>356100</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>135400</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>1210500</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1051500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1273200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1891500</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26000</v>
+      </c>
+      <c r="E59" s="3">
         <v>28600</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>30000</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>29600</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>31000</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>35100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>34400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34500</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>39800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>47100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>41200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>1135700</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1144900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1066300</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1029100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1093200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1166100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1088900</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>988600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>977100</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>1041100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>891600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>761600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>836100</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>877400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>838000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>756700</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>712000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>698200</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>638400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>566500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>641600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>664300</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>595200</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>549900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>606200</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2722100</v>
+      </c>
+      <c r="E60" s="3">
         <v>2674400</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2853200</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2972400</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2672300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2771000</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2937700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>3120100</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3145900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3188600</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3287900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3318400</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3070300</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3904700</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3924400</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3871600</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>2946400</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2901700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>3178900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3007300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>2371200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2387100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>1872200</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>2871300</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2712600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>3114700</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3705800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2045600</v>
+      </c>
+      <c r="E61" s="3">
         <v>2043300</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2054100</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>1990300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1960400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>2014400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>1993100</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>2016300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2039300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>1990600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>2323900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2569300</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>1978600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1020000</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1052100</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1088400</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1700300</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1710200</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1723300</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1719100</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>2356900</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2282800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2573200</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>1514000</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1518400</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1483600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1169500</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>355500</v>
+      </c>
+      <c r="E62" s="3">
         <v>345900</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>334400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>340400</v>
       </c>
-      <c r="G62" s="3">
-        <v>328400</v>
-      </c>
       <c r="H62" s="3">
+        <v>333800</v>
+      </c>
+      <c r="I62" s="3">
         <v>343900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>335100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>361500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>348000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>340300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>356100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>341400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>1053700</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1051200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1106100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1139100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1149700</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1085900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1116700</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1064600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1058500</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>947300</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>999200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>1024000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1029300</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1029200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1109200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>877200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>912100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>870500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>801900</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>783100</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>755000</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>713100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>677900</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>576300</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6563,8 +6711,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6679,8 +6830,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6795,124 +6949,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5308600</v>
+      </c>
+      <c r="E66" s="3">
         <v>5279500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5481200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5546600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5221700</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5457500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5627100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5883700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5930700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5867100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>6373100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6657800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6108900</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>5982300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>6088900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6105700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>5803100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5704800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>6025700</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>5797600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5793400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5623600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5450600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5415600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5266800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5634000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5991000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6953,8 +7113,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7069,8 +7230,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7185,8 +7349,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7301,8 +7468,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7417,124 +7587,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7503100</v>
+      </c>
+      <c r="E72" s="3">
         <v>7544300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7476100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7372200</v>
       </c>
-      <c r="G72" s="3">
-        <v>7325100</v>
-      </c>
       <c r="H72" s="3">
+        <v>7283000</v>
+      </c>
+      <c r="I72" s="3">
         <v>7306800</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7144800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7075200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>6970200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6830800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>7591200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7490000</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7409800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7376300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7910700</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7630800</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7692100</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7930000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7867800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7673100</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7559200</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7430900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7225800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7274100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7232300</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>6991100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6903300</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7649,8 +7825,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7765,8 +7944,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7881,124 +8063,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8373300</v>
+      </c>
+      <c r="E76" s="3">
         <v>8335600</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8292100</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>7856100</v>
       </c>
-      <c r="G76" s="3">
-        <v>7551400</v>
-      </c>
       <c r="H76" s="3">
+        <v>7509300</v>
+      </c>
+      <c r="I76" s="3">
         <v>7849500</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7646500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7641900</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7623100</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7265500</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>8206100</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8099500</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8011500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>7818800</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>8600600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8281000</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8421400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8745500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8767100</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8492400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8534300</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8160700</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>7918800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7841400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>8119800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>7758800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7815100</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8113,245 +8301,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46022</v>
+      </c>
+      <c r="E80" s="2">
         <v>45927</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45836</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45745</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45657</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45563</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45472</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45381</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45199</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45108</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45017</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44926</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44835</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44744</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44653</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44561</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44471</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44380</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44289</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44196</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44100</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44009</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43918</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43830</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43736</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43645</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43554</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43465</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43372</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43281</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43190</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43008</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42917</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42826</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42735</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>42000</v>
+      </c>
+      <c r="E81" s="3">
         <v>108800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>146500</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>72600</v>
       </c>
-      <c r="G81" s="3">
-        <v>93200</v>
-      </c>
       <c r="H81" s="3">
+        <v>90200</v>
+      </c>
+      <c r="I81" s="3">
         <v>162000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>157400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>105000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>139500</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>-760400</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>101200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>80200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>33500</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>-534000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>280400</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>245300</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>189100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>271000</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>336300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>236800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>248200</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>205100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>-48300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>110500</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>264700</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>155500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>202400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>121600</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>226400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>226300</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>196600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>208500</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>240400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>270000</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>260700</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>200600</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>233700</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8392,124 +8589,128 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>149500</v>
+      </c>
+      <c r="E83" s="3">
         <v>149200</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>164800</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>147200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>267500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>142600</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>149600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>162700</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>151800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>146500</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>134700</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>134200</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>159000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>153500</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>141600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>141400</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>143400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>148600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>148500</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>151200</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>156600</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>151300</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>154100</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>145500</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>153800</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>144900</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>140500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>137300</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>139100</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>133000</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>127000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>122700</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>118400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>113500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>109800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>105000</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>104400</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8624,8 +8825,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8740,8 +8944,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8856,8 +9063,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8972,8 +9182,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9088,124 +9301,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>459600</v>
+      </c>
+      <c r="E89" s="3">
         <v>386600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>206300</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>3700</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>397000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>319600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>233600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>183700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>296300</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>512000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>263600</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>257300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>241700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>224800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>147700</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>55000</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>212400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>498700</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>338400</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>259600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>407800</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>598500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>568500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>195000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>440700</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>411800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>396200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>170100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>286900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>273500</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>437800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>183200</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>319400</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>460300</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>248000</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>165900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>342900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9246,124 +9465,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-194400</v>
+      </c>
+      <c r="E91" s="3">
         <v>-76300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-80200</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-89100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-160800</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-115400</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-91400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-86800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-240300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-127400</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-116700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-128500</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-150700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-150000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-150600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-129500</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-300900</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-147700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-112700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-114700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-160100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-69100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-80600</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-115600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-139800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9478,8 +9701,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9594,124 +9820,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-196300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-76300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-80200</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-89100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-160800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-115400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-91400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-86800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-240300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-127400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>37300</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-639900</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-251000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-153300</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-105600</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-115500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-670700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>442500</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>4800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-333300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-324100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-420200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-77000</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-133400</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-141600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-120600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-142100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9752,8 +9984,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9790,8 +10023,8 @@
       <c r="N96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O96" s="3">
-        <v>0</v>
+      <c r="O96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P96" s="3">
         <v>0</v>
@@ -9868,8 +10101,11 @@
       <c r="AN96" s="3">
         <v>0</v>
       </c>
+      <c r="AO96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9984,8 +10220,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10100,8 +10339,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10216,352 +10458,364 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>62400</v>
+      </c>
+      <c r="E100" s="3">
         <v>-327300</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-295900</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>90800</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>22100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-270100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-305400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-76100</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>63200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-430100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-294700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>451000</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>197300</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>39900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-51800</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>9000</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-397300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-559200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-155600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-120200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-119100</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-132000</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-24200</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>87200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-279600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-304900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>26800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>46500</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>221400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>86600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>16300</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>166400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>90900</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>-15700</v>
+      </c>
+      <c r="E101" s="3">
         <v>-7500</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>2100</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>-4900</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>-6900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-8200</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-5100</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5400</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-8400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>3100</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>13300</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>-5400</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-8400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>3100</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>13300</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>-3500</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-7700</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>8900</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>-17500</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>22800</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>7400</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>-20400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>4000</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>600</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>1500</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>1600</v>
       </c>
-      <c r="AI101" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK101" s="3">
         <v>4100</v>
       </c>
-      <c r="AK101" s="3">
+      <c r="AL101" s="3">
         <v>1200</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>12100</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>700</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>339900</v>
+      </c>
+      <c r="E102" s="3">
         <v>-30500</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-155800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>35900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>242600</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-73400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-161100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>15900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>124100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-52400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2000</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>63300</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>182700</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>103000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-6600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-38300</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-859100</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>374400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>196400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-211400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-12600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>43500</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>474600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>128300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>23500</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-16800</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>22400</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>27700</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>403400</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>30000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>400</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>66800</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>9600</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>100</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/MHK_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="199" uniqueCount="92">
   <si>
     <t>MHK</t>
   </si>
@@ -656,527 +656,540 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="6.42578125" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="19" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="23" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="20" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="24" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="14.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E7" s="2">
         <v>46022</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45927</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45836</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45745</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45657</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45563</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45472</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45381</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45199</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45108</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45017</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44926</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44835</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44744</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44653</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44561</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44471</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44380</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44289</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44196</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44100</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44009</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43918</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43830</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43736</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43645</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43554</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43465</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43372</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43281</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43008</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42917</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42826</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42735</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>2728700</v>
+      </c>
+      <c r="E8" s="3">
         <v>2699700</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>2757900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>2802100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>2525800</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>2637200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>2719000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>2801300</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>2679400</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>2612300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>2766100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>2950500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>2806200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>2650700</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>2917500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>3153200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>3015700</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>2760700</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>2817000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>2953800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>2669000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>2641800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>2574900</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>2049800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>2285800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>2424500</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>2519200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>2584500</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>2442500</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>2448600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>2545800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>2577000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>2412200</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>2369100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>2448500</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>2453000</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>2220600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>2182600</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>2294100</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>2052000</v>
+      </c>
+      <c r="E9" s="3">
         <v>2031300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>2058900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>2061500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>1917300</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>1993900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>2010000</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>2042300</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>2024400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>1963400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>2031400</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>2188100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>2133700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>2060300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>2173500</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>2279300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>2212600</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>2020900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>1979200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>2046300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>1867100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>1880800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>1851000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>1629800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>1657500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>1759300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>1820000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>1842000</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>1785000</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>1791900</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>1815200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>1798400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>1693000</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>1604100</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>1656400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>1660900</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>1537500</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>1479300</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>1550100</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>676700</v>
+      </c>
+      <c r="E10" s="3">
         <v>668400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>699000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>740600</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>608500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>643300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>709000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>759000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>655000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>648900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>734700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>762400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>672500</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>590400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>744000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>873900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>803100</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>739800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>837900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>907500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>801900</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>761000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>723900</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>420000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>628300</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>665200</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>699200</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>742500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>657500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>656700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>730600</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>778600</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>719200</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>765000</v>
-      </c>
-      <c r="AK10" s="3">
-        <v>792100</v>
       </c>
       <c r="AL10" s="3">
         <v>792100</v>
       </c>
       <c r="AM10" s="3">
+        <v>792100</v>
+      </c>
+      <c r="AN10" s="3">
         <v>683100</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>703300</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>744000</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1218,8 +1231,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1337,8 +1351,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1456,169 +1473,175 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>37600</v>
+      </c>
+      <c r="E14" s="3">
         <v>122300</v>
       </c>
-      <c r="E14" s="3">
+      <c r="F14" s="3">
         <v>47100</v>
       </c>
-      <c r="F14" s="3">
+      <c r="G14" s="3">
         <v>29400</v>
       </c>
-      <c r="G14" s="3">
+      <c r="H14" s="3">
         <v>25300</v>
       </c>
-      <c r="H14" s="3">
+      <c r="I14" s="3">
         <v>43500</v>
       </c>
-      <c r="I14" s="3">
+      <c r="J14" s="3">
         <v>19500</v>
       </c>
-      <c r="J14" s="3">
+      <c r="K14" s="3">
         <v>41400</v>
       </c>
-      <c r="K14" s="3">
+      <c r="L14" s="3">
         <v>7900</v>
       </c>
-      <c r="L14" s="3">
+      <c r="M14" s="3">
         <v>104600</v>
       </c>
-      <c r="M14" s="3">
+      <c r="N14" s="3">
         <v>923200</v>
       </c>
-      <c r="N14" s="3">
+      <c r="O14" s="3">
         <v>41700</v>
       </c>
-      <c r="O14" s="3">
+      <c r="P14" s="3">
         <v>32200</v>
       </c>
-      <c r="P14" s="3">
+      <c r="Q14" s="3">
         <v>43400</v>
       </c>
-      <c r="Q14" s="3">
+      <c r="R14" s="3">
         <v>730300</v>
-      </c>
-      <c r="R14" s="3">
-        <v>1900</v>
       </c>
       <c r="S14" s="3">
         <v>1900</v>
       </c>
       <c r="T14" s="3">
+        <v>1900</v>
+      </c>
+      <c r="U14" s="3">
         <v>4600</v>
       </c>
-      <c r="U14" s="3">
+      <c r="V14" s="3">
         <v>1100</v>
       </c>
-      <c r="V14" s="3">
+      <c r="W14" s="3">
         <v>6800</v>
       </c>
-      <c r="W14" s="3">
+      <c r="X14" s="3">
         <v>11200</v>
       </c>
-      <c r="X14" s="3">
+      <c r="Y14" s="3">
         <v>26100</v>
       </c>
-      <c r="Y14" s="3">
+      <c r="Z14" s="3">
         <v>26500</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="AA14" s="3">
         <v>67200</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AB14" s="3">
         <v>12700</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AC14" s="3">
         <v>41800</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AD14" s="3">
         <v>74700</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AE14" s="3">
         <v>8900</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AF14" s="3">
         <v>35700</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AG14" s="3">
         <v>20600</v>
       </c>
-      <c r="AG14" s="3">
+      <c r="AH14" s="3">
         <v>19900</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AI14" s="3">
         <v>16000</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AJ14" s="3">
         <v>22100</v>
       </c>
-      <c r="AJ14" s="3">
+      <c r="AK14" s="3">
         <v>15200</v>
       </c>
-      <c r="AK14" s="3">
+      <c r="AL14" s="3">
         <v>13900</v>
       </c>
-      <c r="AL14" s="3">
+      <c r="AM14" s="3">
         <v>15900</v>
       </c>
-      <c r="AM14" s="3">
+      <c r="AN14" s="3">
         <v>4000</v>
       </c>
-      <c r="AN14" s="3">
+      <c r="AO14" s="3">
         <v>16200</v>
       </c>
-      <c r="AO14" s="3">
+      <c r="AP14" s="3">
         <v>21300</v>
       </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>181800</v>
+      </c>
+      <c r="E15" s="3">
         <v>176300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>170300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>155600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>150400</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>156400</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>156200</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>171500</v>
-      </c>
-      <c r="K15" s="3">
-        <v>154200</v>
       </c>
       <c r="L15" s="3">
         <v>154200</v>
       </c>
       <c r="M15" s="3">
+        <v>154200</v>
+      </c>
+      <c r="N15" s="3">
         <v>149600</v>
       </c>
-      <c r="N15" s="3">
+      <c r="O15" s="3">
         <v>156600</v>
       </c>
-      <c r="O15" s="3">
+      <c r="P15" s="3">
         <v>169900</v>
       </c>
-      <c r="P15" s="3">
-        <v>0</v>
-      </c>
       <c r="Q15" s="3">
         <v>0</v>
       </c>
@@ -1664,8 +1687,8 @@
       <c r="AE15" s="3">
         <v>0</v>
       </c>
-      <c r="AF15" s="3" t="s">
-        <v>8</v>
+      <c r="AF15" s="3">
+        <v>0</v>
       </c>
       <c r="AG15" s="3" t="s">
         <v>8</v>
@@ -1676,8 +1699,8 @@
       <c r="AI15" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ15" s="3">
-        <v>0</v>
+      <c r="AJ15" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AK15" s="3">
         <v>0</v>
@@ -1694,8 +1717,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1734,246 +1760,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>2579300</v>
+      </c>
+      <c r="E17" s="3">
         <v>2509100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>2574100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>2584000</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>2404500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>2473100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>2487200</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>2545900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>2524900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>2340600</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>2576600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>2755700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>2648300</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>2589600</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>3423100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>2785300</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>2694900</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>2507600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>2457000</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>2549400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>2351500</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>2359000</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>2312100</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>2114400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>2134300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>2264400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>2344100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>2317600</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>2277200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>2235200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>2258600</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>2250700</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>2143800</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>2025600</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>2068400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>2097200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>1945900</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>1877300</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>1915800</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>149400</v>
+      </c>
+      <c r="E18" s="3">
         <v>190600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>183800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>218100</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>121300</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>164100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>231800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>255400</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>154500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>271700</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>189500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>194800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>157900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>61100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>-505600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>367900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>320800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>253100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>360000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>404400</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>317500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>282800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>262800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-64600</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>151500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>160100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>175100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>266900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>165300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>213400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>287200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>326300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>268400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>343500</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>380100</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>355800</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>274700</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>305300</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>378300</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2015,603 +2048,619 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E20" s="3">
         <v>1100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>3000</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>2200</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>1600</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-1100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-3900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-8500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>2200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-600</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-10000</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>1300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>2800</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-2500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1100</v>
       </c>
-      <c r="U20" s="3">
-        <v>0</v>
-      </c>
       <c r="V20" s="3">
+        <v>0</v>
+      </c>
+      <c r="W20" s="3">
         <v>11200</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>2300</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>6700</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>700</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>2600</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-5700</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>4300</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>12400</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>3000</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>3700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-500</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-2100</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-4000</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-3800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-1300</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-3000</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>2900</v>
       </c>
-      <c r="AN20" s="3">
+      <c r="AO20" s="3">
         <v>3200</v>
       </c>
-      <c r="AO20" s="3">
+      <c r="AP20" s="3">
         <v>-3800</v>
       </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>330000</v>
+      </c>
+      <c r="E21" s="3">
         <v>365800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>354500</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>370700</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>272200</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>318300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>388700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>425300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>309800</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>429800</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>347600</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>349200</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>328400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>210100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>-350900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>512300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>459800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>395400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>508600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>564100</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>471000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>446000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>414800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>92100</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>291300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>318100</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>332400</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>410400</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>306400</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>352000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>419500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>451300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>387100</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>458100</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>492300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>462600</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>382600</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>412800</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>478100</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>5000</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>5200</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>6400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>9900</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>11200</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>12600</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>14900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>17400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>20100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>22900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>17100</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>14600</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>13800</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>12100</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>11500</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>12200</v>
-      </c>
-      <c r="U22" s="3">
-        <v>14900</v>
       </c>
       <c r="V22" s="3">
         <v>14900</v>
       </c>
       <c r="W22" s="3">
+        <v>14900</v>
+      </c>
+      <c r="X22" s="3">
         <v>15200</v>
       </c>
-      <c r="X22" s="3">
+      <c r="Y22" s="3">
         <v>15900</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>14900</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>13000</v>
       </c>
-      <c r="AA22" s="3">
+      <c r="AB22" s="3">
         <v>8700</v>
       </c>
-      <c r="AB22" s="3">
+      <c r="AC22" s="3">
         <v>11000</v>
       </c>
-      <c r="AC22" s="3">
+      <c r="AD22" s="3">
         <v>9300</v>
-      </c>
-      <c r="AD22" s="3">
-        <v>10500</v>
       </c>
       <c r="AE22" s="3">
         <v>10500</v>
       </c>
       <c r="AF22" s="3">
+        <v>10500</v>
+      </c>
+      <c r="AG22" s="3">
         <v>14400</v>
       </c>
-      <c r="AG22" s="3">
+      <c r="AH22" s="3">
         <v>9000</v>
       </c>
-      <c r="AH22" s="3">
+      <c r="AI22" s="3">
         <v>7900</v>
       </c>
-      <c r="AI22" s="3">
+      <c r="AJ22" s="3">
         <v>7500</v>
-      </c>
-      <c r="AJ22" s="3">
-        <v>7300</v>
       </c>
       <c r="AK22" s="3">
         <v>7300</v>
       </c>
       <c r="AL22" s="3">
+        <v>7300</v>
+      </c>
+      <c r="AM22" s="3">
         <v>8400</v>
       </c>
-      <c r="AM22" s="3">
+      <c r="AN22" s="3">
         <v>8200</v>
       </c>
-      <c r="AN22" s="3">
+      <c r="AO22" s="3">
         <v>8500</v>
       </c>
-      <c r="AO22" s="3">
+      <c r="AP22" s="3">
         <v>9400</v>
       </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>108200</v>
+      </c>
+      <c r="E23" s="3">
         <v>66000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>132100</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>180500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>90100</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>108500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>201800</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>199800</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>132800</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>153600</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>-745300</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>128000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>109200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>36500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>-518100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>358700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>306900</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>239800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>345000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>400700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>304500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>273600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>248600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-75000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>137100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>153400</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>178200</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>259400</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>158600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>198500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>277500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>316400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>256900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>332500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>371600</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>344400</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>269400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>300000</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>365100</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>-8900</v>
+      </c>
+      <c r="E24" s="3">
         <v>24000</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>23300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>34000</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>17500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>18300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>39800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>42300</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>27800</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>14200</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>15000</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>26800</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>28900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2900</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>15600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>78200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>61400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>50700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>73800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>64200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>67700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>25200</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>43200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>-26400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>26700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-111300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>22500</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>56700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>37000</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-59800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>49500</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>118800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>47600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>46300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>100500</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>82700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>68400</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>65500</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2729,246 +2778,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E26" s="3">
         <v>42000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>108800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>146500</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>72600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>90200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>162000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>157500</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>105000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>139400</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>-760300</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>101200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>80300</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>33600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>-533700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>280500</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>245400</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>189100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>271200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>336500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>236800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>248400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>205500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-48600</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>110500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>264700</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>155700</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>202700</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>121600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>258200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>228000</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>197500</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>209200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>286100</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>271000</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>261700</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>201100</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>234500</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>270800</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E27" s="3">
         <v>42000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>108800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>146500</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>72600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>90200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>162000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>157400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>105000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>139500</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>-760400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>101200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>80200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>33500</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>-534000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>280400</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>245300</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>189100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>271000</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>336300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>236800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>248200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>205100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>110500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>264700</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>155500</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>202400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>121600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>254600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>226300</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>196600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>208500</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>285600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>270000</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>260700</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>200600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>233700</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3086,8 +3144,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3127,8 +3188,8 @@
       <c r="O29" s="3">
         <v>0</v>
       </c>
-      <c r="P29" s="3" t="s">
-        <v>8</v>
+      <c r="P29" s="3">
+        <v>0</v>
       </c>
       <c r="Q29" s="3" t="s">
         <v>8</v>
@@ -3136,8 +3197,8 @@
       <c r="R29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="S29" s="3">
-        <v>0</v>
+      <c r="S29" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="T29" s="3">
         <v>0</v>
@@ -3157,17 +3218,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -3175,11 +3236,11 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>-28200</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -3187,11 +3248,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AK29" s="3">
         <v>-45200</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3205,8 +3266,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3324,8 +3388,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3443,246 +3510,255 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-1200</v>
+      </c>
+      <c r="E32" s="3">
         <v>-1100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-3000</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-2200</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-1600</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>1100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>3900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>8500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-2200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>600</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>10000</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-1300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-2800</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>2500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1100</v>
       </c>
-      <c r="U32" s="3">
-        <v>0</v>
-      </c>
       <c r="V32" s="3">
+        <v>0</v>
+      </c>
+      <c r="W32" s="3">
         <v>-11200</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-2300</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-6700</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-700</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>5700</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>-12400</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>-3000</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>-3700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>500</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>2100</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>4000</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>3800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>1300</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>3000</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>-2900</v>
       </c>
-      <c r="AN32" s="3">
+      <c r="AO32" s="3">
         <v>-3200</v>
       </c>
-      <c r="AO32" s="3">
+      <c r="AP32" s="3">
         <v>3800</v>
       </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E33" s="3">
         <v>42000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>108800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>146500</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>72600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>90200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>162000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>157400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>105000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>139500</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>-760400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>101200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>80200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>33500</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>-534000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>280400</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>245300</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>189100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>271000</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>336300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>236800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>248200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>205100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>110500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>264700</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>155500</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>202400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>121600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>226400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>226300</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>196600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>208500</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>240400</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>270000</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>260700</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>200600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>233700</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3800,251 +3876,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E35" s="3">
         <v>42000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>108800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>146500</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>72600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>90200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>162000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>157400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>105000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>139500</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>-760400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>101200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>80200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>33500</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>-534000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>280400</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>245300</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>189100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>271000</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>336300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>236800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>248200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>205100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>110500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>264700</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>155500</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>202400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>121600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>226400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>226300</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>196600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>208500</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>240400</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>270000</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>260700</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>200600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>233700</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E38" s="2">
         <v>46022</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45927</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45836</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45745</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45657</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45563</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45472</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45381</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45199</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45108</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45017</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44926</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44835</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44744</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44653</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44561</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44471</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44380</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44289</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44196</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44100</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44009</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43918</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43830</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43736</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43645</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43554</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43465</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43372</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43281</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43008</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42917</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42826</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42735</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4086,8 +4171,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4129,127 +4215,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>872300</v>
+      </c>
+      <c r="E41" s="3">
         <v>856100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>516200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>546700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>702500</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>666600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>424000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>497400</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>658500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>642600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>518500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>570900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>572900</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>509600</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>327000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>224000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>230600</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>268900</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>1128000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>753700</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>557300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>768600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>781200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>737700</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>263100</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>134800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>111300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>128100</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>105700</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>119100</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>91400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>518200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>114800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>84900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>84500</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>130200</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>188400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>121700</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>112100</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4287,40 +4377,40 @@
         <v>0</v>
       </c>
       <c r="O42" s="3">
+        <v>0</v>
+      </c>
+      <c r="P42" s="3">
         <v>150000</v>
       </c>
-      <c r="P42" s="3">
+      <c r="Q42" s="3">
         <v>158000</v>
       </c>
-      <c r="Q42" s="3">
+      <c r="R42" s="3">
         <v>110000</v>
       </c>
-      <c r="R42" s="3">
+      <c r="S42" s="3">
         <v>265000</v>
       </c>
-      <c r="S42" s="3">
+      <c r="T42" s="3">
         <v>310000</v>
       </c>
-      <c r="T42" s="3">
+      <c r="U42" s="3">
         <v>323000</v>
       </c>
-      <c r="U42" s="3">
-        <v>0</v>
-      </c>
       <c r="V42" s="3">
+        <v>0</v>
+      </c>
+      <c r="W42" s="3">
         <v>662400</v>
       </c>
-      <c r="W42" s="3">
+      <c r="X42" s="3">
         <v>782300</v>
       </c>
-      <c r="X42" s="3">
+      <c r="Y42" s="3">
         <v>571700</v>
       </c>
-      <c r="Y42" s="3">
+      <c r="Z42" s="3">
         <v>407800</v>
-      </c>
-      <c r="Z42" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA42" s="3" t="s">
         <v>8</v>
@@ -4337,8 +4427,8 @@
       <c r="AE42" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF42" s="3">
-        <v>0</v>
+      <c r="AF42" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AG42" s="3">
         <v>0</v>
@@ -4367,484 +4457,499 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>2092700</v>
+      </c>
+      <c r="E43" s="3">
         <v>1924100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>2249600</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>2254800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>2129700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>1762100</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>2043400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>2018500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>2007200</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>1874700</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>1943100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>2087100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>2052400</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>1904800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>2003300</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>2105800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>2044700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>1840000</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>1880500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>2017600</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>1813900</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>1709500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>1711000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>1586400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>1644800</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>1526600</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>1787200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>1819500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>1743600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>1606200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>1755700</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>1737900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>1689900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>1558200</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>1656100</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>1639600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>1497900</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>1376200</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>1506300</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>2680500</v>
+      </c>
+      <c r="E44" s="3">
         <v>2661700</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>2692900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>2709900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>2610400</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>2513600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>2612100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>2579900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>2527700</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>2551900</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>2519700</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>2618700</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>2729900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>2793800</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>2900100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>2826000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>2513200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>2391700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>2215600</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>2082000</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>1996600</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>1913000</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>1842000</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>1922000</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>2195400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>2282300</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>2338000</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>2367600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>2338100</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>2287600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>2214300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>2061200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>2045000</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>1948700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>1911000</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>1865900</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>1740900</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>1675800</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>1673200</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>10700</v>
+      </c>
+      <c r="E45" s="3">
         <v>13000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>32800</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>18700</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>23100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>22300</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>20800</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>16800</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>15800</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>19300</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>22400</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>22500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>21900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>528900</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>514000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>519900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>466200</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>414800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>421900</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>434900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>416000</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>400800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>410000</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>499800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>509800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>485700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>491400</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>493100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>501600</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>496500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>487100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>456300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>447300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>481300</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>345500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>374900</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>307800</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>297900</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>284600</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>6200200</v>
+      </c>
+      <c r="E46" s="3">
         <v>5967100</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>6007600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>6064900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>5977900</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>5454800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>5621400</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>5641300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>5721700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>5604300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>5504300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>5851300</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>6061100</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>5895100</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>5854300</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>5940700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>5564700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>5238400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>5646100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>5950600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>5566000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>5363700</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>5152000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>4746000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>4613000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>4429500</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>4727800</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>4808300</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>4689000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>4509300</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>4548500</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>4773700</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>4297000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>4073000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>3997100</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>4010700</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>3735000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>3471500</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>3576300</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4884,8 +4989,8 @@
       <c r="O47" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
+      <c r="P47" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q47" s="3">
         <v>0</v>
@@ -4962,246 +5067,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>5057200</v>
+      </c>
+      <c r="E48" s="3">
         <v>5180700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>5079900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>5187900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>5032100</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>4953900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>5142900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>5155400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>5298700</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>5421700</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>5193300</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>5357600</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>5342000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>5049000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>4924900</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>4986800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>4937400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>5026800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>4827900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>4842700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>4769900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>4914400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>4708300</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>4752600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>4804200</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>5021900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>4934700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>5058000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>4995200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>4699900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>4586200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>4421100</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>4460800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>4270800</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>4090100</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>3892300</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>3506200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>3370300</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>3340900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>1995800</v>
+      </c>
+      <c r="E49" s="3">
         <v>2023500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>2032900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>2044600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>1950000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>1904000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>2019300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>1978100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>1994000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>2035000</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>1979900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>2919000</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>2915500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>2785700</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>2651100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>3392700</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>3462900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>3507900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>3523500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>3531900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>3516600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>3602400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>3493400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>3452700</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>3424000</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>3498900</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>3436200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>3516300</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>3499600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>3482800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>3466800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>3305600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>3412600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>3363200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>3344700</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>3295400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>3128900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>3109000</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>3208500</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5319,8 +5433,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5438,8 +5555,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5479,86 +5599,89 @@
       <c r="O52" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P52" s="3">
+      <c r="P52" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q52" s="3">
         <v>390600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>370700</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>369200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>421700</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>451400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>452800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>467600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>437600</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>447300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>430500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>418100</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>415700</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>436400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>294100</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>423400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>421300</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>407100</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>399400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>393700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>389900</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>387900</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>390900</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>391200</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>357500</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>279700</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>294900</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5676,127 +5799,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>13791100</v>
+      </c>
+      <c r="E54" s="3">
         <v>13687300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>13620500</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>13778800</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>13408500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>12736500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>13313200</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>13279600</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>13531500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>13559800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>13138500</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>14585200</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>14763500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>14120400</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>13801000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>14689500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>14386700</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>14224500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>14450300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>14792800</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>14290100</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>14327800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>13784200</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>13369400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>13256900</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>13386700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>13392800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>13806100</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>13605100</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>13099100</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>13000900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>12894000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>12560400</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>12094900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>11822800</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>11589500</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>10727500</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>10230600</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>10420600</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5838,8 +5967,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5881,722 +6011,741 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>1205400</v>
+      </c>
+      <c r="E57" s="3">
         <v>1088900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>1187800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>1173100</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>1124600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>978500</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>1061200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>1082800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>1101900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>1038000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>1082400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>1184100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>1211700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>1094000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>1217700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>1359200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>1296100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>1228600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>1147000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>1131200</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>1064800</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>1016900</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>989900</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>845300</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>899200</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>825000</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>964100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>976200</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>914200</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>811900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>925200</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>951200</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>897500</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>810000</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>859900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>871400</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>780500</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>729400</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>767200</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>501100</v>
+      </c>
+      <c r="E58" s="3">
         <v>411700</v>
       </c>
-      <c r="E58" s="3">
+      <c r="F58" s="3">
         <v>294800</v>
       </c>
-      <c r="F58" s="3">
+      <c r="G58" s="3">
         <v>575000</v>
       </c>
-      <c r="G58" s="3">
+      <c r="H58" s="3">
         <v>797900</v>
       </c>
-      <c r="H58" s="3">
+      <c r="I58" s="3">
         <v>667900</v>
       </c>
-      <c r="I58" s="3">
+      <c r="J58" s="3">
         <v>576900</v>
       </c>
-      <c r="J58" s="3">
+      <c r="K58" s="3">
         <v>827900</v>
       </c>
-      <c r="K58" s="3">
+      <c r="L58" s="3">
         <v>1040800</v>
       </c>
-      <c r="L58" s="3">
+      <c r="M58" s="3">
         <v>1110600</v>
       </c>
-      <c r="M58" s="3">
+      <c r="N58" s="3">
         <v>1029100</v>
       </c>
-      <c r="N58" s="3">
+      <c r="O58" s="3">
         <v>1144100</v>
       </c>
-      <c r="O58" s="3">
+      <c r="P58" s="3">
         <v>1163000</v>
       </c>
-      <c r="P58" s="3">
+      <c r="Q58" s="3">
         <v>840600</v>
       </c>
-      <c r="Q58" s="3">
+      <c r="R58" s="3">
         <v>1542100</v>
       </c>
-      <c r="R58" s="3">
+      <c r="S58" s="3">
         <v>1498900</v>
       </c>
-      <c r="S58" s="3">
+      <c r="T58" s="3">
         <v>1546500</v>
       </c>
-      <c r="T58" s="3">
+      <c r="U58" s="3">
         <v>624500</v>
       </c>
-      <c r="U58" s="3">
+      <c r="V58" s="3">
         <v>588700</v>
       </c>
-      <c r="V58" s="3">
+      <c r="W58" s="3">
         <v>958800</v>
       </c>
-      <c r="W58" s="3">
+      <c r="X58" s="3">
         <v>953900</v>
       </c>
-      <c r="X58" s="3">
+      <c r="Y58" s="3">
         <v>377300</v>
       </c>
-      <c r="Y58" s="3">
+      <c r="Z58" s="3">
         <v>356100</v>
       </c>
-      <c r="Z58" s="3">
+      <c r="AA58" s="3">
         <v>135400</v>
       </c>
-      <c r="AA58" s="3">
+      <c r="AB58" s="3">
         <v>1210500</v>
       </c>
-      <c r="AB58" s="3">
+      <c r="AC58" s="3">
         <v>1051500</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>1273200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>1891500</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>1763300</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>1742400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>1333900</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>1146500</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>1331900</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>1203700</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>1172800</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>1754100</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>1498000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>1382700</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>1548300</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>21200</v>
+      </c>
+      <c r="E59" s="3">
         <v>26000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28600</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>30000</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>29600</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>31000</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>35100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>34400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>34500</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>39800</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>39200</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>47100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>41200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>1135700</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>1144900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>1066300</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>1029100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>1093200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>1166100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>1088900</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>988600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>977100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>1041100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>891600</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>761600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>836100</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>877400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>838000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>756700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>712000</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>698200</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>638400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>566500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>641600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>664300</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>595200</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>549900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>606200</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>667800</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>2871300</v>
+      </c>
+      <c r="E60" s="3">
         <v>2722100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>2674400</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>2853200</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>2972400</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>2672300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>2771000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>2937700</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>3120100</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>3145900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>3188600</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>3287900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>3318400</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>3070300</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>3904700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>3924400</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>3871600</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>2946400</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>2901700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>3178900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>3007300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>2371200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>2387100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>1872200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>2871300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>2712600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>3114700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>3705800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>3434200</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>3266200</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>2957300</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>2736100</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>2795900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>2655400</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>2697000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>3220700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>2828300</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>2718300</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>2983300</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>2022400</v>
+      </c>
+      <c r="E61" s="3">
         <v>2045600</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>2043300</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>2054100</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>1990300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>1960400</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>2014400</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>1993100</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>2016300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>2039300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>1990600</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>2323900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>2569300</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>1978600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>1020000</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>1052100</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>1088400</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>1700300</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>1710200</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>1723300</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>1719100</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>2356900</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>2282800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>2573200</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>1514000</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>1518400</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>1483600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>1169500</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>1498000</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>1515600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>1528600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>1884000</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>1585700</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>1559900</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>1544700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>1174400</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>1132300</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>1128700</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>1165600</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>346600</v>
+      </c>
+      <c r="E62" s="3">
         <v>355500</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>345900</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>334400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>340400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>333800</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>343900</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>335100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>361500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>348000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>340300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>356100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>341400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>1053700</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>1051200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>1106100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>1139100</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>1149700</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>1085900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>1116700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>1064600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>1058500</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>947300</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>999200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>1024000</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>1029300</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>1029200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>1109200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>1095800</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>877200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>912100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>870500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>801900</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>783100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>755000</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>713100</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>677900</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>576300</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>574300</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6714,8 +6863,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6833,8 +6985,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6952,127 +7107,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>5411400</v>
+      </c>
+      <c r="E66" s="3">
         <v>5308600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>5279500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>5481200</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>5546600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>5221700</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>5457500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>5627100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>5883700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>5930700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>5867100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>6373100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>6657800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>6108900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>5982300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>6088900</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>6105700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>5803100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>5704800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>6025700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>5797600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>5793400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>5623600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>5450600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>5415600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>5266800</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>5634000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>5991000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>6034300</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>5665300</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>5437200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>5528500</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>5222400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>5035700</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>5033800</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>5143000</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>4670100</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>4454100</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>4755200</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7114,8 +7275,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7233,8 +7395,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7352,8 +7517,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7471,8 +7639,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7590,127 +7761,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>7555600</v>
+      </c>
+      <c r="E72" s="3">
         <v>7503100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>7544300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>7476100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>7372200</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>7283000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>7306800</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>7144800</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>7075200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>6970200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>6830800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>7591200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>7490000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>7409800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>7376300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>7910700</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>7630800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>7692100</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>7930000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>7867800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>7673100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>7559200</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>7430900</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>7225800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>7274100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>7232300</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>6991100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>6903300</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>6709800</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>6588200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>6635900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>6409600</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>6213000</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>6004500</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>5764100</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>5494100</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>5233500</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>5032900</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>4799200</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7828,8 +8005,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7947,8 +8127,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8066,127 +8249,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>8375600</v>
+      </c>
+      <c r="E76" s="3">
         <v>8373300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>8335600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>8292100</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>7856100</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>7509300</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>7849500</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>7646500</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>7641900</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>7623100</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>7265500</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>8206100</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>8099500</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>8011500</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>7818800</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>8600600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>8281000</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>8421400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>8745500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>8767100</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>8492400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>8534300</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>8160700</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>7918800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>7841400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>8119800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>7758800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>7815100</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>7570800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>7433800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>7563800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>7365600</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>7337900</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>7059200</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>6789100</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>6446500</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>6057400</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>5776500</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>5665400</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8304,251 +8493,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46116</v>
+      </c>
+      <c r="E80" s="2">
         <v>46022</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45927</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45836</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45745</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45657</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45563</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45472</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45381</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45199</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45108</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45017</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44926</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44835</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44744</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44653</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44561</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44471</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44380</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44289</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44196</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44100</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44009</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43918</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43830</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43736</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43645</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43554</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43465</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43372</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43281</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43190</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43008</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42917</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42826</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42735</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42644</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>117100</v>
+      </c>
+      <c r="E81" s="3">
         <v>42000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>108800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>146500</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>72600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>90200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>162000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>157400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>105000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>139500</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>-760400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>101200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>80200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>33500</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>-534000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>280400</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>245300</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>189100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>271000</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>336300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>236800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>248200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>205100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-48300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>110500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>264700</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>155500</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>202400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>121600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>226400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>226300</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>196600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>208500</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>240400</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>270000</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>260700</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>200600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>233700</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>269800</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8590,127 +8788,131 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>143800</v>
+      </c>
+      <c r="E83" s="3">
         <v>149500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>149200</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>164800</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>147200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>267500</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>142600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>149600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>162700</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>151800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>146500</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>134700</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>134200</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>159000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>153500</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>141600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>141400</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>143400</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>148600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>148500</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>151200</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>156600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>151300</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>154100</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>145500</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>153800</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>144900</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>140500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>137300</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>139100</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>133000</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>127000</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>122700</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>118400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>113500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>109800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>105000</v>
       </c>
-      <c r="AN83" s="3">
+      <c r="AO83" s="3">
         <v>104400</v>
       </c>
-      <c r="AO83" s="3">
+      <c r="AP83" s="3">
         <v>103700</v>
       </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8828,8 +9030,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8947,8 +9152,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9066,8 +9274,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9185,8 +9396,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9304,127 +9518,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>110100</v>
+      </c>
+      <c r="E89" s="3">
         <v>459600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>386600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>206300</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>3700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>397000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>319600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>233600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>183700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>296300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>512000</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>263600</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>257300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>241700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>224800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>147700</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>55000</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>212400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>498700</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>338400</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>259600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>407800</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>598500</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>568500</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>195000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>440700</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>411800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>396200</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>170100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>286900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>273500</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>437800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>183200</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>319400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>460300</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>248000</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>165900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>342900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>419900</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9466,127 +9686,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-194400</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-76300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-80200</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-89100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-160800</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-115400</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-91400</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-86800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-240300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-127400</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-116700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-128500</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-150700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-150000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-150600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-129500</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-300900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-147700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-112700</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-114700</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-160100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-69100</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-80600</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-115600</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-139800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-124600</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-144100</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-136900</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-151200</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-144600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-247400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-250900</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-251400</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-229200</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-224200</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-201300</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-211400</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>93100</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9704,8 +9928,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9823,127 +10050,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-102300</v>
+      </c>
+      <c r="E94" s="3">
         <v>-196300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-76300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-80200</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-89100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-160800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-115400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-91400</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-86800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-240300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-127400</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>37300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-639900</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-251000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-153300</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-105600</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-115500</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-670700</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>442500</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>4800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-333300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-324100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-420200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-77000</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-133400</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-141600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-120600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-142100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-211800</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-303900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-542500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-244400</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-241400</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-335300</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-229500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-473800</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-202100</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-211400</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-183800</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9985,8 +10218,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10026,8 +10260,8 @@
       <c r="O96" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P96" s="3">
-        <v>0</v>
+      <c r="P96" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q96" s="3">
         <v>0</v>
@@ -10104,8 +10338,11 @@
       <c r="AO96" s="3">
         <v>0</v>
       </c>
+      <c r="AP96" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10223,8 +10460,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10342,8 +10582,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10461,361 +10704,373 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>11800</v>
+      </c>
+      <c r="E100" s="3">
         <v>62400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-327300</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-295900</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>90800</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>22100</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-270100</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-305400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-76100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>63200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-430100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-294700</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>451000</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>197300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>39900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-51800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>9000</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-397300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-559200</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-155600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-120200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-119100</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-132000</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-24200</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>87200</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-279600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-304900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-232200</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>26800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>46500</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-156500</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>221400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>86600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>16300</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-280600</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>166400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>90900</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-122700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-251900</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
       <c r="D101" s="3">
+        <v>30500</v>
+      </c>
+      <c r="E101" s="3">
         <v>-15700</v>
       </c>
-      <c r="E101" s="3">
+      <c r="F101" s="3">
         <v>-7500</v>
       </c>
-      <c r="F101" s="3">
+      <c r="G101" s="3">
         <v>2100</v>
       </c>
-      <c r="G101" s="3">
+      <c r="H101" s="3">
         <v>-4900</v>
       </c>
-      <c r="H101" s="3">
+      <c r="I101" s="3">
         <v>4900</v>
       </c>
-      <c r="I101" s="3">
+      <c r="J101" s="3">
         <v>-6900</v>
       </c>
-      <c r="J101" s="3">
+      <c r="K101" s="3">
         <v>-8200</v>
       </c>
-      <c r="K101" s="3">
+      <c r="L101" s="3">
         <v>-5100</v>
       </c>
-      <c r="L101" s="3">
+      <c r="M101" s="3">
         <v>-5400</v>
       </c>
-      <c r="M101" s="3">
+      <c r="N101" s="3">
         <v>-8400</v>
       </c>
-      <c r="N101" s="3">
+      <c r="O101" s="3">
         <v>3100</v>
       </c>
-      <c r="O101" s="3">
+      <c r="P101" s="3">
         <v>13300</v>
       </c>
-      <c r="P101" s="3">
+      <c r="Q101" s="3">
         <v>-5400</v>
       </c>
-      <c r="Q101" s="3">
+      <c r="R101" s="3">
         <v>-8400</v>
       </c>
-      <c r="R101" s="3">
+      <c r="S101" s="3">
         <v>3100</v>
       </c>
-      <c r="S101" s="3">
+      <c r="T101" s="3">
         <v>13300</v>
       </c>
-      <c r="T101" s="3">
+      <c r="U101" s="3">
         <v>-3500</v>
       </c>
-      <c r="U101" s="3">
+      <c r="V101" s="3">
         <v>-7700</v>
       </c>
-      <c r="V101" s="3">
+      <c r="W101" s="3">
         <v>8900</v>
       </c>
-      <c r="W101" s="3">
+      <c r="X101" s="3">
         <v>-17500</v>
       </c>
-      <c r="X101" s="3">
+      <c r="Y101" s="3">
         <v>22800</v>
       </c>
-      <c r="Y101" s="3">
+      <c r="Z101" s="3">
         <v>-2700</v>
       </c>
-      <c r="Z101" s="3">
+      <c r="AA101" s="3">
         <v>7400</v>
       </c>
-      <c r="AA101" s="3">
+      <c r="AB101" s="3">
         <v>-20400</v>
       </c>
-      <c r="AB101" s="3">
+      <c r="AC101" s="3">
         <v>4000</v>
       </c>
-      <c r="AC101" s="3">
+      <c r="AD101" s="3">
         <v>-3100</v>
       </c>
-      <c r="AD101" s="3">
+      <c r="AE101" s="3">
         <v>600</v>
       </c>
-      <c r="AE101" s="3">
+      <c r="AF101" s="3">
         <v>1500</v>
       </c>
-      <c r="AF101" s="3">
+      <c r="AG101" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG101" s="3">
+      <c r="AH101" s="3">
         <v>-1400</v>
       </c>
-      <c r="AH101" s="3">
+      <c r="AI101" s="3">
         <v>-11400</v>
       </c>
-      <c r="AI101" s="3">
+      <c r="AJ101" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ101" s="3">
-        <v>0</v>
-      </c>
       <c r="AK101" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL101" s="3">
         <v>4100</v>
       </c>
-      <c r="AL101" s="3">
+      <c r="AM101" s="3">
         <v>1200</v>
       </c>
-      <c r="AM101" s="3">
+      <c r="AN101" s="3">
         <v>12100</v>
       </c>
-      <c r="AN101" s="3">
+      <c r="AO101" s="3">
         <v>700</v>
       </c>
-      <c r="AO101" s="3">
+      <c r="AP101" s="3">
         <v>500</v>
       </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E102" s="3">
         <v>339900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-30500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-155800</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>35900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>242600</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-73400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-161100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>15900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>124100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-52400</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>63300</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>182700</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>103000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-6600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-38300</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-859100</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>374400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>196400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-211400</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-12600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>43500</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>474600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>128300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>23500</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-16800</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>22400</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-13400</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>27700</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-426900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>403400</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>30000</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>400</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-45700</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-58200</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>66800</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>9600</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>100</v>
       </c>
     </row>
